--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -1,39 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1375601-CD6E-4AD3-ABD6-8667D2F0AD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -42,7 +48,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -53,7 +58,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为0：</t>
@@ -62,20 +66,10 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">道具ID，道具数量
+道具ID，道具数量
 </t>
         </r>
         <r>
@@ -83,7 +77,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为1：</t>
@@ -92,60 +85,14 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">出现概率，
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">道具ID，
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">道具数量，
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">购买次数， 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">购买类型（ 0 表示 金币  1表示钻石）
+出现概率，
+道具ID，
+道具数量，
+购买次数， 
+购买类型（ 0 表示 金币  1表示钻石）
 </t>
         </r>
         <r>
@@ -153,7 +100,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为2：</t>
@@ -162,20 +108,10 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">出现最小等级，出现最大等级，道具ID，道具数量
+出现最小等级，出现最大等级，道具ID，道具数量
 </t>
         </r>
         <r>
@@ -183,7 +119,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>商店类型为3：</t>
@@ -192,31 +127,20 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>出现最小等级，出现最大等级，道具ID，道具数量，购买使用什么道具，购买使用道具数量</t>
+出现最小等级，出现最大等级，道具ID，道具数量，购买使用什么道具，购买使用道具数量</t>
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -225,7 +149,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -246,33 +169,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">作者:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>0:</t>
+          <t>作者:
+0:</t>
         </r>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>表示不拉近</t>
@@ -281,38 +194,28 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>1</t>
+1</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：表示拉近</t>
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -321,26 +224,16 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>播放音效</t>
+播放音效</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>ID,</t>
         </r>
@@ -348,7 +241,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>文件存储在</t>
@@ -357,7 +249,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>UI</t>
         </r>
@@ -365,7 +257,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>文件夹下</t>
@@ -374,7 +265,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -382,7 +273,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>多个音效用</t>
@@ -391,7 +281,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>;</t>
         </r>
@@ -399,7 +289,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>号间隔</t>
@@ -408,7 +297,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -416,7 +305,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>将会随机播放一个</t>
@@ -425,7 +313,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -433,7 +321,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>如果有概率不播放就写成</t>
@@ -442,7 +329,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">100;0  </t>
         </r>
@@ -450,7 +337,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>就表示</t>
@@ -459,7 +345,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>50%</t>
         </r>
@@ -467,7 +353,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>概率播放</t>
@@ -476,7 +361,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>100</t>
         </r>
@@ -484,21 +369,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>号音效</t>
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -507,26 +390,16 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>玩家等级在此区间才会显示此</t>
+玩家等级在此区间才会显示此</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">NPC
 </t>
@@ -535,7 +408,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>例如</t>
@@ -544,7 +416,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">:10;20 </t>
         </r>
@@ -552,7 +424,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>表示</t>
@@ -561,7 +432,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> 10-20</t>
         </r>
@@ -569,21 +440,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>级会出现</t>
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -592,91 +461,26 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">0.默认,不执行
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1.NPC出现时间
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2.地图内击败指定数量的怪物
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">3.地图内击败指定ID的怪物后NPC出现
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">4.当自身某个ID的任务完成后出现
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">5.穿戴要求指定数量的装备出现(玩家进地图时)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>6.背包内有某个道具出现(玩家进地图时)</t>
+0.默认,不执行
+1.NPC出现时间
+2.地图内击败指定数量的怪物
+3.地图内击败指定ID的怪物后NPC出现
+4.当自身某个ID的任务完成后出现
+5.穿戴要求指定数量的装备出现(玩家进地图时)
+6.背包内有某个道具出现(玩家进地图时)</t>
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -685,111 +489,28 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">0. 不需要填写
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1. 以秒为单位,最大86400。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">出现秒，消失秒。（例如10000,20000）
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2. 指定击败怪物数量
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">3. 指定击败怪物的ID
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">4. 指定任务ID
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">5. 要求装备数量;装备ID_1,装备ID_2,装备ID_3……
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">6. 背包内有某个道具出现
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>指定道具ID,指定数量</t>
+0. 不需要填写
+1. 以秒为单位,最大86400。
+出现秒，消失秒。（例如10000,20000）
+2. 指定击败怪物数量
+3. 指定击败怪物的ID
+4. 指定任务ID
+5. 要求装备数量;装备ID_1,装备ID_2,装备ID_3……
+6. 背包内有某个道具出现
+指定道具ID,指定数量</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="Y4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -798,60 +519,14 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">此字段目前没使用,留存的
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">0：普通商店
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">1：随机商店
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2：普通购买消失商店
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3：随机购买消失商店</t>
+此字段目前没使用,留存的
+0：普通商店
+1：随机商店
+2：普通购买消失商店
+3：随机购买消失商店</t>
         </r>
       </text>
     </comment>
@@ -860,7 +535,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="520">
   <si>
     <t>#</t>
   </si>
@@ -901,6 +576,9 @@
     <t>方向</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>移动坐标</t>
   </si>
   <si>
@@ -1321,9 +999,15 @@
     <t>3816,-428,-3622</t>
   </si>
   <si>
+    <t>20000024</t>
+  </si>
+  <si>
     <t>任务使者:赛利</t>
   </si>
   <si>
+    <t>50000101,50000102,50000103,50000104,50000105,50000201,50000202,50000203,50000301,50000302,50000303,60001001,50000003,30050024,30050025,30090001,30090002,30090003,30090004,30090005,30090006,30090007,30090008,30090009,30090010</t>
+  </si>
+  <si>
     <t>NPC_ShangJin</t>
   </si>
   <si>
@@ -1435,6 +1119,9 @@
     <t>5195,-404,-97</t>
   </si>
   <si>
+    <t>每到节日的时候,超过20级的玩家都可以来我这里领取奖励哦~</t>
+  </si>
+  <si>
     <t>20000034</t>
   </si>
   <si>
@@ -1516,21 +1203,69 @@
     <t>当你拥有全部神兽时,你可以用多余的神兽碎片来我这里换取璀璨传承哦。</t>
   </si>
   <si>
+    <t>20000041</t>
+  </si>
+  <si>
+    <t>封印之塔</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanPet2</t>
+  </si>
+  <si>
+    <t>-2954,-403,-1198</t>
+  </si>
+  <si>
+    <t>在我这里有100层,听说能闯到最后的都是勇士哦！</t>
+  </si>
+  <si>
+    <t>20000042</t>
+  </si>
+  <si>
+    <t>神兽商人</t>
+  </si>
+  <si>
+    <t>1459,-421,840</t>
+  </si>
+  <si>
+    <t>20000043</t>
+  </si>
+  <si>
+    <t>宠物装备商人</t>
+  </si>
+  <si>
+    <t>1759,-421,880</t>
+  </si>
+  <si>
     <t>20000101</t>
   </si>
   <si>
+    <t>家族管理</t>
+  </si>
+  <si>
+    <t>-8304,5,203</t>
+  </si>
+  <si>
     <t>20000102</t>
   </si>
   <si>
     <t>家族任务</t>
   </si>
   <si>
+    <t>-4274,5,2498</t>
+  </si>
+  <si>
+    <t>我这里的家族试炼任务每完成20、40、60、80、100环都会获得一份特殊奖励哦!</t>
+  </si>
+  <si>
     <t>20000103</t>
   </si>
   <si>
     <t>家族捐献</t>
   </si>
   <si>
+    <t>-5882,5,76</t>
+  </si>
+  <si>
     <t>20000104</t>
   </si>
   <si>
@@ -1540,6 +1275,27 @@
     <t>NPC_CunZhang</t>
   </si>
   <si>
+    <t>-6660,5,2006</t>
+  </si>
+  <si>
+    <t>20000105</t>
+  </si>
+  <si>
+    <t>家族商店</t>
+  </si>
+  <si>
+    <t>-8439,5,-1948</t>
+  </si>
+  <si>
+    <t>20000106</t>
+  </si>
+  <si>
+    <t>家族科技</t>
+  </si>
+  <si>
+    <t>-7715,5,2106</t>
+  </si>
+  <si>
     <t>20001001</t>
   </si>
   <si>
@@ -1558,6 +1314,9 @@
     <t>村长·乌尔</t>
   </si>
   <si>
+    <t>30010001,30010002,30010003,30010006,30010008,30010020,30010044,31001008</t>
+  </si>
+  <si>
     <t>140,16,150</t>
   </si>
   <si>
@@ -1648,6 +1407,9 @@
     <t>艾丽公主</t>
   </si>
   <si>
+    <t>30010018,30010019,31001001</t>
+  </si>
+  <si>
     <t>14275,2896,-1827</t>
   </si>
   <si>
@@ -1699,6 +1461,9 @@
     <t>森林守卫</t>
   </si>
   <si>
+    <t>30010023,30010024,30010025,31001002</t>
+  </si>
+  <si>
     <t>14313,2905,-6593</t>
   </si>
   <si>
@@ -1714,6 +1479,9 @@
     <t>石墓守陵人</t>
   </si>
   <si>
+    <t>30010027,30010028,30010029,30010030,30010031,31001003,31001004</t>
+  </si>
+  <si>
     <t>14705,2904,-3602</t>
   </si>
   <si>
@@ -1732,6 +1500,12 @@
     <t>15180,2904,-4445</t>
   </si>
   <si>
+    <t>地下洞穴守洞人</t>
+  </si>
+  <si>
+    <t>30010032,30010033,30010034,30010035,30010036,30010037,30010038,30010039,30010040,30010041,30010042,30010043,31001005,31001006,31001007</t>
+  </si>
+  <si>
     <t>17004,2893,-6304</t>
   </si>
   <si>
@@ -1750,6 +1524,9 @@
     <t>14222,2896,-4417</t>
   </si>
   <si>
+    <t>20002002</t>
+  </si>
+  <si>
     <t>15449,2888,-5419</t>
   </si>
   <si>
@@ -2071,6 +1848,66 @@
     <t>别说话,这里需要安静！</t>
   </si>
   <si>
+    <t>小龟赛跑大使</t>
+  </si>
+  <si>
+    <t>-844,-771,-4836</t>
+  </si>
+  <si>
+    <t>小龟1号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_1</t>
+  </si>
+  <si>
+    <t>-529,-765,-5248</t>
+  </si>
+  <si>
+    <t>我年轻力胜,获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟2号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_2</t>
+  </si>
+  <si>
+    <t>-205,-765,-5248</t>
+  </si>
+  <si>
+    <t>我是来自沙漠的龟,这么热的天获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟3号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_3</t>
+  </si>
+  <si>
+    <t>92,-765,-5248</t>
+  </si>
+  <si>
+    <t>我拥有丰富的赛龟经验,获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟一号选手</t>
+  </si>
+  <si>
+    <t>20000,5000,5000</t>
+  </si>
+  <si>
+    <t>-2.46;3.55;97.41</t>
+  </si>
+  <si>
+    <t>小龟二号选手</t>
+  </si>
+  <si>
+    <t>小龟三号选手</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>30000001</t>
   </si>
   <si>
@@ -2116,6 +1953,9 @@
     <t>NPC_JiaYuanGongGao</t>
   </si>
   <si>
+    <t>1450,0,-3250</t>
+  </si>
+  <si>
     <t>30000005</t>
   </si>
   <si>
@@ -2194,334 +2034,80 @@
     <t>-1556,0,1277</t>
   </si>
   <si>
-    <t>20000024</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>地下洞穴守洞人</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>30000014</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_CangKu</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>藏宝图生活技能仓库</t>
   </si>
   <si>
     <t>2350,0,1620</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>藏宝图生活技能仓库</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>封印之塔</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_JiaYuanPet2</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000041</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>像试试自己差距嘛,那就来我这里吧。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>在我这里有100层,听说能闯到最后的都是勇士哦！</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2954,-403,-1198</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>30000015</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>装备增幅</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>1450,0,-3250</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_Task_1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_JiaYuanShiBing</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>3439,0,804</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>30000016</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>家园觉醒大师</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>14,0,2133</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_LaoTou</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>40000001</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>战场招募·猎魔</t>
+  </si>
+  <si>
+    <t>-7655,0,-1313</t>
   </si>
   <si>
     <t>40000002</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>战场招募·猎魔</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>战场招募·曙光</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-7655,0,-1313</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>9256,0,-1330</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000105</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>家族商店</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟1号</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟2号</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟3号</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-844,-771,-4836</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟一号选手</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟二号选手</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟三号选手</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2.46;3.55;97.41</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_1</t>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_2</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_3</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-529,-765,-5248</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>92,-765,-5248</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>我年轻力胜,获胜最终胜利的一定是我！</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是来自沙漠的龟,这么热的天获胜最终胜利的一定是我！</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>我拥有丰富的赛龟经验,获胜最终胜利的一定是我！</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-205,-765,-5248</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000,5000,5000</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龟赛跑大使</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>40000003</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>神秘之门</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>NPC_ShenMiZhiMen</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>50000101,50000102,50000103,50000104,50000105,50000201,50000202,50000203,50000301,50000302,50000303,60001001,50000003,30050024,30050025,30090001,30090002,30090003,30090004,30090005,30090006,30090007,30090008,30090009,30090010</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>每到节日的时候,超过20级的玩家都可以来我这里领取奖励哦~</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>30010018,30010019,31001001</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>30010023,30010024,30010025,31001002</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>30010027,30010028,30010029,30010030,30010031,31001003,31001004</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>30010032,30010033,30010034,30010035,30010036,30010037,30010038,30010039,30010040,30010041,30010042,30010043,31001005,31001006,31001007</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>30010001,30010002,30010003,30010006,30010008,30010020,30010044,31001008</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000106</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>家族科技</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>我这里的家族试炼任务每完成20、40、60、80、100环都会获得一份特殊奖励哦!</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>家族管理</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-4274,5,2498</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-8304,5,203</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-8439,5,-1948</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-6660,5,2006</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-5882,5,76</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>-7715,5,2106</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>40000004</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>返回</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_LaoTou_2</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC_LaoTou_2</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>0,0,-300</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20002002</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000042</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>神兽商人</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>1459,-421,840</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2533,14 +2119,12 @@
       <sz val="9"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2548,14 +2132,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2563,7 +2145,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2571,7 +2152,6 @@
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2579,49 +2159,176 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2642,12 +2349,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14972380748924222"/>
+        <fgColor theme="0" tint="-0.149723807489242"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2698,13 +2591,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2769,6 +2904,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2777,47 +2915,91 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 5" xfId="49"/>
+    <cellStyle name="常规 6" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3104,14 +3286,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y163"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
@@ -3139,13 +3321,13 @@
     <col min="26" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="4:4">
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="20.1" customHeight="1" spans="3:25">
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
@@ -3183,183 +3365,183 @@
         <v>12</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>482</v>
+        <v>13</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="3:25">
       <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>482</v>
+        <v>13</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R4" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X4" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="3:25">
       <c r="C5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="M5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="S5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="V5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="W5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="X5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="Y5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="3:18">
       <c r="C6" s="12">
         <v>10001</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="12"/>
       <c r="H6" s="4">
@@ -3377,14 +3559,14 @@
       <c r="N6" s="5">
         <v>0</v>
       </c>
-      <c r="R6" s="25"/>
-    </row>
-    <row r="7" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="26"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="3:18">
       <c r="C7" s="12">
         <v>10002</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="12"/>
       <c r="H7" s="4">
@@ -3402,14 +3584,14 @@
       <c r="N7" s="5">
         <v>0</v>
       </c>
-      <c r="R7" s="25"/>
-    </row>
-    <row r="8" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="26"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="3:18">
       <c r="C8" s="12">
         <v>10003</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="12"/>
       <c r="H8" s="4">
@@ -3427,14 +3609,14 @@
       <c r="N8" s="5">
         <v>0</v>
       </c>
-      <c r="R8" s="25"/>
-    </row>
-    <row r="9" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="26"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="3:19">
       <c r="C9" s="12">
         <v>10004</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="12"/>
       <c r="H9" s="4">
@@ -3452,19 +3634,19 @@
       <c r="N9" s="5">
         <v>0</v>
       </c>
-      <c r="R9" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="S9" s="26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="3:18">
       <c r="C10" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" s="12">
         <v>200001</v>
@@ -3479,22 +3661,22 @@
         <v>0</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="27" t="s">
         <v>55</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>56</v>
       </c>
       <c r="N10" s="5">
         <v>-90</v>
       </c>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="20.1" customHeight="1" spans="3:18">
       <c r="C11" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" s="12">
         <v>10001201</v>
@@ -3509,22 +3691,22 @@
         <v>0</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="27" t="s">
         <v>59</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>60</v>
       </c>
       <c r="N11" s="5">
         <v>-280</v>
       </c>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="20.1" customHeight="1" spans="3:18">
       <c r="C12" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="4">
@@ -3537,22 +3719,22 @@
         <v>0</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" s="27" t="s">
         <v>63</v>
+      </c>
+      <c r="M12" s="30" t="s">
+        <v>64</v>
       </c>
       <c r="N12" s="5">
         <v>-180</v>
       </c>
       <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="20.1" customHeight="1" spans="3:18">
       <c r="C13" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="4">
@@ -3565,23 +3747,23 @@
         <v>0</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" s="27" t="s">
         <v>67</v>
+      </c>
+      <c r="M13" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="N13" s="5">
         <v>-280</v>
       </c>
       <c r="R13" s="12"/>
     </row>
-    <row r="14" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
       <c r="C14" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17">
@@ -3597,8 +3779,8 @@
       <c r="L14" s="16">
         <v>20001007</v>
       </c>
-      <c r="M14" s="28" t="s">
-        <v>70</v>
+      <c r="M14" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="N14" s="15">
         <v>-180</v>
@@ -3607,7 +3789,7 @@
       <c r="P14" s="22"/>
       <c r="Q14" s="22"/>
       <c r="R14" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S14" s="22"/>
       <c r="T14" s="22"/>
@@ -3617,12 +3799,12 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
     </row>
-    <row r="15" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="20.1" customHeight="1" spans="3:18">
       <c r="C15" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" s="4">
         <v>1005</v>
@@ -3634,10 +3816,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M15" s="29" t="s">
         <v>75</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>76</v>
       </c>
       <c r="N15" s="4">
         <v>-180</v>
@@ -3645,17 +3827,17 @@
       <c r="O15" s="4"/>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
-      <c r="R15" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
       <c r="C16" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="17">
@@ -3671,8 +3853,8 @@
       <c r="L16" s="16">
         <v>20001024</v>
       </c>
-      <c r="M16" s="28" t="s">
-        <v>79</v>
+      <c r="M16" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="N16" s="15">
         <v>-90</v>
@@ -3681,7 +3863,7 @@
       <c r="P16" s="22"/>
       <c r="Q16" s="22"/>
       <c r="R16" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S16" s="22"/>
       <c r="T16" s="22"/>
@@ -3691,13 +3873,13 @@
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
     </row>
-    <row r="17" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
       <c r="C17" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="17">
@@ -3713,8 +3895,8 @@
       <c r="L17" s="16">
         <v>20001024</v>
       </c>
-      <c r="M17" s="28" t="s">
-        <v>82</v>
+      <c r="M17" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="N17" s="15">
         <v>90</v>
@@ -3723,7 +3905,7 @@
       <c r="P17" s="22"/>
       <c r="Q17" s="22"/>
       <c r="R17" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S17" s="22"/>
       <c r="T17" s="22"/>
@@ -3733,12 +3915,12 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
     </row>
-    <row r="18" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="20.1" customHeight="1" spans="3:18">
       <c r="C18" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="4">
@@ -3751,24 +3933,24 @@
         <v>0</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="M18" s="27" t="s">
         <v>86</v>
       </c>
+      <c r="M18" s="30" t="s">
+        <v>87</v>
+      </c>
       <c r="N18" s="5">
         <v>0</v>
       </c>
       <c r="R18" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="3:18">
       <c r="C19" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="4">
@@ -3781,24 +3963,24 @@
         <v>0</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="M19" s="27" t="s">
         <v>91</v>
+      </c>
+      <c r="M19" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="N19" s="5">
         <v>-270</v>
       </c>
       <c r="R19" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="3:18">
       <c r="C20" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="4">
@@ -3811,25 +3993,25 @@
         <v>0</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" s="27" t="s">
         <v>96</v>
+      </c>
+      <c r="M20" s="30" t="s">
+        <v>97</v>
       </c>
       <c r="N20" s="5">
         <v>45</v>
       </c>
       <c r="R20" s="12"/>
     </row>
-    <row r="21" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" ht="20.1" customHeight="1" spans="3:18">
       <c r="C21" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G21" s="4">
         <v>1007</v>
@@ -3841,27 +4023,27 @@
         <v>0</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="M21" s="30" t="s">
         <v>101</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>102</v>
       </c>
       <c r="N21" s="5">
         <v>90</v>
       </c>
-      <c r="R21" s="24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="3:18">
       <c r="C22" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G22" s="4">
         <v>1006</v>
@@ -3873,27 +4055,27 @@
         <v>0</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="M22" s="30" t="s">
         <v>107</v>
+      </c>
+      <c r="M22" s="33" t="s">
+        <v>108</v>
       </c>
       <c r="N22" s="5">
         <v>90</v>
       </c>
-      <c r="R22" s="24" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="3:18">
       <c r="C23" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G23" s="4">
         <v>1008</v>
@@ -3905,24 +4087,24 @@
         <v>0</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="M23" s="30" t="s">
         <v>113</v>
+      </c>
+      <c r="M23" s="33" t="s">
+        <v>114</v>
       </c>
       <c r="N23" s="5">
         <v>225</v>
       </c>
-      <c r="R23" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="3:18">
       <c r="C24" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G24" s="4">
         <v>1002</v>
@@ -3934,24 +4116,24 @@
         <v>0</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="M24" s="30" t="s">
         <v>118</v>
       </c>
+      <c r="M24" s="33" t="s">
+        <v>119</v>
+      </c>
       <c r="N24" s="5">
         <v>0</v>
       </c>
-      <c r="R24" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="3:18">
       <c r="C25" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G25" s="4">
         <v>5</v>
@@ -3963,22 +4145,22 @@
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="M25" s="30" t="s">
         <v>123</v>
+      </c>
+      <c r="M25" s="33" t="s">
+        <v>124</v>
       </c>
       <c r="N25" s="5">
         <v>-90</v>
       </c>
-      <c r="R25" s="24"/>
-    </row>
-    <row r="26" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R25" s="25"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="3:18">
       <c r="C26" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G26" s="4">
         <v>1014</v>
@@ -3990,24 +4172,24 @@
         <v>0</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M26" s="30" t="s">
         <v>127</v>
+      </c>
+      <c r="M26" s="33" t="s">
+        <v>128</v>
       </c>
       <c r="N26" s="5">
         <v>180</v>
       </c>
-      <c r="R26" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="3:18">
       <c r="C27" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F27" s="5">
         <v>4</v>
@@ -4022,24 +4204,24 @@
         <v>0</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="M27" s="30" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="M27" s="33" t="s">
+        <v>132</v>
       </c>
       <c r="N27" s="5">
         <v>180</v>
       </c>
-      <c r="R27" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" spans="3:18">
       <c r="C28" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G28" s="4">
         <v>1</v>
@@ -4054,22 +4236,22 @@
         <v>52</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="M28" s="30" t="s">
         <v>135</v>
+      </c>
+      <c r="M28" s="33" t="s">
+        <v>136</v>
       </c>
       <c r="N28" s="5">
         <v>90</v>
       </c>
-      <c r="R28" s="24"/>
-    </row>
-    <row r="29" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="25"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="3:18">
       <c r="C29" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G29" s="4">
         <v>1</v>
@@ -4084,22 +4266,22 @@
         <v>53</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="M29" s="30" t="s">
         <v>139</v>
+      </c>
+      <c r="M29" s="33" t="s">
+        <v>140</v>
       </c>
       <c r="N29" s="5">
         <v>90</v>
       </c>
-      <c r="R29" s="24"/>
-    </row>
-    <row r="30" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="25"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="3:18">
       <c r="C30" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
@@ -4114,22 +4296,22 @@
         <v>54</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="M30" s="30" t="s">
         <v>143</v>
+      </c>
+      <c r="M30" s="33" t="s">
+        <v>144</v>
       </c>
       <c r="N30" s="5">
         <v>90</v>
       </c>
-      <c r="R30" s="24"/>
-    </row>
-    <row r="31" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="25"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="3:18">
       <c r="C31" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F31" s="12">
         <v>100001</v>
@@ -4138,28 +4320,28 @@
         <v>1012</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="M31" s="30" t="s">
         <v>148</v>
+      </c>
+      <c r="M31" s="33" t="s">
+        <v>149</v>
       </c>
       <c r="N31" s="5">
         <v>-110</v>
       </c>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="20.1" customHeight="1" spans="3:18">
       <c r="C32" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F32" s="5">
         <v>5</v>
@@ -4174,53 +4356,53 @@
         <v>0</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="M32" s="30" t="s">
         <v>152</v>
+      </c>
+      <c r="M32" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="N32" s="5">
         <v>-30</v>
       </c>
-      <c r="R32" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R32" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" spans="3:18">
       <c r="C33" s="13" t="s">
-        <v>444</v>
+        <v>154</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G33" s="4">
         <v>3</v>
       </c>
-      <c r="H33" s="31" t="s">
-        <v>499</v>
+      <c r="H33" s="34" t="s">
+        <v>156</v>
       </c>
       <c r="I33" s="4">
         <v>0</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="M33" s="30" t="s">
-        <v>155</v>
+        <v>157</v>
+      </c>
+      <c r="M33" s="33" t="s">
+        <v>158</v>
       </c>
       <c r="N33" s="5">
         <v>180</v>
       </c>
-      <c r="R33" s="24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R33" s="25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" spans="3:18">
       <c r="C34" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F34" s="18">
         <v>0</v>
@@ -4229,24 +4411,24 @@
         <v>1024</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M34" s="30" t="s">
-        <v>159</v>
+        <v>67</v>
+      </c>
+      <c r="M34" s="33" t="s">
+        <v>162</v>
       </c>
       <c r="N34" s="5">
         <v>-30</v>
       </c>
-      <c r="R34" s="24" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R34" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" spans="3:18">
       <c r="C35" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F35" s="5">
         <v>6</v>
@@ -4261,24 +4443,24 @@
         <v>0</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="M35" s="30" t="s">
-        <v>163</v>
+        <v>123</v>
+      </c>
+      <c r="M35" s="33" t="s">
+        <v>166</v>
       </c>
       <c r="N35" s="5">
         <v>-144</v>
       </c>
-      <c r="R35" s="24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R35" s="25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" spans="3:18">
       <c r="C36" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G36" s="4">
         <v>2</v>
@@ -4286,25 +4468,25 @@
       <c r="J36" s="4">
         <v>2000001</v>
       </c>
-      <c r="L36" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="M36" s="30" t="s">
-        <v>167</v>
+      <c r="L36" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M36" s="33" t="s">
+        <v>170</v>
       </c>
       <c r="N36" s="5">
         <v>-180</v>
       </c>
-      <c r="R36" s="24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R36" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" spans="3:18">
       <c r="C37" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -4312,73 +4494,73 @@
       <c r="J37" s="6">
         <v>2000002</v>
       </c>
-      <c r="L37" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="M37" s="30" t="s">
-        <v>171</v>
+      <c r="L37" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="M37" s="33" t="s">
+        <v>174</v>
       </c>
       <c r="N37" s="5">
         <v>90</v>
       </c>
-      <c r="R37" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" ht="20.1" customHeight="1" spans="3:18">
       <c r="C38" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G38" s="4">
         <v>1027</v>
       </c>
-      <c r="L38" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="M38" s="30" t="s">
-        <v>175</v>
+      <c r="L38" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="M38" s="33" t="s">
+        <v>178</v>
       </c>
       <c r="N38" s="5">
         <v>90</v>
       </c>
-      <c r="P38" s="23"/>
-      <c r="R38" s="24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P38" s="24"/>
+      <c r="R38" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" ht="20.1" customHeight="1" spans="3:18">
       <c r="C39" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G39" s="4">
         <v>1028</v>
       </c>
-      <c r="L39" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="M39" s="30" t="s">
-        <v>179</v>
+      <c r="L39" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="M39" s="33" t="s">
+        <v>182</v>
       </c>
       <c r="N39" s="5">
         <v>129</v>
       </c>
-      <c r="P39" s="23"/>
-      <c r="R39" s="24" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="40" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P39" s="24"/>
+      <c r="R39" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" ht="20.1" customHeight="1" spans="3:18">
       <c r="C40" s="13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G40" s="4">
         <v>0</v>
@@ -4393,143 +4575,143 @@
         <v>0</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M40" s="30" t="s">
-        <v>182</v>
+        <v>127</v>
+      </c>
+      <c r="M40" s="33" t="s">
+        <v>185</v>
       </c>
       <c r="N40" s="5">
         <v>180</v>
       </c>
-      <c r="R40" s="24"/>
-    </row>
-    <row r="41" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R40" s="25"/>
+    </row>
+    <row r="41" ht="20.1" customHeight="1" spans="3:18">
       <c r="C41" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="4">
         <v>1030</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="M41" s="30" t="s">
-        <v>186</v>
+        <v>188</v>
+      </c>
+      <c r="M41" s="33" t="s">
+        <v>189</v>
       </c>
       <c r="N41" s="5">
         <v>0</v>
       </c>
       <c r="R41" s="12"/>
     </row>
-    <row r="42" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="20.1" customHeight="1" spans="3:18">
       <c r="C42" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="4">
         <v>6</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="M42" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="M42" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="N42" s="5">
         <v>270</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="43" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" ht="20.1" customHeight="1" spans="3:18">
       <c r="C43" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="4">
         <v>7</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="M43" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
+      </c>
+      <c r="M43" s="33" t="s">
+        <v>197</v>
       </c>
       <c r="N43" s="5">
         <v>-146</v>
       </c>
       <c r="R43" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" ht="20.1" customHeight="1" spans="3:18">
       <c r="C44" s="13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="4">
         <v>2</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="M44" s="30" t="s">
-        <v>198</v>
+        <v>192</v>
+      </c>
+      <c r="M44" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="N44" s="5">
         <v>-146</v>
       </c>
       <c r="R44" s="12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="45" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" ht="20.1" customHeight="1" spans="3:18">
       <c r="C45" s="13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F45" s="12">
         <v>50000001</v>
@@ -4544,22 +4726,22 @@
         <v>0</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M45" s="27" t="s">
-        <v>202</v>
+        <v>59</v>
+      </c>
+      <c r="M45" s="30" t="s">
+        <v>206</v>
       </c>
       <c r="N45" s="5">
         <v>106</v>
       </c>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="20.1" customHeight="1" spans="3:18">
       <c r="C46" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F46" s="12">
         <v>0</v>
@@ -4574,24 +4756,24 @@
         <v>0</v>
       </c>
       <c r="L46" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M46" s="27" t="s">
-        <v>205</v>
+        <v>127</v>
+      </c>
+      <c r="M46" s="30" t="s">
+        <v>209</v>
       </c>
       <c r="N46" s="5">
         <v>-90</v>
       </c>
       <c r="R46" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" ht="20.1" customHeight="1" spans="3:18">
       <c r="C47" s="13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F47" s="12">
         <v>0</v>
@@ -4606,24 +4788,24 @@
         <v>0</v>
       </c>
       <c r="L47" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M47" s="27" t="s">
-        <v>209</v>
+        <v>127</v>
+      </c>
+      <c r="M47" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="N47" s="5">
         <v>90</v>
       </c>
       <c r="R47" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" ht="20.1" customHeight="1" spans="3:18">
       <c r="C48" s="13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F48" s="12">
         <v>60000001</v>
@@ -4638,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M48" s="27" t="s">
-        <v>213</v>
+        <v>67</v>
+      </c>
+      <c r="M48" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="N48" s="5">
         <v>180</v>
       </c>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="20.1" customHeight="1" spans="3:18">
       <c r="C49" s="13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F49" s="12">
         <v>0</v>
@@ -4668,47 +4850,47 @@
         <v>0</v>
       </c>
       <c r="L49" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M49" s="27" t="s">
-        <v>216</v>
+        <v>67</v>
+      </c>
+      <c r="M49" s="30" t="s">
+        <v>220</v>
       </c>
       <c r="N49" s="5">
         <v>-90</v>
       </c>
       <c r="R49" s="12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="50" ht="20.1" customHeight="1" spans="3:18">
       <c r="C50" s="13" t="s">
-        <v>452</v>
+        <v>222</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>450</v>
+        <v>223</v>
       </c>
       <c r="G50" s="4">
         <v>1050</v>
       </c>
-      <c r="L50" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="M50" s="30" t="s">
-        <v>455</v>
+      <c r="L50" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="M50" s="33" t="s">
+        <v>225</v>
       </c>
       <c r="N50" s="5">
         <v>90</v>
       </c>
-      <c r="R50" s="24" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R50" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" ht="20.1" customHeight="1" spans="3:18">
       <c r="C51" s="13" t="s">
-        <v>522</v>
+        <v>227</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>523</v>
+        <v>228</v>
       </c>
       <c r="F51" s="12">
         <v>92000001</v>
@@ -4723,31 +4905,31 @@
         <v>0</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M51" s="27" t="s">
-        <v>524</v>
+        <v>67</v>
+      </c>
+      <c r="M51" s="30" t="s">
+        <v>229</v>
       </c>
       <c r="N51" s="5">
         <v>135</v>
       </c>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="13" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="12" t="s">
-        <v>509</v>
+        <v>231</v>
       </c>
       <c r="F52" s="12">
-        <v>0</v>
+        <v>6000101</v>
       </c>
       <c r="G52" s="4">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="H52" s="4">
         <v>0</v>
@@ -4758,13 +4940,13 @@
       <c r="J52" s="6"/>
       <c r="K52" s="3"/>
       <c r="L52" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M52" s="27" t="s">
-        <v>511</v>
+        <v>67</v>
+      </c>
+      <c r="M52" s="30" t="s">
+        <v>232</v>
       </c>
       <c r="N52" s="5">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="O52" s="5"/>
       <c r="R52" s="12"/>
@@ -4774,21 +4956,21 @@
       <c r="X52" s="5"/>
       <c r="Y52" s="5"/>
     </row>
-    <row r="53" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="13" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="12" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F53" s="12">
         <v>0</v>
       </c>
       <c r="G53" s="4">
-        <v>0</v>
+        <v>1046</v>
       </c>
       <c r="H53" s="4">
         <v>0</v>
@@ -4799,39 +4981,37 @@
       <c r="J53" s="6"/>
       <c r="K53" s="3"/>
       <c r="L53" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="M53" s="27" t="s">
-        <v>510</v>
+        <v>127</v>
+      </c>
+      <c r="M53" s="30" t="s">
+        <v>235</v>
       </c>
       <c r="N53" s="5">
-        <v>-140</v>
+        <v>90</v>
       </c>
       <c r="O53" s="5"/>
-      <c r="R53" s="12" t="s">
-        <v>508</v>
-      </c>
+      <c r="R53" s="12"/>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
       <c r="X53" s="5"/>
       <c r="Y53" s="5"/>
     </row>
-    <row r="54" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="13" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="12" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="F54" s="12">
         <v>0</v>
       </c>
       <c r="G54" s="4">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H54" s="4">
         <v>0</v>
@@ -4842,37 +5022,39 @@
       <c r="J54" s="6"/>
       <c r="K54" s="3"/>
       <c r="L54" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M54" s="27" t="s">
-        <v>514</v>
+        <v>127</v>
+      </c>
+      <c r="M54" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="N54" s="5">
-        <v>90</v>
+        <v>-140</v>
       </c>
       <c r="O54" s="5"/>
-      <c r="R54" s="12"/>
+      <c r="R54" s="12" t="s">
+        <v>239</v>
+      </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
       <c r="W54" s="5"/>
       <c r="X54" s="5"/>
       <c r="Y54" s="5"/>
     </row>
-    <row r="55" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="13" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="12" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="F55" s="12">
         <v>0</v>
       </c>
       <c r="G55" s="4">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H55" s="4">
         <v>0</v>
@@ -4883,13 +5065,13 @@
       <c r="J55" s="6"/>
       <c r="K55" s="3"/>
       <c r="L55" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="M55" s="27" t="s">
-        <v>513</v>
+        <v>67</v>
+      </c>
+      <c r="M55" s="30" t="s">
+        <v>242</v>
       </c>
       <c r="N55" s="5">
-        <v>-180</v>
+        <v>90</v>
       </c>
       <c r="O55" s="5"/>
       <c r="R55" s="12"/>
@@ -4899,21 +5081,21 @@
       <c r="X55" s="5"/>
       <c r="Y55" s="5"/>
     </row>
-    <row r="56" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="13" t="s">
-        <v>472</v>
+        <v>243</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="12" t="s">
-        <v>473</v>
+        <v>244</v>
       </c>
       <c r="F56" s="12">
         <v>0</v>
       </c>
       <c r="G56" s="4">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="H56" s="4">
         <v>0</v>
@@ -4924,13 +5106,13 @@
       <c r="J56" s="6"/>
       <c r="K56" s="3"/>
       <c r="L56" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="M56" s="27" t="s">
-        <v>512</v>
+        <v>245</v>
+      </c>
+      <c r="M56" s="30" t="s">
+        <v>246</v>
       </c>
       <c r="N56" s="5">
-        <v>30</v>
+        <v>-180</v>
       </c>
       <c r="O56" s="5"/>
       <c r="R56" s="12"/>
@@ -4940,21 +5122,21 @@
       <c r="X56" s="5"/>
       <c r="Y56" s="5"/>
     </row>
-    <row r="57" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="13" t="s">
-        <v>506</v>
+        <v>247</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="12" t="s">
-        <v>507</v>
+        <v>248</v>
       </c>
       <c r="F57" s="12">
         <v>0</v>
       </c>
       <c r="G57" s="4">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="H57" s="4">
         <v>0</v>
@@ -4965,13 +5147,13 @@
       <c r="J57" s="6"/>
       <c r="K57" s="3"/>
       <c r="L57" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="M57" s="27" t="s">
-        <v>515</v>
+        <v>152</v>
+      </c>
+      <c r="M57" s="30" t="s">
+        <v>249</v>
       </c>
       <c r="N57" s="5">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="O57" s="5"/>
       <c r="R57" s="12"/>
@@ -4981,1947 +5163,1960 @@
       <c r="X57" s="5"/>
       <c r="Y57" s="5"/>
     </row>
-    <row r="58" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
       <c r="C58" s="13" t="s">
-        <v>226</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="D58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4">
+        <v>1072</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M58" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="N58" s="5">
+        <v>130</v>
+      </c>
+      <c r="O58" s="5"/>
+      <c r="R58" s="12"/>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
+    </row>
+    <row r="59" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C59" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="12">
         <v>10001101</v>
-      </c>
-      <c r="G58" s="4">
-        <v>1009</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M58" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="N58" s="5">
-        <v>60</v>
-      </c>
-      <c r="R58" s="12"/>
-    </row>
-    <row r="59" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="13">
-        <v>20001002</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F59" s="12">
-        <v>10001201</v>
       </c>
       <c r="G59" s="4">
         <v>1009</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L59" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M59" s="5" t="s">
-        <v>230</v>
+        <v>55</v>
+      </c>
+      <c r="M59" s="30" t="s">
+        <v>255</v>
       </c>
       <c r="N59" s="5">
+        <v>60</v>
+      </c>
+      <c r="R59" s="12"/>
+    </row>
+    <row r="60" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C60" s="13">
+        <v>20001002</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F60" s="12">
+        <v>10001201</v>
+      </c>
+      <c r="G60" s="4">
+        <v>1009</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="N60" s="5">
         <v>-45</v>
       </c>
-      <c r="R59" s="12"/>
-    </row>
-    <row r="60" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="12">
+      <c r="R60" s="12"/>
+    </row>
+    <row r="61" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C61" s="12">
         <v>20001003</v>
       </c>
-      <c r="E60" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="F60" s="12"/>
-      <c r="H60" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="M60" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="N60" s="5">
-        <v>180</v>
-      </c>
-      <c r="R60" s="25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="13">
-        <v>20001004</v>
-      </c>
       <c r="E61" s="12" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="F61" s="12"/>
       <c r="H61" s="6" t="s">
-        <v>146</v>
+        <v>259</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L61" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="M61" s="27" t="s">
-        <v>236</v>
+        <v>245</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="N61" s="5">
-        <v>90</v>
-      </c>
-      <c r="R61" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="12">
-        <v>20001005</v>
+        <v>180</v>
+      </c>
+      <c r="R61" s="26" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="62" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C62" s="13">
+        <v>20001004</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="F62" s="12"/>
       <c r="H62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L62" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="M62" s="5" t="s">
-        <v>239</v>
+        <v>263</v>
+      </c>
+      <c r="M62" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="N62" s="5">
-        <v>-45</v>
-      </c>
-      <c r="R62" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="R62" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="63" ht="20.1" customHeight="1" spans="3:18">
       <c r="C63" s="12">
-        <v>20001006</v>
+        <v>20001005</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F63" s="12"/>
       <c r="H63" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="M63" s="27" t="s">
-        <v>241</v>
+        <v>263</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="N63" s="5">
-        <v>45</v>
-      </c>
-      <c r="R63" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-45</v>
+      </c>
+      <c r="R63" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="64" ht="20.1" customHeight="1" spans="3:18">
       <c r="C64" s="12">
-        <v>20001007</v>
+        <v>20001006</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F64" s="12"/>
       <c r="H64" s="6" t="s">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L64" s="12">
+        <v>147</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="M64" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="N64" s="5">
+        <v>45</v>
+      </c>
+      <c r="R64" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="65" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C65" s="12">
         <v>20001007</v>
       </c>
-      <c r="M64" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="N64" s="5">
-        <v>150</v>
-      </c>
-      <c r="R64" s="25" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="65" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="12">
-        <v>20001008</v>
-      </c>
       <c r="E65" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="F65" s="12"/>
       <c r="H65" s="6" t="s">
-        <v>146</v>
+        <v>272</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L65" s="12">
+        <v>20001007</v>
+      </c>
+      <c r="M65" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="N65" s="5">
+        <v>150</v>
+      </c>
+      <c r="R65" s="26" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C66" s="12">
         <v>20001008</v>
       </c>
-      <c r="M65" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="N65" s="5">
-        <v>-155</v>
-      </c>
-      <c r="R65" s="25" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="66" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="12">
-        <v>20001009</v>
-      </c>
       <c r="E66" s="12" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F66" s="12"/>
       <c r="H66" s="6" t="s">
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L66" s="12">
+        <v>20001008</v>
+      </c>
+      <c r="M66" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="N66" s="5">
+        <v>-155</v>
+      </c>
+      <c r="R66" s="26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C67" s="12">
         <v>20001009</v>
       </c>
-      <c r="M66" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="N66" s="5">
-        <v>35</v>
-      </c>
-      <c r="R66" s="25" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="67" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="12">
-        <v>20001010</v>
-      </c>
       <c r="E67" s="12" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="F67" s="12"/>
       <c r="H67" s="6" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L67" s="12">
+        <v>20001009</v>
+      </c>
+      <c r="M67" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="N67" s="5">
+        <v>35</v>
+      </c>
+      <c r="R67" s="26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="68" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C68" s="12">
         <v>20001010</v>
       </c>
-      <c r="M67" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="N67" s="5">
-        <v>180</v>
-      </c>
-      <c r="R67" s="25" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="68" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="12">
-        <v>20001011</v>
-      </c>
       <c r="E68" s="12" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="F68" s="12"/>
       <c r="H68" s="6" t="s">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L68" s="12">
+        <v>20001010</v>
+      </c>
+      <c r="M68" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="N68" s="5">
+        <v>180</v>
+      </c>
+      <c r="R68" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="69" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C69" s="12">
         <v>20001011</v>
       </c>
-      <c r="M68" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="N68" s="5">
-        <v>-180</v>
-      </c>
-      <c r="R68" s="25" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="69" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="12">
-        <v>20001012</v>
-      </c>
       <c r="E69" s="12" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="F69" s="12"/>
       <c r="H69" s="6" t="s">
-        <v>501</v>
+        <v>286</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L69" s="12">
+        <v>20001011</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N69" s="5">
+        <v>-180</v>
+      </c>
+      <c r="R69" s="26" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="70" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C70" s="12">
         <v>20001012</v>
       </c>
-      <c r="M69" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="N69" s="5">
-        <v>80</v>
-      </c>
-      <c r="R69" s="25" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="70" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="12">
-        <v>20001013</v>
-      </c>
       <c r="E70" s="12" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="F70" s="12"/>
       <c r="H70" s="6" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L70" s="12">
+        <v>20001012</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="N70" s="5">
+        <v>80</v>
+      </c>
+      <c r="R70" s="26" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="71" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C71" s="12">
         <v>20001013</v>
       </c>
-      <c r="M70" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="N70" s="5">
-        <v>180</v>
-      </c>
-      <c r="R70" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="71" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="12">
-        <v>20001014</v>
-      </c>
       <c r="E71" s="12" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F71" s="12"/>
       <c r="H71" s="6" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L71" s="12">
-        <v>20001014</v>
+        <v>20001013</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="N71" s="5">
         <v>180</v>
       </c>
-      <c r="R71" s="25" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="72" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R71" s="26" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="72" ht="20.1" customHeight="1" spans="3:18">
       <c r="C72" s="12">
-        <v>20001015</v>
+        <v>20001014</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="F72" s="12"/>
       <c r="H72" s="6" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L72" s="12">
+        <v>20001014</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="N72" s="5">
+        <v>180</v>
+      </c>
+      <c r="R72" s="26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="73" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C73" s="12">
         <v>20001015</v>
       </c>
-      <c r="M72" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="N72" s="5">
-        <v>128</v>
-      </c>
-      <c r="R72" s="25" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="73" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="12">
-        <v>20001016</v>
-      </c>
       <c r="E73" s="12" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="F73" s="12"/>
       <c r="H73" s="6" t="s">
-        <v>146</v>
+        <v>302</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L73" s="12">
+        <v>20001015</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="N73" s="5">
+        <v>128</v>
+      </c>
+      <c r="R73" s="26" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C74" s="12">
         <v>20001016</v>
       </c>
-      <c r="M73" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N73" s="5">
-        <v>180</v>
-      </c>
-      <c r="R73" s="25" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="74" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="12">
-        <v>20001017</v>
-      </c>
       <c r="E74" s="12" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F74" s="12"/>
       <c r="H74" s="6" t="s">
-        <v>502</v>
+        <v>147</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L74" s="12">
+        <v>20001016</v>
+      </c>
+      <c r="M74" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N74" s="5">
+        <v>180</v>
+      </c>
+      <c r="R74" s="26" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C75" s="12">
         <v>20001017</v>
       </c>
-      <c r="M74" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="N74" s="5">
-        <v>120</v>
-      </c>
-      <c r="R74" s="25" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="75" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="12">
-        <v>20001018</v>
-      </c>
       <c r="E75" s="12" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="F75" s="12"/>
       <c r="H75" s="6" t="s">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J75" s="4"/>
-      <c r="L75" s="24">
-        <v>0</v>
+        <v>147</v>
+      </c>
+      <c r="L75" s="12">
+        <v>20001017</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="N75" s="5">
-        <v>180</v>
-      </c>
-      <c r="R75" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="76" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="R75" s="26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" ht="20.1" customHeight="1" spans="3:18">
       <c r="C76" s="12">
-        <v>20001019</v>
+        <v>20001018</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="F76" s="12"/>
       <c r="H76" s="6" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L76" s="12">
+        <v>147</v>
+      </c>
+      <c r="J76" s="4"/>
+      <c r="L76" s="25">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N76" s="5">
+        <v>180</v>
+      </c>
+      <c r="R76" s="26" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="77" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C77" s="12">
         <v>20001019</v>
       </c>
-      <c r="M76" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="N76" s="5">
-        <v>-180</v>
-      </c>
-      <c r="R76" s="25" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="77" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="12">
-        <v>20001020</v>
-      </c>
       <c r="E77" s="12" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="F77" s="12"/>
       <c r="H77" s="6" t="s">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L77" s="12">
         <v>20001019</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="N77" s="5">
-        <v>180</v>
-      </c>
-      <c r="R77" s="25" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="78" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-180</v>
+      </c>
+      <c r="R77" s="26" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="78" ht="20.1" customHeight="1" spans="3:18">
       <c r="C78" s="12">
-        <v>20001021</v>
+        <v>20001020</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="F78" s="12"/>
       <c r="H78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L78" s="12">
+        <v>20001019</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N78" s="5">
+        <v>180</v>
+      </c>
+      <c r="R78" s="26" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C79" s="12">
         <v>20001021</v>
       </c>
-      <c r="M78" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="N78" s="5">
-        <v>-180</v>
-      </c>
-      <c r="R78" s="25" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="79" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="12">
-        <v>20001022</v>
-      </c>
       <c r="E79" s="12" t="s">
-        <v>445</v>
+        <v>319</v>
       </c>
       <c r="F79" s="12"/>
       <c r="H79" s="6" t="s">
-        <v>504</v>
+        <v>147</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L79" s="12">
+        <v>20001021</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="N79" s="5">
+        <v>-180</v>
+      </c>
+      <c r="R79" s="26" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="80" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C80" s="12">
         <v>20001022</v>
       </c>
-      <c r="M79" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="N79" s="5">
+      <c r="E80" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F80" s="12"/>
+      <c r="H80" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L80" s="12">
+        <v>20001022</v>
+      </c>
+      <c r="M80" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="N80" s="5">
         <v>-106</v>
       </c>
-      <c r="R79" s="25" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="80" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="12">
+      <c r="R80" s="26" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="81" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C81" s="12">
         <v>20001023</v>
       </c>
-      <c r="E80" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="4">
+      <c r="E81" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F81" s="12"/>
+      <c r="G81" s="4">
         <v>1004</v>
       </c>
-      <c r="H80" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L80" s="12">
+      <c r="H81" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L81" s="12">
         <v>20001023</v>
       </c>
-      <c r="M80" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N80" s="5">
+      <c r="M81" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N81" s="5">
         <v>180</v>
       </c>
-      <c r="R80" s="12"/>
-    </row>
-    <row r="81" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="12">
+      <c r="R81" s="12"/>
+    </row>
+    <row r="82" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C82" s="12">
         <v>20001024</v>
       </c>
-      <c r="E81" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F81" s="12"/>
-      <c r="H81" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L81" s="12">
+      <c r="E82" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F82" s="12"/>
+      <c r="H82" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L82" s="12">
         <v>20001024</v>
       </c>
-      <c r="M81" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="N81" s="5">
+      <c r="M82" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="N82" s="5">
         <v>-152</v>
       </c>
-      <c r="R81" s="12"/>
-    </row>
-    <row r="82" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F82" s="12">
+      <c r="R82" s="12"/>
+    </row>
+    <row r="83" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C83" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F83" s="12">
         <v>10002101</v>
-      </c>
-      <c r="G82" s="4">
-        <v>1009</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L82" s="12">
-        <v>20001001</v>
-      </c>
-      <c r="M82" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="N82" s="5">
-        <v>-147</v>
-      </c>
-      <c r="R82" s="12"/>
-    </row>
-    <row r="83" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C83" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F83" s="12">
-        <v>10002201</v>
       </c>
       <c r="G83" s="4">
         <v>1009</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L83" s="12">
+        <v>20001001</v>
+      </c>
+      <c r="M83" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="N83" s="5">
+        <v>-147</v>
+      </c>
+      <c r="R83" s="12"/>
+    </row>
+    <row r="84" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C84" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F84" s="12">
+        <v>10002201</v>
+      </c>
+      <c r="G84" s="4">
+        <v>1009</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L84" s="12">
         <v>20001002</v>
       </c>
-      <c r="M83" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="N83" s="5">
+      <c r="M84" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="N84" s="5">
         <v>-129</v>
       </c>
-      <c r="R83" s="12"/>
-    </row>
-    <row r="84" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C84" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="F84" s="12"/>
-      <c r="H84" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L84" s="24">
-        <v>20001007</v>
-      </c>
-      <c r="M84" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="N84" s="5">
-        <v>-131</v>
-      </c>
-      <c r="R84" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="85" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R84" s="12"/>
+    </row>
+    <row r="85" ht="20.1" customHeight="1" spans="3:18">
       <c r="C85" s="13" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="F85" s="12"/>
       <c r="H85" s="6" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L85" s="12">
-        <v>20001005</v>
+        <v>147</v>
+      </c>
+      <c r="L85" s="25">
+        <v>20001007</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="N85" s="5">
-        <v>180</v>
-      </c>
-      <c r="R85" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="86" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-131</v>
+      </c>
+      <c r="R85" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="86" ht="20.1" customHeight="1" spans="3:18">
       <c r="C86" s="13" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="F86" s="12"/>
       <c r="H86" s="6" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L86" s="24">
-        <v>20001009</v>
+        <v>147</v>
+      </c>
+      <c r="L86" s="12">
+        <v>20001005</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="N86" s="5">
         <v>180</v>
       </c>
-      <c r="R86" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="87" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R86" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="87" ht="20.1" customHeight="1" spans="3:18">
       <c r="C87" s="13" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="F87" s="12"/>
       <c r="H87" s="6" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L87" s="12">
-        <v>20001005</v>
+        <v>147</v>
+      </c>
+      <c r="L87" s="25">
+        <v>20001009</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="N87" s="5">
         <v>180</v>
       </c>
-      <c r="R87" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="88" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R87" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="88" ht="20.1" customHeight="1" spans="3:18">
       <c r="C88" s="13" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>238</v>
+        <v>344</v>
       </c>
       <c r="F88" s="12"/>
       <c r="H88" s="6" t="s">
-        <v>146</v>
+        <v>345</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L88" s="12" t="s">
-        <v>235</v>
+        <v>147</v>
+      </c>
+      <c r="L88" s="12">
+        <v>20001005</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>255</v>
+        <v>346</v>
       </c>
       <c r="N88" s="5">
         <v>180</v>
       </c>
-      <c r="R88" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="89" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R88" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="89" ht="20.1" customHeight="1" spans="3:18">
       <c r="C89" s="13" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F89" s="12"/>
       <c r="H89" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L89" s="12" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N89" s="5">
         <v>180</v>
       </c>
-      <c r="R89" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R89" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" ht="20.1" customHeight="1" spans="3:18">
       <c r="C90" s="13" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c r="F90" s="12"/>
       <c r="H90" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L90" s="24">
+        <v>147</v>
+      </c>
+      <c r="L90" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="M90" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N90" s="5">
+        <v>180</v>
+      </c>
+      <c r="R90" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C91" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="H91" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L91" s="25">
         <v>20001017</v>
       </c>
-      <c r="M90" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="N90" s="5">
+      <c r="M91" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="N91" s="5">
         <v>27</v>
       </c>
-      <c r="R90" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="91" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C91" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F91" s="12">
+      <c r="R91" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="92" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C92" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F92" s="12">
         <v>10003101</v>
-      </c>
-      <c r="G91" s="4">
-        <v>1009</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L91" s="12">
-        <v>20001001</v>
-      </c>
-      <c r="M91" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="N91" s="5">
-        <v>123</v>
-      </c>
-      <c r="R91" s="12"/>
-    </row>
-    <row r="92" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C92" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F92" s="12">
-        <v>10003201</v>
       </c>
       <c r="G92" s="4">
         <v>1009</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L92" s="12">
+        <v>20001001</v>
+      </c>
+      <c r="M92" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="N92" s="5">
+        <v>123</v>
+      </c>
+      <c r="R92" s="12"/>
+    </row>
+    <row r="93" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C93" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F93" s="12">
+        <v>10003201</v>
+      </c>
+      <c r="G93" s="4">
+        <v>1009</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L93" s="12">
         <v>20001002</v>
       </c>
-      <c r="M92" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="N92" s="5">
+      <c r="M93" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="N93" s="5">
         <v>45</v>
       </c>
-      <c r="R92" s="12"/>
-    </row>
-    <row r="93" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="H93" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L93" s="24">
-        <v>20001007</v>
-      </c>
-      <c r="M93" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="N93" s="5">
-        <v>90</v>
-      </c>
-      <c r="R93" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="94" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R93" s="12"/>
+    </row>
+    <row r="94" ht="20.1" customHeight="1" spans="3:18">
       <c r="C94" s="13" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="F94" s="12"/>
       <c r="H94" s="6" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L94" s="24">
-        <v>20001011</v>
+        <v>147</v>
+      </c>
+      <c r="L94" s="25">
+        <v>20001007</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="N94" s="5">
-        <v>180</v>
-      </c>
-      <c r="R94" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="R94" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="95" ht="20.1" customHeight="1" spans="3:18">
       <c r="C95" s="13" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="F95" s="12"/>
       <c r="H95" s="6" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L95" s="24">
-        <v>20001017</v>
+        <v>147</v>
+      </c>
+      <c r="L95" s="25">
+        <v>20001011</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="N95" s="5">
-        <v>95</v>
-      </c>
-      <c r="R95" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="96" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R95" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="96" ht="20.1" customHeight="1" spans="3:18">
       <c r="C96" s="13" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F96" s="12"/>
       <c r="H96" s="6" t="s">
-        <v>146</v>
+        <v>365</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L96" s="12">
-        <v>20001005</v>
+        <v>147</v>
+      </c>
+      <c r="L96" s="25">
+        <v>20001017</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="N96" s="5">
-        <v>-70</v>
-      </c>
-      <c r="R96" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="97" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="R96" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" ht="20.1" customHeight="1" spans="3:18">
       <c r="C97" s="13" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>238</v>
+        <v>344</v>
       </c>
       <c r="F97" s="12"/>
       <c r="H97" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L97" s="12" t="s">
-        <v>235</v>
+        <v>147</v>
+      </c>
+      <c r="L97" s="12">
+        <v>20001005</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>255</v>
+        <v>368</v>
       </c>
       <c r="N97" s="5">
-        <v>180</v>
-      </c>
-      <c r="R97" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="98" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-70</v>
+      </c>
+      <c r="R97" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" ht="20.1" customHeight="1" spans="3:18">
       <c r="C98" s="13" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F98" s="12"/>
       <c r="H98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L98" s="12" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N98" s="5">
         <v>180</v>
       </c>
-      <c r="R98" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="99" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R98" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" ht="20.1" customHeight="1" spans="3:18">
       <c r="C99" s="13" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="F99" s="12"/>
       <c r="H99" s="6" t="s">
-        <v>339</v>
+        <v>147</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L99" s="12">
-        <v>20001008</v>
+        <v>147</v>
+      </c>
+      <c r="L99" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>340</v>
+        <v>283</v>
       </c>
       <c r="N99" s="5">
-        <v>-70</v>
-      </c>
-      <c r="R99" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="100" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R99" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="100" ht="20.1" customHeight="1" spans="3:18">
       <c r="C100" s="13" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="F100" s="12"/>
       <c r="H100" s="6" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L100" s="24">
+        <v>147</v>
+      </c>
+      <c r="L100" s="12">
+        <v>20001008</v>
+      </c>
+      <c r="M100" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="N100" s="5">
+        <v>-70</v>
+      </c>
+      <c r="R100" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C101" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="F101" s="12"/>
+      <c r="H101" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L101" s="25">
         <v>20001011</v>
       </c>
-      <c r="M100" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="N100" s="5">
+      <c r="M101" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="N101" s="5">
         <v>-180</v>
       </c>
-      <c r="R100" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C101" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="E101" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F101" s="12">
+      <c r="R101" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C102" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F102" s="12">
         <v>10004101</v>
-      </c>
-      <c r="G101" s="4">
-        <v>1009</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L101" s="12">
-        <v>20001001</v>
-      </c>
-      <c r="M101" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="N101" s="5">
-        <v>35</v>
-      </c>
-      <c r="R101" s="12"/>
-    </row>
-    <row r="102" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="E102" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F102" s="12">
-        <v>10004201</v>
       </c>
       <c r="G102" s="4">
         <v>1009</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L102" s="12">
+        <v>20001001</v>
+      </c>
+      <c r="M102" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="N102" s="5">
+        <v>35</v>
+      </c>
+      <c r="R102" s="12"/>
+    </row>
+    <row r="103" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C103" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F103" s="12">
+        <v>10004201</v>
+      </c>
+      <c r="G103" s="4">
+        <v>1009</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L103" s="12">
         <v>20001002</v>
       </c>
-      <c r="M102" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="N102" s="5">
+      <c r="M103" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="N103" s="5">
         <v>-41</v>
       </c>
-      <c r="R102" s="12"/>
-    </row>
-    <row r="103" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F103" s="12"/>
-      <c r="H103" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L103" s="24">
-        <v>20001007</v>
-      </c>
-      <c r="M103" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="N103" s="5">
-        <v>0</v>
-      </c>
-      <c r="R103" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="104" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R103" s="12"/>
+    </row>
+    <row r="104" ht="20.1" customHeight="1" spans="3:18">
       <c r="C104" s="13" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="F104" s="12"/>
       <c r="H104" s="6" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L104" s="24">
-        <v>20001017</v>
+        <v>147</v>
+      </c>
+      <c r="L104" s="25">
+        <v>20001007</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="N104" s="5">
-        <v>101</v>
-      </c>
-      <c r="R104" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="105" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="R104" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" ht="20.1" customHeight="1" spans="3:18">
       <c r="C105" s="13" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="F105" s="12"/>
       <c r="H105" s="6" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L105" s="24">
-        <v>20001013</v>
+        <v>147</v>
+      </c>
+      <c r="L105" s="25">
+        <v>20001017</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="N105" s="5">
-        <v>-3</v>
-      </c>
-      <c r="R105" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="106" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="R105" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="106" ht="20.1" customHeight="1" spans="3:18">
       <c r="C106" s="13" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>238</v>
+        <v>392</v>
       </c>
       <c r="F106" s="12"/>
       <c r="H106" s="6" t="s">
-        <v>146</v>
+        <v>393</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L106" s="12" t="s">
-        <v>235</v>
+        <v>147</v>
+      </c>
+      <c r="L106" s="25">
+        <v>20001013</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="N106" s="5">
-        <v>180</v>
-      </c>
-      <c r="R106" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="107" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-3</v>
+      </c>
+      <c r="R106" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" ht="20.1" customHeight="1" spans="3:18">
       <c r="C107" s="13" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F107" s="12"/>
       <c r="H107" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L107" s="12" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N107" s="5">
         <v>180</v>
       </c>
-      <c r="R107" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R107" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="108" ht="20.1" customHeight="1" spans="3:18">
       <c r="C108" s="13" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>364</v>
+        <v>266</v>
       </c>
       <c r="F108" s="12"/>
       <c r="H108" s="6" t="s">
-        <v>365</v>
+        <v>147</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L108" s="24">
-        <v>20001015</v>
+        <v>147</v>
+      </c>
+      <c r="L108" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c r="N108" s="5">
-        <v>-180</v>
-      </c>
-      <c r="R108" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="109" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R108" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="109" ht="20.1" customHeight="1" spans="3:18">
       <c r="C109" s="13" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="F109" s="12"/>
       <c r="H109" s="6" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L109" s="24">
+        <v>147</v>
+      </c>
+      <c r="L109" s="25">
         <v>20001015</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="N109" s="5">
+        <v>-180</v>
+      </c>
+      <c r="R109" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="110" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C110" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="F110" s="12"/>
+      <c r="H110" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L110" s="25">
+        <v>20001015</v>
+      </c>
+      <c r="M110" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="N110" s="5">
         <v>83</v>
       </c>
-      <c r="R109" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="110" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="E110" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F110" s="12">
+      <c r="R110" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="111" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C111" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F111" s="12">
         <v>10005101</v>
-      </c>
-      <c r="G110" s="4">
-        <v>1009</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L110" s="12">
-        <v>20001001</v>
-      </c>
-      <c r="M110" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="N110" s="5">
-        <v>51</v>
-      </c>
-      <c r="R110" s="12"/>
-    </row>
-    <row r="111" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F111" s="12">
-        <v>10005201</v>
       </c>
       <c r="G111" s="4">
         <v>1009</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L111" s="12">
+        <v>20001001</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="N111" s="5">
+        <v>51</v>
+      </c>
+      <c r="R111" s="12"/>
+    </row>
+    <row r="112" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C112" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F112" s="12">
+        <v>10005201</v>
+      </c>
+      <c r="G112" s="4">
+        <v>1009</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L112" s="12">
         <v>20001002</v>
       </c>
-      <c r="M111" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="N111" s="5">
+      <c r="M112" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="N112" s="5">
         <v>-44</v>
       </c>
-      <c r="R111" s="12"/>
-    </row>
-    <row r="112" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="F112" s="12"/>
-      <c r="H112" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L112" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="M112" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="N112" s="5">
-        <v>180</v>
-      </c>
-      <c r="R112" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="113" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R112" s="12"/>
+    </row>
+    <row r="113" ht="20.1" customHeight="1" spans="3:18">
       <c r="C113" s="13" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F113" s="12"/>
       <c r="H113" s="6" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L113" s="24">
-        <v>20001012</v>
+        <v>147</v>
+      </c>
+      <c r="L113" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="N113" s="5">
-        <v>92</v>
-      </c>
-      <c r="R113" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="114" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R113" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" ht="20.1" customHeight="1" spans="3:18">
       <c r="C114" s="13" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="F114" s="12"/>
       <c r="H114" s="6" t="s">
-        <v>146</v>
+        <v>415</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L114" s="24">
-        <v>20001015</v>
+        <v>147</v>
+      </c>
+      <c r="L114" s="25">
+        <v>20001012</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>255</v>
+        <v>416</v>
       </c>
       <c r="N114" s="5">
-        <v>180</v>
-      </c>
-      <c r="R114" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="115" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="R114" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="115" ht="20.1" customHeight="1" spans="3:18">
       <c r="C115" s="13" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="F115" s="12"/>
       <c r="H115" s="6" t="s">
-        <v>387</v>
+        <v>147</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L115" s="24">
-        <v>20001013</v>
+        <v>147</v>
+      </c>
+      <c r="L115" s="25">
+        <v>20001015</v>
       </c>
       <c r="M115" s="5" t="s">
-        <v>388</v>
+        <v>283</v>
       </c>
       <c r="N115" s="5">
-        <v>145</v>
-      </c>
-      <c r="R115" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="116" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="R115" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="116" ht="20.1" customHeight="1" spans="3:18">
       <c r="C116" s="13" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>238</v>
+        <v>420</v>
       </c>
       <c r="F116" s="12"/>
       <c r="H116" s="6" t="s">
-        <v>146</v>
+        <v>421</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L116" s="12" t="s">
-        <v>235</v>
+        <v>147</v>
+      </c>
+      <c r="L116" s="25">
+        <v>20001013</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="N116" s="5">
-        <v>180</v>
-      </c>
-      <c r="R116" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="117" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+      <c r="R116" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="117" ht="20.1" customHeight="1" spans="3:18">
       <c r="C117" s="13" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F117" s="12"/>
       <c r="H117" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L117" s="12" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="M117" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N117" s="5">
         <v>180</v>
       </c>
-      <c r="R117" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="118" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C118" s="12">
-        <v>20099001</v>
+      <c r="R117" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="118" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C118" s="13" t="s">
+        <v>424</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>391</v>
+        <v>266</v>
       </c>
       <c r="F118" s="12"/>
       <c r="H118" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L118" s="24" t="s">
-        <v>459</v>
+        <v>147</v>
+      </c>
+      <c r="L118" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N118" s="5">
         <v>180</v>
       </c>
-      <c r="R118" s="25" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="119" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R118" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" ht="20.1" customHeight="1" spans="3:18">
       <c r="C119" s="12">
-        <v>20099002</v>
+        <v>20099001</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="F119" s="12"/>
       <c r="H119" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L119" s="24" t="s">
-        <v>392</v>
+        <v>147</v>
+      </c>
+      <c r="L119" s="25" t="s">
+        <v>426</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N119" s="5">
         <v>180</v>
       </c>
-      <c r="R119" s="25" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="120" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R119" s="26" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="120" ht="20.1" customHeight="1" spans="3:18">
       <c r="C120" s="12">
-        <v>20099003</v>
+        <v>20099002</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="F120" s="12"/>
       <c r="H120" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L120" s="24" t="s">
-        <v>392</v>
+        <v>147</v>
+      </c>
+      <c r="L120" s="25" t="s">
+        <v>426</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N120" s="5">
         <v>180</v>
       </c>
-      <c r="R120" s="25" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="121" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R120" s="26" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="121" ht="20.1" customHeight="1" spans="3:18">
       <c r="C121" s="12">
-        <v>20099004</v>
+        <v>20099003</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="F121" s="12"/>
       <c r="H121" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L121" s="24" t="s">
-        <v>392</v>
+        <v>147</v>
+      </c>
+      <c r="L121" s="25" t="s">
+        <v>426</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N121" s="5">
         <v>180</v>
       </c>
-      <c r="R121" s="25" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="122" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R121" s="26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="122" ht="20.1" customHeight="1" spans="3:18">
       <c r="C122" s="12">
-        <v>20099005</v>
+        <v>20099004</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="F122" s="12"/>
       <c r="H122" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L122" s="24" t="s">
-        <v>392</v>
+        <v>147</v>
+      </c>
+      <c r="L122" s="25" t="s">
+        <v>426</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N122" s="5">
         <v>180</v>
       </c>
-      <c r="R122" s="25" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="123" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R122" s="26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="123" ht="20.1" customHeight="1" spans="3:18">
       <c r="C123" s="12">
-        <v>20099006</v>
+        <v>20099005</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>238</v>
+        <v>434</v>
       </c>
       <c r="F123" s="12"/>
       <c r="H123" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="L123" s="12">
-        <v>20001005</v>
+        <v>147</v>
+      </c>
+      <c r="L123" s="25" t="s">
+        <v>426</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="N123" s="5">
         <v>180</v>
       </c>
-      <c r="R123" s="25" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="124" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R123" s="26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="124" ht="20.1" customHeight="1" spans="3:18">
       <c r="C124" s="12">
-        <v>20099007</v>
-      </c>
-      <c r="E124" s="32" t="s">
-        <v>495</v>
-      </c>
-      <c r="F124" s="32"/>
-      <c r="G124" s="4">
-        <v>1057</v>
-      </c>
-      <c r="L124" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M124" s="27" t="s">
-        <v>477</v>
+        <v>20099006</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F124" s="12"/>
+      <c r="H124" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I124" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L124" s="12">
+        <v>20001005</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="N124" s="5">
         <v>180</v>
       </c>
-      <c r="R124" s="33"/>
-    </row>
-    <row r="125" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R124" s="26" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="125" ht="20.1" customHeight="1" spans="3:18">
       <c r="C125" s="12">
+        <v>20099007</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>437</v>
+      </c>
+      <c r="F125" s="27"/>
+      <c r="G125" s="4">
+        <v>1057</v>
+      </c>
+      <c r="L125" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M125" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="N125" s="5">
+        <v>180</v>
+      </c>
+      <c r="R125" s="28"/>
+    </row>
+    <row r="126" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C126" s="12">
         <v>20099008</v>
       </c>
-      <c r="E125" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="F125" s="32"/>
-      <c r="L125" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="M125" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="N125" s="5">
-        <v>0</v>
-      </c>
-      <c r="R125" s="33" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="126" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C126" s="12">
+      <c r="E126" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="F126" s="27"/>
+      <c r="L126" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="M126" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="N126" s="5">
+        <v>0</v>
+      </c>
+      <c r="R126" s="28" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="127" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C127" s="12">
         <v>20099009</v>
       </c>
-      <c r="E126" s="32" t="s">
-        <v>475</v>
-      </c>
-      <c r="F126" s="32"/>
-      <c r="L126" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="M126" s="27" t="s">
-        <v>493</v>
-      </c>
-      <c r="N126" s="5">
-        <v>0</v>
-      </c>
-      <c r="R126" s="33" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="127" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C127" s="12">
+      <c r="E127" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F127" s="27"/>
+      <c r="L127" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="M127" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="N127" s="5">
+        <v>0</v>
+      </c>
+      <c r="R127" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="128" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C128" s="12">
         <v>20099010</v>
       </c>
-      <c r="E127" s="32" t="s">
-        <v>476</v>
-      </c>
-      <c r="F127" s="32"/>
-      <c r="L127" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="M127" s="27" t="s">
-        <v>489</v>
-      </c>
-      <c r="N127" s="5">
-        <v>0</v>
-      </c>
-      <c r="R127" s="33" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="128" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C128" s="12">
+      <c r="E128" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="F128" s="27"/>
+      <c r="L128" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="M128" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="N128" s="5">
+        <v>0</v>
+      </c>
+      <c r="R128" s="28" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="129" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C129" s="12">
         <v>20099011</v>
       </c>
-      <c r="E128" s="32" t="s">
-        <v>479</v>
-      </c>
-      <c r="F128" s="32"/>
-      <c r="J128" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="L128" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="M128" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="N128" s="5">
-        <v>0</v>
-      </c>
-      <c r="O128" s="5">
-        <v>13</v>
-      </c>
-      <c r="P128" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="R128" s="33"/>
-    </row>
-    <row r="129" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="12">
-        <v>20099012</v>
-      </c>
-      <c r="E129" s="32" t="s">
-        <v>480</v>
-      </c>
-      <c r="F129" s="32"/>
+      <c r="E129" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F129" s="27"/>
       <c r="J129" s="6" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
       <c r="L129" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="M129" s="27" t="s">
-        <v>493</v>
+        <v>440</v>
+      </c>
+      <c r="M129" s="30" t="s">
+        <v>441</v>
       </c>
       <c r="N129" s="5">
         <v>0</v>
@@ -6929,27 +7124,27 @@
       <c r="O129" s="5">
         <v>13</v>
       </c>
-      <c r="P129" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="R129" s="33"/>
-    </row>
-    <row r="130" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P129" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="R129" s="28"/>
+    </row>
+    <row r="130" ht="20.1" customHeight="1" spans="3:18">
       <c r="C130" s="12">
-        <v>20099013</v>
-      </c>
-      <c r="E130" s="32" t="s">
-        <v>481</v>
-      </c>
-      <c r="F130" s="32"/>
+        <v>20099012</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="F130" s="27"/>
       <c r="J130" s="6" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
       <c r="L130" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="M130" s="27" t="s">
-        <v>489</v>
+        <v>444</v>
+      </c>
+      <c r="M130" s="30" t="s">
+        <v>445</v>
       </c>
       <c r="N130" s="5">
         <v>0</v>
@@ -6957,68 +7152,56 @@
       <c r="O130" s="5">
         <v>13</v>
       </c>
-      <c r="P130" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="R130" s="33"/>
-    </row>
-    <row r="131" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B131" s="3"/>
-      <c r="C131" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="D131" s="5"/>
-      <c r="E131" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="F131" s="5">
-        <v>300001</v>
-      </c>
-      <c r="G131" s="4">
-        <v>1034</v>
-      </c>
-      <c r="H131" s="4">
-        <v>0</v>
-      </c>
-      <c r="I131" s="4">
-        <v>0</v>
-      </c>
-      <c r="J131" s="4"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="26" t="s">
-        <v>405</v>
+      <c r="P130" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="R130" s="28"/>
+    </row>
+    <row r="131" ht="20.1" customHeight="1" spans="3:18">
+      <c r="C131" s="12">
+        <v>20099013</v>
+      </c>
+      <c r="E131" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="F131" s="27"/>
+      <c r="J131" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="L131" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="M131" s="30" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="N131" s="5">
         <v>0</v>
       </c>
-      <c r="O131" s="5"/>
-      <c r="P131" s="23"/>
-      <c r="R131" s="24"/>
-      <c r="U131" s="5"/>
-      <c r="V131" s="5"/>
-      <c r="W131" s="5"/>
-      <c r="X131" s="5"/>
-      <c r="Y131" s="5"/>
-    </row>
-    <row r="132" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
+      <c r="O131" s="5">
+        <v>13</v>
+      </c>
+      <c r="P131" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="R131" s="28"/>
+    </row>
+    <row r="132" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+      <c r="A132" s="3" t="s">
+        <v>456</v>
+      </c>
       <c r="B132" s="3"/>
       <c r="C132" s="13" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="D132" s="5"/>
-      <c r="E132" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="F132" s="5"/>
+      <c r="E132" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="F132" s="5">
+        <v>300001</v>
+      </c>
       <c r="G132" s="4">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H132" s="4">
         <v>0</v>
@@ -7028,37 +7211,37 @@
       </c>
       <c r="J132" s="4"/>
       <c r="K132" s="3"/>
-      <c r="L132" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="M132" s="30" t="s">
-        <v>410</v>
+      <c r="L132" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="M132" s="33" t="s">
+        <v>460</v>
       </c>
       <c r="N132" s="5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O132" s="5"/>
-      <c r="P132" s="23"/>
-      <c r="R132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="R132" s="25"/>
       <c r="U132" s="5"/>
       <c r="V132" s="5"/>
       <c r="W132" s="5"/>
       <c r="X132" s="5"/>
       <c r="Y132" s="5"/>
     </row>
-    <row r="133" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="13" t="s">
-        <v>411</v>
+        <v>461</v>
       </c>
       <c r="D133" s="5"/>
-      <c r="E133" s="26" t="s">
-        <v>412</v>
+      <c r="E133" s="29" t="s">
+        <v>462</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="4">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="H133" s="4">
         <v>0</v>
@@ -7068,36 +7251,37 @@
       </c>
       <c r="J133" s="4"/>
       <c r="K133" s="3"/>
-      <c r="L133" s="26" t="s">
-        <v>413</v>
-      </c>
-      <c r="M133" s="30" t="s">
-        <v>414</v>
+      <c r="L133" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="M133" s="33" t="s">
+        <v>464</v>
       </c>
       <c r="N133" s="5">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="O133" s="5"/>
-      <c r="R133" s="24"/>
+      <c r="P133" s="24"/>
+      <c r="R133" s="25"/>
       <c r="U133" s="5"/>
       <c r="V133" s="5"/>
       <c r="W133" s="5"/>
       <c r="X133" s="5"/>
       <c r="Y133" s="5"/>
     </row>
-    <row r="134" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="13" t="s">
-        <v>415</v>
+        <v>465</v>
       </c>
       <c r="D134" s="5"/>
-      <c r="E134" s="26" t="s">
-        <v>416</v>
+      <c r="E134" s="29" t="s">
+        <v>466</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="4">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="H134" s="4">
         <v>0</v>
@@ -7107,344 +7291,356 @@
       </c>
       <c r="J134" s="4"/>
       <c r="K134" s="3"/>
-      <c r="L134" s="26" t="s">
-        <v>417</v>
-      </c>
-      <c r="M134" s="23" t="s">
-        <v>458</v>
+      <c r="L134" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="M134" s="33" t="s">
+        <v>468</v>
       </c>
       <c r="N134" s="5">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O134" s="5"/>
-      <c r="R134" s="24"/>
+      <c r="R134" s="25"/>
       <c r="U134" s="5"/>
       <c r="V134" s="5"/>
       <c r="W134" s="5"/>
       <c r="X134" s="5"/>
       <c r="Y134" s="5"/>
     </row>
-    <row r="135" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
       <c r="C135" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="E135" s="26" t="s">
-        <v>419</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="D135" s="5"/>
+      <c r="E135" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="F135" s="5"/>
       <c r="G135" s="4">
+        <v>1039</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0</v>
+      </c>
+      <c r="I135" s="4">
+        <v>0</v>
+      </c>
+      <c r="J135" s="4"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="M135" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="N135" s="5">
+        <v>0</v>
+      </c>
+      <c r="O135" s="5"/>
+      <c r="R135" s="25"/>
+      <c r="U135" s="5"/>
+      <c r="V135" s="5"/>
+      <c r="W135" s="5"/>
+      <c r="X135" s="5"/>
+      <c r="Y135" s="5"/>
+    </row>
+    <row r="136" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C136" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="E136" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="G136" s="4">
         <v>1036</v>
       </c>
-      <c r="H135" s="4">
-        <v>0</v>
-      </c>
-      <c r="I135" s="4">
-        <v>0</v>
-      </c>
-      <c r="J135" s="4"/>
-      <c r="L135" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="M135" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="N135" s="5">
+      <c r="H136" s="4">
+        <v>0</v>
+      </c>
+      <c r="I136" s="4">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4"/>
+      <c r="L136" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M136" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="N136" s="5">
         <v>-100</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="E136" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="G136" s="4">
+    <row r="137" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C137" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="E137" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="G137" s="4">
         <v>1032</v>
       </c>
-      <c r="H136" s="4">
-        <v>0</v>
-      </c>
-      <c r="I136" s="4">
-        <v>0</v>
-      </c>
-      <c r="J136" s="4"/>
-      <c r="L136" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="M136" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="N136" s="5">
+      <c r="H137" s="4">
+        <v>0</v>
+      </c>
+      <c r="I137" s="4">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4"/>
+      <c r="L137" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="M137" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="N137" s="5">
         <v>123</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C137" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="E137" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="G137" s="4">
-        <v>0</v>
-      </c>
-      <c r="H137" s="4">
-        <v>0</v>
-      </c>
-      <c r="I137" s="4">
-        <v>0</v>
-      </c>
-      <c r="J137" s="4"/>
-      <c r="L137" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="M137" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="N137" s="5">
+    <row r="138" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C138" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="E138" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="G138" s="4">
+        <v>0</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0</v>
+      </c>
+      <c r="I138" s="4">
+        <v>0</v>
+      </c>
+      <c r="J138" s="4"/>
+      <c r="L138" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="M138" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="N138" s="5">
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C138" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="E138" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="G138" s="4">
-        <v>0</v>
-      </c>
-      <c r="H138" s="4">
-        <v>0</v>
-      </c>
-      <c r="I138" s="4">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4"/>
-      <c r="L138" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="M138" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="N138" s="5">
+    <row r="139" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C139" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="E139" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="G139" s="4">
+        <v>0</v>
+      </c>
+      <c r="H139" s="4">
+        <v>0</v>
+      </c>
+      <c r="I139" s="4">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4"/>
+      <c r="L139" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="M139" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="N139" s="5">
         <v>270</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C139" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="E139" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="G139" s="4">
+    <row r="140" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C140" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="E140" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="G140" s="4">
         <v>1037</v>
       </c>
-      <c r="H139" s="4">
-        <v>0</v>
-      </c>
-      <c r="I139" s="4">
-        <v>0</v>
-      </c>
-      <c r="J139" s="4"/>
-      <c r="L139" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="M139" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="N139" s="5">
+      <c r="H140" s="4">
+        <v>0</v>
+      </c>
+      <c r="I140" s="4">
+        <v>0</v>
+      </c>
+      <c r="J140" s="4"/>
+      <c r="L140" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="M140" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="N140" s="5">
         <v>-90</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C140" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="E140" s="26" t="s">
-        <v>436</v>
-      </c>
-      <c r="G140" s="4">
+    <row r="141" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C141" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="E141" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="G141" s="4">
         <v>1038</v>
       </c>
-      <c r="H140" s="4">
-        <v>0</v>
-      </c>
-      <c r="I140" s="4">
-        <v>0</v>
-      </c>
-      <c r="J140" s="4"/>
-      <c r="L140" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="M140" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="N140" s="5">
+      <c r="H141" s="4">
+        <v>0</v>
+      </c>
+      <c r="I141" s="4">
+        <v>0</v>
+      </c>
+      <c r="J141" s="4"/>
+      <c r="L141" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="M141" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="N141" s="5">
         <v>-150</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C141" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="E141" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="G141" s="4">
+    <row r="142" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C142" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E142" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="G142" s="4">
         <v>1047</v>
       </c>
-      <c r="H141" s="4">
-        <v>0</v>
-      </c>
-      <c r="I141" s="4">
-        <v>0</v>
-      </c>
-      <c r="J141" s="4"/>
-      <c r="L141" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="M141" s="29" t="s">
-        <v>440</v>
-      </c>
-      <c r="N141" s="4">
+      <c r="H142" s="4">
+        <v>0</v>
+      </c>
+      <c r="I142" s="4">
+        <v>0</v>
+      </c>
+      <c r="J142" s="4"/>
+      <c r="L142" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M142" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="N142" s="4">
         <v>90</v>
       </c>
-      <c r="O141" s="4"/>
-    </row>
-    <row r="142" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="D142" s="5"/>
-      <c r="E142" s="26" t="s">
-        <v>442</v>
-      </c>
-      <c r="F142" s="5">
+      <c r="O142" s="4"/>
+    </row>
+    <row r="143" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="D143" s="5"/>
+      <c r="E143" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="F143" s="5">
         <v>400001</v>
       </c>
-      <c r="G142" s="4">
+      <c r="G143" s="4">
         <v>1034</v>
       </c>
-      <c r="H142" s="4">
-        <v>0</v>
-      </c>
-      <c r="I142" s="4">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4"/>
-      <c r="K142" s="3"/>
-      <c r="L142" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="M142" s="30" t="s">
-        <v>443</v>
-      </c>
-      <c r="N142" s="5">
+      <c r="H143" s="4">
+        <v>0</v>
+      </c>
+      <c r="I143" s="4">
+        <v>0</v>
+      </c>
+      <c r="J143" s="4"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M143" s="33" t="s">
+        <v>498</v>
+      </c>
+      <c r="N143" s="5">
         <v>110</v>
       </c>
-      <c r="O142" s="5"/>
-      <c r="U142" s="5"/>
-      <c r="V142" s="5"/>
-      <c r="W142" s="5"/>
-      <c r="X142" s="5"/>
-      <c r="Y142" s="5"/>
-    </row>
-    <row r="143" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C143" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="E143" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="G143" s="4">
+      <c r="O143" s="5"/>
+      <c r="U143" s="5"/>
+      <c r="V143" s="5"/>
+      <c r="W143" s="5"/>
+      <c r="X143" s="5"/>
+      <c r="Y143" s="5"/>
+    </row>
+    <row r="144" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C144" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="E144" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="G144" s="4">
         <v>1049</v>
       </c>
-      <c r="H143" s="4">
-        <v>0</v>
-      </c>
-      <c r="I143" s="4">
-        <v>0</v>
-      </c>
-      <c r="J143" s="4"/>
-      <c r="L143" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="M143" s="30" t="s">
-        <v>448</v>
-      </c>
-      <c r="N143" s="5">
+      <c r="H144" s="4">
+        <v>0</v>
+      </c>
+      <c r="I144" s="4">
+        <v>0</v>
+      </c>
+      <c r="J144" s="4"/>
+      <c r="L144" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="M144" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="N144" s="5">
         <v>173</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="E144" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="G144" s="4">
+    <row r="145" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C145" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="E145" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="G145" s="4">
         <v>1051</v>
       </c>
-      <c r="H144" s="4">
-        <v>0</v>
-      </c>
-      <c r="I144" s="4">
-        <v>0</v>
-      </c>
-      <c r="J144" s="4"/>
-      <c r="L144" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="M144" s="30" t="s">
-        <v>461</v>
-      </c>
-      <c r="N144" s="5">
+      <c r="H145" s="4">
+        <v>0</v>
+      </c>
+      <c r="I145" s="4">
+        <v>0</v>
+      </c>
+      <c r="J145" s="4"/>
+      <c r="L145" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="M145" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="N145" s="5">
         <v>235</v>
       </c>
     </row>
-    <row r="145" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C145" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="E145" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="G145" s="4">
+    <row r="146" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C146" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="E146" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="G146" s="4">
         <v>1053</v>
       </c>
-      <c r="H145" s="4">
-        <v>0</v>
-      </c>
-      <c r="I145" s="4">
-        <v>0</v>
-      </c>
-      <c r="J145" s="4"/>
-      <c r="L145" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="M145" s="30" t="s">
-        <v>464</v>
-      </c>
-      <c r="N145" s="5">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="146" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C146" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="E146" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="G146" s="4">
-        <v>1054</v>
-      </c>
       <c r="H146" s="4">
         <v>0</v>
       </c>
@@ -7452,22 +7648,22 @@
         <v>0</v>
       </c>
       <c r="J146" s="4"/>
-      <c r="L146" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="M146" s="30" t="s">
-        <v>470</v>
+      <c r="L146" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="M146" s="33" t="s">
+        <v>507</v>
       </c>
       <c r="N146" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="147" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" ht="20.1" customHeight="1" spans="3:14">
       <c r="C147" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="E147" s="26" t="s">
-        <v>469</v>
+        <v>508</v>
+      </c>
+      <c r="E147" s="29" t="s">
+        <v>509</v>
       </c>
       <c r="G147" s="4">
         <v>1054</v>
@@ -7479,25 +7675,25 @@
         <v>0</v>
       </c>
       <c r="J147" s="4"/>
-      <c r="L147" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="M147" s="30" t="s">
-        <v>471</v>
+      <c r="L147" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="M147" s="33" t="s">
+        <v>510</v>
       </c>
       <c r="N147" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="148" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" ht="20.1" customHeight="1" spans="3:14">
       <c r="C148" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="E148" s="26" t="s">
-        <v>497</v>
+        <v>511</v>
+      </c>
+      <c r="E148" s="29" t="s">
+        <v>512</v>
       </c>
       <c r="G148" s="4">
-        <v>10</v>
+        <v>1054</v>
       </c>
       <c r="H148" s="4">
         <v>0</v>
@@ -7506,60 +7702,87 @@
         <v>0</v>
       </c>
       <c r="J148" s="4"/>
-      <c r="L148" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="M148" s="30" t="s">
-        <v>471</v>
+      <c r="L148" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="M148" s="33" t="s">
+        <v>513</v>
       </c>
       <c r="N148" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="149" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" ht="20.1" customHeight="1" spans="3:14">
       <c r="C149" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="E149" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="G149" s="4">
+        <v>10</v>
+      </c>
+      <c r="H149" s="4">
+        <v>0</v>
+      </c>
+      <c r="I149" s="4">
+        <v>0</v>
+      </c>
+      <c r="J149" s="4"/>
+      <c r="L149" s="29" t="s">
         <v>516</v>
       </c>
-      <c r="E149" s="26" t="s">
+      <c r="M149" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="N149" s="5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150" ht="20.1" customHeight="1" spans="3:14">
+      <c r="C150" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="G149" s="4">
+      <c r="E150" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="G150" s="4">
         <v>19</v>
       </c>
-      <c r="H149" s="4">
-        <v>0</v>
-      </c>
-      <c r="I149" s="4">
-        <v>0</v>
-      </c>
-      <c r="J149" s="4"/>
-      <c r="L149" s="26" t="s">
+      <c r="H150" s="4">
+        <v>0</v>
+      </c>
+      <c r="I150" s="4">
+        <v>0</v>
+      </c>
+      <c r="J150" s="4"/>
+      <c r="L150" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M150" s="33" t="s">
         <v>519</v>
       </c>
-      <c r="M149" s="30" t="s">
-        <v>520</v>
-      </c>
-      <c r="N149" s="5">
+      <c r="N150" s="5">
         <v>180</v>
       </c>
     </row>
-    <row r="150" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="20.1" customHeight="1"/>
+    <row r="152" ht="20.1" customHeight="1"/>
+    <row r="153" ht="20.1" customHeight="1"/>
+    <row r="154" ht="20.1" customHeight="1"/>
+    <row r="155" ht="20.1" customHeight="1"/>
+    <row r="156" ht="20.1" customHeight="1"/>
+    <row r="157" ht="20.1" customHeight="1"/>
+    <row r="158" ht="20.1" customHeight="1"/>
+    <row r="159" ht="20.1" customHeight="1"/>
+    <row r="160" ht="20.1" customHeight="1"/>
+    <row r="161" ht="20.1" customHeight="1"/>
+    <row r="162" ht="20.1" customHeight="1"/>
+    <row r="163" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -4929,7 +4929,7 @@
         <v>6000101</v>
       </c>
       <c r="G52" s="4">
-        <v>1029</v>
+        <v>1073</v>
       </c>
       <c r="H52" s="4">
         <v>0</v>

--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC97ED00-E116-40D5-949D-FAD3462D14FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -134,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="1">
+    <comment ref="G3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -169,14 +162,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>作者:
 0:</t>
@@ -194,7 +187,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 1</t>
@@ -209,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -233,7 +226,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID,</t>
         </r>
@@ -249,7 +242,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>UI</t>
         </r>
@@ -265,7 +258,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -281,7 +274,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>;</t>
         </r>
@@ -297,7 +290,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -313,7 +306,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -329,7 +322,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">100;0  </t>
         </r>
@@ -345,7 +338,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>50%</t>
         </r>
@@ -361,7 +354,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>100</t>
         </r>
@@ -375,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -399,7 +392,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">NPC
 </t>
@@ -416,7 +409,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">:10;20 </t>
         </r>
@@ -432,7 +425,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 10-20</t>
         </r>
@@ -446,7 +439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -474,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -504,7 +497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="0">
+    <comment ref="Y4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1227,887 +1220,884 @@
     <t>1459,-421,840</t>
   </si>
   <si>
+    <t>20000101</t>
+  </si>
+  <si>
+    <t>家族管理</t>
+  </si>
+  <si>
+    <t>-8304,5,203</t>
+  </si>
+  <si>
+    <t>20000102</t>
+  </si>
+  <si>
+    <t>家族任务</t>
+  </si>
+  <si>
+    <t>-4274,5,2498</t>
+  </si>
+  <si>
+    <t>我这里的家族试炼任务每完成20、40、60、80、100环都会获得一份特殊奖励哦!</t>
+  </si>
+  <si>
+    <t>20000103</t>
+  </si>
+  <si>
+    <t>家族捐献</t>
+  </si>
+  <si>
+    <t>-5882,5,76</t>
+  </si>
+  <si>
+    <t>20000104</t>
+  </si>
+  <si>
+    <t>家族强化</t>
+  </si>
+  <si>
+    <t>NPC_CunZhang</t>
+  </si>
+  <si>
+    <t>-6660,5,2006</t>
+  </si>
+  <si>
+    <t>20000105</t>
+  </si>
+  <si>
+    <t>家族商店</t>
+  </si>
+  <si>
+    <t>-8439,5,-1948</t>
+  </si>
+  <si>
+    <t>20000106</t>
+  </si>
+  <si>
+    <t>家族科技</t>
+  </si>
+  <si>
+    <t>-7715,5,2106</t>
+  </si>
+  <si>
+    <t>20001001</t>
+  </si>
+  <si>
+    <t>杂货药店老板</t>
+  </si>
+  <si>
+    <t>-442,0,-600</t>
+  </si>
+  <si>
+    <t>装备店老板</t>
+  </si>
+  <si>
+    <t>912,0,-700</t>
+  </si>
+  <si>
+    <t>村长·乌尔</t>
+  </si>
+  <si>
+    <t>30010001,30010002,30010003,30010006,30010008,30010020,30010044,31001008</t>
+  </si>
+  <si>
+    <t>140,16,150</t>
+  </si>
+  <si>
+    <t>勇士,我是这里的村长,这里是一个被诅咒的村子,如果怕死,你还是赶紧离开这个鬼地方吧！</t>
+  </si>
+  <si>
+    <t>圣光军队长</t>
+  </si>
+  <si>
+    <t>NPC_ShiBing</t>
+  </si>
+  <si>
+    <t>-196,0,-1568</t>
+  </si>
+  <si>
+    <t>我们是国王圣恩手下的圣光军,不要轻易的出村子,那并不是我们的保护范围.</t>
+  </si>
+  <si>
+    <t>圣光军士兵</t>
+  </si>
+  <si>
+    <t>200,0,-2600</t>
+  </si>
+  <si>
+    <t>我觉得我们队长很懦弱,他总是告诫我们不要出村子,但我认为外面并没有什么可怕的！</t>
+  </si>
+  <si>
+    <t>-242,0,-2600</t>
+  </si>
+  <si>
+    <t>我是刚来这里的,这里每个人看起来都很害怕去外面！</t>
+  </si>
+  <si>
+    <t>勇士帕托</t>
+  </si>
+  <si>
+    <t>30010004,30010005</t>
+  </si>
+  <si>
+    <t>-1100,0,-4500</t>
+  </si>
+  <si>
+    <t>这些该死的野狼,真相让这些它们赶紧离开这个鬼地方！</t>
+  </si>
+  <si>
+    <t>安迪·凯伦</t>
+  </si>
+  <si>
+    <t>-2729,0,747</t>
+  </si>
+  <si>
+    <t>在村子里我的力气最大,如果你愿意给我金币,我可以帮你做一些事。</t>
+  </si>
+  <si>
+    <t>流浪者</t>
+  </si>
+  <si>
+    <t>30010007</t>
+  </si>
+  <si>
+    <t>-3364,-9,-876</t>
+  </si>
+  <si>
+    <t>有一天我梦游,不知不觉的就来到了这个村子.</t>
+  </si>
+  <si>
+    <t>受伤的士兵</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>不要问我,我什么都不知道！</t>
+  </si>
+  <si>
+    <t>走失的矿工</t>
+  </si>
+  <si>
+    <t>30010009</t>
+  </si>
+  <si>
+    <t>6831,-92,-4900</t>
+  </si>
+  <si>
+    <t>我好不容易逃出了那个该死的矿洞,在里面我发现了一个很凶猛的怪兽,不过我还没来的急看清那怪兽的样子就已经被那巨大的爪子拍晕了.</t>
+  </si>
+  <si>
+    <t>艾丽公主</t>
+  </si>
+  <si>
+    <t>30010018,30010019,31001001</t>
+  </si>
+  <si>
+    <t>14275,2896,-1827</t>
+  </si>
+  <si>
+    <t>我多么希望赶紧离开这个阴森的地方,我好怕,谁来救救我啊</t>
+  </si>
+  <si>
+    <t>矿工艾伯特</t>
+  </si>
+  <si>
+    <t>30010011,30010012,30010013,30010014</t>
+  </si>
+  <si>
+    <t>14719,2893,-5084</t>
+  </si>
+  <si>
+    <t>该死的！刚才双眼一黑我就什么也不知道了！这个矿洞里究竟发生了什么！</t>
+  </si>
+  <si>
+    <t>艾伯特博士</t>
+  </si>
+  <si>
+    <t>30010015,30010016,30010017</t>
+  </si>
+  <si>
+    <t>15756,2896,-7486</t>
+  </si>
+  <si>
+    <t>我想我已经知道了事情的真相,这里已经非常危险了！</t>
+  </si>
+  <si>
+    <t>勇士博肯</t>
+  </si>
+  <si>
+    <t>30010021,30010022,30010026</t>
+  </si>
+  <si>
+    <t>20083,2903,-3521</t>
+  </si>
+  <si>
+    <t>希望这次旅行可以平安的到达目的地.</t>
+  </si>
+  <si>
+    <t>石墓护卫</t>
+  </si>
+  <si>
+    <t>镇压在这里的怪物已经一年多没什么动静了,都不知道是死是活！</t>
+  </si>
+  <si>
+    <t>森林守卫</t>
+  </si>
+  <si>
+    <t>30010023,30010024,30010025,31001002</t>
+  </si>
+  <si>
+    <t>14313,2905,-6593</t>
+  </si>
+  <si>
+    <t>森林中有一个大型的怪兽,没事还是去别的地方转转吧,这里太危险.</t>
+  </si>
+  <si>
+    <t>石墓带刀护卫</t>
+  </si>
+  <si>
+    <t>禁止入内！</t>
+  </si>
+  <si>
+    <t>石墓守陵人</t>
+  </si>
+  <si>
+    <t>30010027,30010028,30010029,30010030,30010031,31001003,31001004</t>
+  </si>
+  <si>
+    <t>14705,2904,-3602</t>
+  </si>
+  <si>
+    <t>这个古墓已经很久没人来过了.</t>
+  </si>
+  <si>
+    <t>森林任务大使</t>
+  </si>
+  <si>
+    <t>这里已经大半年没有任何人来到这里了,我好像都不太会说话了.</t>
+  </si>
+  <si>
+    <t>石墓二层守陵人</t>
+  </si>
+  <si>
+    <t>15180,2904,-4445</t>
+  </si>
+  <si>
+    <t>地下洞穴守洞人</t>
+  </si>
+  <si>
+    <t>30010032,30010033,30010034,30010035,30010036,30010037,30010038,30010039,30010040,30010041,30010042,30010043,31001005,31001006,31001007</t>
+  </si>
+  <si>
+    <t>17004,2893,-6304</t>
+  </si>
+  <si>
+    <t>没想到竟然有人发现了这里的秘密！</t>
+  </si>
+  <si>
+    <t>仓库管理员</t>
+  </si>
+  <si>
+    <t>118400,-500,16600</t>
+  </si>
+  <si>
+    <t>20002001</t>
+  </si>
+  <si>
+    <t>14222,2896,-4417</t>
+  </si>
+  <si>
+    <t>20002002</t>
+  </si>
+  <si>
+    <t>15449,2888,-5419</t>
+  </si>
+  <si>
+    <t>20002003</t>
+  </si>
+  <si>
+    <t>将军·希尔</t>
+  </si>
+  <si>
+    <t>30020101,30020102,30020103,30020104,30020105,30020106,30020124,50000002,41001001,41001002,41001003,41001101,41001102,41001103</t>
+  </si>
+  <si>
+    <t>14962,2890,-4838</t>
+  </si>
+  <si>
+    <t>20002004</t>
+  </si>
+  <si>
+    <t>探路的军士</t>
+  </si>
+  <si>
+    <t>30020107,30020108,30020109,30020110</t>
+  </si>
+  <si>
+    <t>15373,2893,-9020</t>
+  </si>
+  <si>
+    <t>20002005</t>
+  </si>
+  <si>
+    <t>幸存者</t>
+  </si>
+  <si>
+    <t>30020111,30020112,30020113,30020114,30020115,30020116,30020117,</t>
+  </si>
+  <si>
+    <t>15689,2889,-6938</t>
+  </si>
+  <si>
+    <t>20002006</t>
+  </si>
+  <si>
+    <t>走失的士兵</t>
+  </si>
+  <si>
+    <t>30020118,30020119,30020120,30020121,30020122,30020123,30020124,</t>
+  </si>
+  <si>
+    <t>14414,2801,-6748</t>
+  </si>
+  <si>
+    <t>20002007</t>
+  </si>
+  <si>
+    <t>20002008</t>
+  </si>
+  <si>
+    <t>20002009</t>
+  </si>
+  <si>
+    <t>12961,2896,-7298</t>
+  </si>
+  <si>
+    <t>20003001</t>
+  </si>
+  <si>
+    <t>14671,2902,-3600</t>
+  </si>
+  <si>
+    <t>20003002</t>
+  </si>
+  <si>
+    <t>14664,2897,-4950</t>
+  </si>
+  <si>
+    <t>20003003</t>
+  </si>
+  <si>
+    <t>镇长卡瑟</t>
+  </si>
+  <si>
+    <t>30030001,30030002,30030003,30030004,30030005,30030006,30030007,30030008,30030035,30030036,30030037,30030038,41002001,41002002,41002003,41002101,41002102,41002103,41003001,41003002,41003003,41003101,41003102,41003103</t>
+  </si>
+  <si>
+    <t>14635,2897,-4301</t>
+  </si>
+  <si>
+    <t>20003004</t>
+  </si>
+  <si>
+    <t>侍卫卡夫</t>
+  </si>
+  <si>
+    <t>30030009,30030010,30030011,30030012,30030013,30030014</t>
+  </si>
+  <si>
+    <t>14589,2905,-5444</t>
+  </si>
+  <si>
+    <t>20003005</t>
+  </si>
+  <si>
+    <t>冰雪之路引路人</t>
+  </si>
+  <si>
+    <t>30030023,30030024,30030025,30030026,30030027,30030028,30030029</t>
+  </si>
+  <si>
+    <t>13792,2904,-7159</t>
+  </si>
+  <si>
+    <t>20003006</t>
+  </si>
+  <si>
+    <t>15088,3459,-7501</t>
+  </si>
+  <si>
+    <t>20003007</t>
+  </si>
+  <si>
+    <t>20003008</t>
+  </si>
+  <si>
+    <t>20003009</t>
+  </si>
+  <si>
+    <t>魔穴守护人</t>
+  </si>
+  <si>
+    <t>30030030,30030031,30030032,30030033,30030034</t>
+  </si>
+  <si>
+    <t>15088,3459,-7500</t>
+  </si>
+  <si>
+    <t>20003010</t>
+  </si>
+  <si>
+    <t>瑞斯</t>
+  </si>
+  <si>
+    <t>30030015,30030016,30030017,30030018,30030019,30030020,30030021,30030022</t>
+  </si>
+  <si>
+    <t>14291,2901,-3398</t>
+  </si>
+  <si>
+    <t>20004001</t>
+  </si>
+  <si>
+    <t>17987,2913,-5746</t>
+  </si>
+  <si>
+    <t>20004002</t>
+  </si>
+  <si>
+    <t>19623,2904,-5818</t>
+  </si>
+  <si>
+    <t>20004003</t>
+  </si>
+  <si>
+    <t>镇长莫林</t>
+  </si>
+  <si>
+    <t>30040001,30040002,30040003,30040004,30040005,30040006,30040007,30040008,30040009,30040022,30040023,30040029,30040030,30040031,30040032,30040033</t>
+  </si>
+  <si>
+    <t>18788,2904,-5706</t>
+  </si>
+  <si>
+    <t>20004005</t>
+  </si>
+  <si>
+    <t>森林守护人</t>
+  </si>
+  <si>
+    <t>30040010,30040011,30040012,30040013,30040014,30040015,30040016</t>
+  </si>
+  <si>
+    <t>17060,2902,-7683</t>
+  </si>
+  <si>
+    <t>20004006</t>
+  </si>
+  <si>
+    <t>矿工哈登</t>
+  </si>
+  <si>
+    <t>30040017,30040018,30040019,30040020,30040021</t>
+  </si>
+  <si>
+    <t>25878,2895,-6669</t>
+  </si>
+  <si>
+    <t>20004007</t>
+  </si>
+  <si>
+    <t>20004008</t>
+  </si>
+  <si>
+    <t>20004009</t>
+  </si>
+  <si>
+    <t>峡谷护卫</t>
+  </si>
+  <si>
+    <t>30040024,30040025,30040026,30040027</t>
+  </si>
+  <si>
+    <t>14323,2904,-2681</t>
+  </si>
+  <si>
+    <t>20004010</t>
+  </si>
+  <si>
+    <t>裂谷护卫</t>
+  </si>
+  <si>
+    <t>30040028</t>
+  </si>
+  <si>
+    <t>23872,2904,-11240</t>
+  </si>
+  <si>
+    <t>20005001</t>
+  </si>
+  <si>
+    <t>-442,2888,-1611</t>
+  </si>
+  <si>
+    <t>20005002</t>
+  </si>
+  <si>
+    <t>912,2888,-1707</t>
+  </si>
+  <si>
+    <t>20005003</t>
+  </si>
+  <si>
+    <t>镇长乌尔</t>
+  </si>
+  <si>
+    <t>30050001,30050002,30050003,30050004,30050005,30050006,30050007,30050008,41004001,41004002,41004003,41004101,41004102,41004103,30050023</t>
+  </si>
+  <si>
+    <t>228,2941,-620</t>
+  </si>
+  <si>
+    <t>20005004</t>
+  </si>
+  <si>
+    <t>卡琳娜</t>
+  </si>
+  <si>
+    <t>30050009,30050010,30050011,30050012,30050013,30050014</t>
+  </si>
+  <si>
+    <t>14606,2880,-6651</t>
+  </si>
+  <si>
+    <t>20005005</t>
+  </si>
+  <si>
+    <t>卡尔</t>
+  </si>
+  <si>
+    <t>20005006</t>
+  </si>
+  <si>
+    <t>潜伏者·乌利兹</t>
+  </si>
+  <si>
+    <t>30050015,30050016,30050017,30050018,30050019,30050020,30050021,30050022</t>
+  </si>
+  <si>
+    <t>14149,2801,-6951</t>
+  </si>
+  <si>
+    <t>20005007</t>
+  </si>
+  <si>
+    <t>20005008</t>
+  </si>
+  <si>
+    <t>圣光城装备老板</t>
+  </si>
+  <si>
+    <t>NPC_Task_1</t>
+  </si>
+  <si>
+    <t>我这里的货物物美价廉!赶紧来看看有什么需要的,过段时间可不是这个价格呦！</t>
+  </si>
+  <si>
+    <t>圣光城药店老板</t>
+  </si>
+  <si>
+    <t>如果你在野外受伤了,赶紧来我这里买点药,保证喝完精神焕发</t>
+  </si>
+  <si>
+    <t>圣恩·帕托</t>
+  </si>
+  <si>
+    <t>在这个圣光城里,我时刻都感受到神圣的力量</t>
+  </si>
+  <si>
+    <t>圣恩·乌尔</t>
+  </si>
+  <si>
+    <t>我们不能在这样懦弱下去了,我们要复仇你明白嘛？</t>
+  </si>
+  <si>
+    <t>圣恩·瑞儿</t>
+  </si>
+  <si>
+    <t>听过国王马上要下令进攻恶魔军团了,我们应该做好准备！</t>
+  </si>
+  <si>
+    <t>别说话,这里需要安静！</t>
+  </si>
+  <si>
+    <t>小龟赛跑大使</t>
+  </si>
+  <si>
+    <t>-844,-771,-4836</t>
+  </si>
+  <si>
+    <t>小龟1号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_1</t>
+  </si>
+  <si>
+    <t>-529,-765,-5248</t>
+  </si>
+  <si>
+    <t>我年轻力胜,获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟2号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_2</t>
+  </si>
+  <si>
+    <t>-205,-765,-5248</t>
+  </si>
+  <si>
+    <t>我是来自沙漠的龟,这么热的天获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟3号</t>
+  </si>
+  <si>
+    <t>NPC_XiaoGui_3</t>
+  </si>
+  <si>
+    <t>92,-765,-5248</t>
+  </si>
+  <si>
+    <t>我拥有丰富的赛龟经验,获胜最终胜利的一定是我！</t>
+  </si>
+  <si>
+    <t>小龟一号选手</t>
+  </si>
+  <si>
+    <t>20000,5000,5000</t>
+  </si>
+  <si>
+    <t>-2.46;3.55;97.41</t>
+  </si>
+  <si>
+    <t>小龟二号选手</t>
+  </si>
+  <si>
+    <t>小龟三号选手</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>30000001</t>
+  </si>
+  <si>
+    <t>农场管理员</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanNongChang</t>
+  </si>
+  <si>
+    <t>-468,0,-2912</t>
+  </si>
+  <si>
+    <t>30000002</t>
+  </si>
+  <si>
+    <t>牧场管理员</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanMuChang</t>
+  </si>
+  <si>
+    <t>-1090,0,-1494</t>
+  </si>
+  <si>
+    <t>30000003</t>
+  </si>
+  <si>
+    <t>家园管家</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanGuanLi</t>
+  </si>
+  <si>
+    <t>3061,0,1224</t>
+  </si>
+  <si>
+    <t>30000004</t>
+  </si>
+  <si>
+    <t>家园公告牌</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanGongGao</t>
+  </si>
+  <si>
+    <t>1450,0,-3250</t>
+  </si>
+  <si>
+    <t>30000005</t>
+  </si>
+  <si>
+    <t>采购管理员</t>
+  </si>
+  <si>
+    <t>2963,0,-3074</t>
+  </si>
+  <si>
+    <t>30000006</t>
+  </si>
+  <si>
+    <t>家园存放员</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanPet</t>
+  </si>
+  <si>
+    <t>-1293,0,1892</t>
+  </si>
+  <si>
+    <t>30000007</t>
+  </si>
+  <si>
+    <t>家园士兵</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanShiBing</t>
+  </si>
+  <si>
+    <t>949,0,-4357</t>
+  </si>
+  <si>
+    <t>30000008</t>
+  </si>
+  <si>
+    <t>1532,0,-4366</t>
+  </si>
+  <si>
+    <t>30000009</t>
+  </si>
+  <si>
+    <t>美味大师</t>
+  </si>
+  <si>
+    <t>NPC_JiaYuanMeiWei</t>
+  </si>
+  <si>
+    <t>2845,0,-2586</t>
+  </si>
+  <si>
+    <t>30000010</t>
+  </si>
+  <si>
+    <t>家园宠物管理员</t>
+  </si>
+  <si>
+    <t>941,0,1588</t>
+  </si>
+  <si>
+    <t>30000011</t>
+  </si>
+  <si>
+    <t>装备宠物加锁</t>
+  </si>
+  <si>
+    <t>906,-423,-1201</t>
+  </si>
+  <si>
+    <t>30000013</t>
+  </si>
+  <si>
+    <t>家园商人</t>
+  </si>
+  <si>
+    <t>-1556,0,1277</t>
+  </si>
+  <si>
+    <t>30000014</t>
+  </si>
+  <si>
+    <t>藏宝图生活技能仓库</t>
+  </si>
+  <si>
+    <t>2350,0,1620</t>
+  </si>
+  <si>
+    <t>30000015</t>
+  </si>
+  <si>
+    <t>装备增幅</t>
+  </si>
+  <si>
+    <t>3439,0,804</t>
+  </si>
+  <si>
+    <t>30000016</t>
+  </si>
+  <si>
+    <t>家园觉醒大师</t>
+  </si>
+  <si>
+    <t>14,0,2133</t>
+  </si>
+  <si>
+    <t>40000001</t>
+  </si>
+  <si>
+    <t>战场招募·猎魔</t>
+  </si>
+  <si>
+    <t>-7655,0,-1313</t>
+  </si>
+  <si>
+    <t>40000002</t>
+  </si>
+  <si>
+    <t>战场招募·曙光</t>
+  </si>
+  <si>
+    <t>9256,0,-1330</t>
+  </si>
+  <si>
+    <t>40000003</t>
+  </si>
+  <si>
+    <t>神秘之门</t>
+  </si>
+  <si>
+    <t>NPC_ShenMiZhiMen</t>
+  </si>
+  <si>
+    <t>40000004</t>
+  </si>
+  <si>
+    <t>返回</t>
+  </si>
+  <si>
+    <t>0,0,-300</t>
+  </si>
+  <si>
+    <t>宠物装备制造</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <t>20000043</t>
-  </si>
-  <si>
-    <t>宠物装备商人</t>
-  </si>
-  <si>
-    <t>1759,-421,880</t>
-  </si>
-  <si>
-    <t>20000101</t>
-  </si>
-  <si>
-    <t>家族管理</t>
-  </si>
-  <si>
-    <t>-8304,5,203</t>
-  </si>
-  <si>
-    <t>20000102</t>
-  </si>
-  <si>
-    <t>家族任务</t>
-  </si>
-  <si>
-    <t>-4274,5,2498</t>
-  </si>
-  <si>
-    <t>我这里的家族试炼任务每完成20、40、60、80、100环都会获得一份特殊奖励哦!</t>
-  </si>
-  <si>
-    <t>20000103</t>
-  </si>
-  <si>
-    <t>家族捐献</t>
-  </si>
-  <si>
-    <t>-5882,5,76</t>
-  </si>
-  <si>
-    <t>20000104</t>
-  </si>
-  <si>
-    <t>家族强化</t>
-  </si>
-  <si>
-    <t>NPC_CunZhang</t>
-  </si>
-  <si>
-    <t>-6660,5,2006</t>
-  </si>
-  <si>
-    <t>20000105</t>
-  </si>
-  <si>
-    <t>家族商店</t>
-  </si>
-  <si>
-    <t>-8439,5,-1948</t>
-  </si>
-  <si>
-    <t>20000106</t>
-  </si>
-  <si>
-    <t>家族科技</t>
-  </si>
-  <si>
-    <t>-7715,5,2106</t>
-  </si>
-  <si>
-    <t>20001001</t>
-  </si>
-  <si>
-    <t>杂货药店老板</t>
-  </si>
-  <si>
-    <t>-442,0,-600</t>
-  </si>
-  <si>
-    <t>装备店老板</t>
-  </si>
-  <si>
-    <t>912,0,-700</t>
-  </si>
-  <si>
-    <t>村长·乌尔</t>
-  </si>
-  <si>
-    <t>30010001,30010002,30010003,30010006,30010008,30010020,30010044,31001008</t>
-  </si>
-  <si>
-    <t>140,16,150</t>
-  </si>
-  <si>
-    <t>勇士,我是这里的村长,这里是一个被诅咒的村子,如果怕死,你还是赶紧离开这个鬼地方吧！</t>
-  </si>
-  <si>
-    <t>圣光军队长</t>
-  </si>
-  <si>
-    <t>NPC_ShiBing</t>
-  </si>
-  <si>
-    <t>-196,0,-1568</t>
-  </si>
-  <si>
-    <t>我们是国王圣恩手下的圣光军,不要轻易的出村子,那并不是我们的保护范围.</t>
-  </si>
-  <si>
-    <t>圣光军士兵</t>
-  </si>
-  <si>
-    <t>200,0,-2600</t>
-  </si>
-  <si>
-    <t>我觉得我们队长很懦弱,他总是告诫我们不要出村子,但我认为外面并没有什么可怕的！</t>
-  </si>
-  <si>
-    <t>-242,0,-2600</t>
-  </si>
-  <si>
-    <t>我是刚来这里的,这里每个人看起来都很害怕去外面！</t>
-  </si>
-  <si>
-    <t>勇士帕托</t>
-  </si>
-  <si>
-    <t>30010004,30010005</t>
-  </si>
-  <si>
-    <t>-1100,0,-4500</t>
-  </si>
-  <si>
-    <t>这些该死的野狼,真相让这些它们赶紧离开这个鬼地方！</t>
-  </si>
-  <si>
-    <t>安迪·凯伦</t>
-  </si>
-  <si>
-    <t>-2729,0,747</t>
-  </si>
-  <si>
-    <t>在村子里我的力气最大,如果你愿意给我金币,我可以帮你做一些事。</t>
-  </si>
-  <si>
-    <t>流浪者</t>
-  </si>
-  <si>
-    <t>30010007</t>
-  </si>
-  <si>
-    <t>-3364,-9,-876</t>
-  </si>
-  <si>
-    <t>有一天我梦游,不知不觉的就来到了这个村子.</t>
-  </si>
-  <si>
-    <t>受伤的士兵</t>
-  </si>
-  <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>不要问我,我什么都不知道！</t>
-  </si>
-  <si>
-    <t>走失的矿工</t>
-  </si>
-  <si>
-    <t>30010009</t>
-  </si>
-  <si>
-    <t>6831,-92,-4900</t>
-  </si>
-  <si>
-    <t>我好不容易逃出了那个该死的矿洞,在里面我发现了一个很凶猛的怪兽,不过我还没来的急看清那怪兽的样子就已经被那巨大的爪子拍晕了.</t>
-  </si>
-  <si>
-    <t>艾丽公主</t>
-  </si>
-  <si>
-    <t>30010018,30010019,31001001</t>
-  </si>
-  <si>
-    <t>14275,2896,-1827</t>
-  </si>
-  <si>
-    <t>我多么希望赶紧离开这个阴森的地方,我好怕,谁来救救我啊</t>
-  </si>
-  <si>
-    <t>矿工艾伯特</t>
-  </si>
-  <si>
-    <t>30010011,30010012,30010013,30010014</t>
-  </si>
-  <si>
-    <t>14719,2893,-5084</t>
-  </si>
-  <si>
-    <t>该死的！刚才双眼一黑我就什么也不知道了！这个矿洞里究竟发生了什么！</t>
-  </si>
-  <si>
-    <t>艾伯特博士</t>
-  </si>
-  <si>
-    <t>30010015,30010016,30010017</t>
-  </si>
-  <si>
-    <t>15756,2896,-7486</t>
-  </si>
-  <si>
-    <t>我想我已经知道了事情的真相,这里已经非常危险了！</t>
-  </si>
-  <si>
-    <t>勇士博肯</t>
-  </si>
-  <si>
-    <t>30010021,30010022,30010026</t>
-  </si>
-  <si>
-    <t>20083,2903,-3521</t>
-  </si>
-  <si>
-    <t>希望这次旅行可以平安的到达目的地.</t>
-  </si>
-  <si>
-    <t>石墓护卫</t>
-  </si>
-  <si>
-    <t>镇压在这里的怪物已经一年多没什么动静了,都不知道是死是活！</t>
-  </si>
-  <si>
-    <t>森林守卫</t>
-  </si>
-  <si>
-    <t>30010023,30010024,30010025,31001002</t>
-  </si>
-  <si>
-    <t>14313,2905,-6593</t>
-  </si>
-  <si>
-    <t>森林中有一个大型的怪兽,没事还是去别的地方转转吧,这里太危险.</t>
-  </si>
-  <si>
-    <t>石墓带刀护卫</t>
-  </si>
-  <si>
-    <t>禁止入内！</t>
-  </si>
-  <si>
-    <t>石墓守陵人</t>
-  </si>
-  <si>
-    <t>30010027,30010028,30010029,30010030,30010031,31001003,31001004</t>
-  </si>
-  <si>
-    <t>14705,2904,-3602</t>
-  </si>
-  <si>
-    <t>这个古墓已经很久没人来过了.</t>
-  </si>
-  <si>
-    <t>森林任务大使</t>
-  </si>
-  <si>
-    <t>这里已经大半年没有任何人来到这里了,我好像都不太会说话了.</t>
-  </si>
-  <si>
-    <t>石墓二层守陵人</t>
-  </si>
-  <si>
-    <t>15180,2904,-4445</t>
-  </si>
-  <si>
-    <t>地下洞穴守洞人</t>
-  </si>
-  <si>
-    <t>30010032,30010033,30010034,30010035,30010036,30010037,30010038,30010039,30010040,30010041,30010042,30010043,31001005,31001006,31001007</t>
-  </si>
-  <si>
-    <t>17004,2893,-6304</t>
-  </si>
-  <si>
-    <t>没想到竟然有人发现了这里的秘密！</t>
-  </si>
-  <si>
-    <t>仓库管理员</t>
-  </si>
-  <si>
-    <t>118400,-500,16600</t>
-  </si>
-  <si>
-    <t>20002001</t>
-  </si>
-  <si>
-    <t>14222,2896,-4417</t>
-  </si>
-  <si>
-    <t>20002002</t>
-  </si>
-  <si>
-    <t>15449,2888,-5419</t>
-  </si>
-  <si>
-    <t>20002003</t>
-  </si>
-  <si>
-    <t>将军·希尔</t>
-  </si>
-  <si>
-    <t>30020101,30020102,30020103,30020104,30020105,30020106,30020124,50000002,41001001,41001002,41001003,41001101,41001102,41001103</t>
-  </si>
-  <si>
-    <t>14962,2890,-4838</t>
-  </si>
-  <si>
-    <t>20002004</t>
-  </si>
-  <si>
-    <t>探路的军士</t>
-  </si>
-  <si>
-    <t>30020107,30020108,30020109,30020110</t>
-  </si>
-  <si>
-    <t>15373,2893,-9020</t>
-  </si>
-  <si>
-    <t>20002005</t>
-  </si>
-  <si>
-    <t>幸存者</t>
-  </si>
-  <si>
-    <t>30020111,30020112,30020113,30020114,30020115,30020116,30020117,</t>
-  </si>
-  <si>
-    <t>15689,2889,-6938</t>
-  </si>
-  <si>
-    <t>20002006</t>
-  </si>
-  <si>
-    <t>走失的士兵</t>
-  </si>
-  <si>
-    <t>30020118,30020119,30020120,30020121,30020122,30020123,30020124,</t>
-  </si>
-  <si>
-    <t>14414,2801,-6748</t>
-  </si>
-  <si>
-    <t>20002007</t>
-  </si>
-  <si>
-    <t>20002008</t>
-  </si>
-  <si>
-    <t>20002009</t>
-  </si>
-  <si>
-    <t>12961,2896,-7298</t>
-  </si>
-  <si>
-    <t>20003001</t>
-  </si>
-  <si>
-    <t>14671,2902,-3600</t>
-  </si>
-  <si>
-    <t>20003002</t>
-  </si>
-  <si>
-    <t>14664,2897,-4950</t>
-  </si>
-  <si>
-    <t>20003003</t>
-  </si>
-  <si>
-    <t>镇长卡瑟</t>
-  </si>
-  <si>
-    <t>30030001,30030002,30030003,30030004,30030005,30030006,30030007,30030008,30030035,30030036,30030037,30030038,41002001,41002002,41002003,41002101,41002102,41002103,41003001,41003002,41003003,41003101,41003102,41003103</t>
-  </si>
-  <si>
-    <t>14635,2897,-4301</t>
-  </si>
-  <si>
-    <t>20003004</t>
-  </si>
-  <si>
-    <t>侍卫卡夫</t>
-  </si>
-  <si>
-    <t>30030009,30030010,30030011,30030012,30030013,30030014</t>
-  </si>
-  <si>
-    <t>14589,2905,-5444</t>
-  </si>
-  <si>
-    <t>20003005</t>
-  </si>
-  <si>
-    <t>冰雪之路引路人</t>
-  </si>
-  <si>
-    <t>30030023,30030024,30030025,30030026,30030027,30030028,30030029</t>
-  </si>
-  <si>
-    <t>13792,2904,-7159</t>
-  </si>
-  <si>
-    <t>20003006</t>
-  </si>
-  <si>
-    <t>15088,3459,-7501</t>
-  </si>
-  <si>
-    <t>20003007</t>
-  </si>
-  <si>
-    <t>20003008</t>
-  </si>
-  <si>
-    <t>20003009</t>
-  </si>
-  <si>
-    <t>魔穴守护人</t>
-  </si>
-  <si>
-    <t>30030030,30030031,30030032,30030033,30030034</t>
-  </si>
-  <si>
-    <t>15088,3459,-7500</t>
-  </si>
-  <si>
-    <t>20003010</t>
-  </si>
-  <si>
-    <t>瑞斯</t>
-  </si>
-  <si>
-    <t>30030015,30030016,30030017,30030018,30030019,30030020,30030021,30030022</t>
-  </si>
-  <si>
-    <t>14291,2901,-3398</t>
-  </si>
-  <si>
-    <t>20004001</t>
-  </si>
-  <si>
-    <t>17987,2913,-5746</t>
-  </si>
-  <si>
-    <t>20004002</t>
-  </si>
-  <si>
-    <t>19623,2904,-5818</t>
-  </si>
-  <si>
-    <t>20004003</t>
-  </si>
-  <si>
-    <t>镇长莫林</t>
-  </si>
-  <si>
-    <t>30040001,30040002,30040003,30040004,30040005,30040006,30040007,30040008,30040009,30040022,30040023,30040029,30040030,30040031,30040032,30040033</t>
-  </si>
-  <si>
-    <t>18788,2904,-5706</t>
-  </si>
-  <si>
-    <t>20004005</t>
-  </si>
-  <si>
-    <t>森林守护人</t>
-  </si>
-  <si>
-    <t>30040010,30040011,30040012,30040013,30040014,30040015,30040016</t>
-  </si>
-  <si>
-    <t>17060,2902,-7683</t>
-  </si>
-  <si>
-    <t>20004006</t>
-  </si>
-  <si>
-    <t>矿工哈登</t>
-  </si>
-  <si>
-    <t>30040017,30040018,30040019,30040020,30040021</t>
-  </si>
-  <si>
-    <t>25878,2895,-6669</t>
-  </si>
-  <si>
-    <t>20004007</t>
-  </si>
-  <si>
-    <t>20004008</t>
-  </si>
-  <si>
-    <t>20004009</t>
-  </si>
-  <si>
-    <t>峡谷护卫</t>
-  </si>
-  <si>
-    <t>30040024,30040025,30040026,30040027</t>
-  </si>
-  <si>
-    <t>14323,2904,-2681</t>
-  </si>
-  <si>
-    <t>20004010</t>
-  </si>
-  <si>
-    <t>裂谷护卫</t>
-  </si>
-  <si>
-    <t>30040028</t>
-  </si>
-  <si>
-    <t>23872,2904,-11240</t>
-  </si>
-  <si>
-    <t>20005001</t>
-  </si>
-  <si>
-    <t>-442,2888,-1611</t>
-  </si>
-  <si>
-    <t>20005002</t>
-  </si>
-  <si>
-    <t>912,2888,-1707</t>
-  </si>
-  <si>
-    <t>20005003</t>
-  </si>
-  <si>
-    <t>镇长乌尔</t>
-  </si>
-  <si>
-    <t>30050001,30050002,30050003,30050004,30050005,30050006,30050007,30050008,41004001,41004002,41004003,41004101,41004102,41004103,30050023</t>
-  </si>
-  <si>
-    <t>228,2941,-620</t>
-  </si>
-  <si>
-    <t>20005004</t>
-  </si>
-  <si>
-    <t>卡琳娜</t>
-  </si>
-  <si>
-    <t>30050009,30050010,30050011,30050012,30050013,30050014</t>
-  </si>
-  <si>
-    <t>14606,2880,-6651</t>
-  </si>
-  <si>
-    <t>20005005</t>
-  </si>
-  <si>
-    <t>卡尔</t>
-  </si>
-  <si>
-    <t>20005006</t>
-  </si>
-  <si>
-    <t>潜伏者·乌利兹</t>
-  </si>
-  <si>
-    <t>30050015,30050016,30050017,30050018,30050019,30050020,30050021,30050022</t>
-  </si>
-  <si>
-    <t>14149,2801,-6951</t>
-  </si>
-  <si>
-    <t>20005007</t>
-  </si>
-  <si>
-    <t>20005008</t>
-  </si>
-  <si>
-    <t>圣光城装备老板</t>
-  </si>
-  <si>
-    <t>NPC_Task_1</t>
-  </si>
-  <si>
-    <t>我这里的货物物美价廉!赶紧来看看有什么需要的,过段时间可不是这个价格呦！</t>
-  </si>
-  <si>
-    <t>圣光城药店老板</t>
-  </si>
-  <si>
-    <t>如果你在野外受伤了,赶紧来我这里买点药,保证喝完精神焕发</t>
-  </si>
-  <si>
-    <t>圣恩·帕托</t>
-  </si>
-  <si>
-    <t>在这个圣光城里,我时刻都感受到神圣的力量</t>
-  </si>
-  <si>
-    <t>圣恩·乌尔</t>
-  </si>
-  <si>
-    <t>我们不能在这样懦弱下去了,我们要复仇你明白嘛？</t>
-  </si>
-  <si>
-    <t>圣恩·瑞儿</t>
-  </si>
-  <si>
-    <t>听过国王马上要下令进攻恶魔军团了,我们应该做好准备！</t>
-  </si>
-  <si>
-    <t>别说话,这里需要安静！</t>
-  </si>
-  <si>
-    <t>小龟赛跑大使</t>
-  </si>
-  <si>
-    <t>-844,-771,-4836</t>
-  </si>
-  <si>
-    <t>小龟1号</t>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_1</t>
-  </si>
-  <si>
-    <t>-529,-765,-5248</t>
-  </si>
-  <si>
-    <t>我年轻力胜,获胜最终胜利的一定是我！</t>
-  </si>
-  <si>
-    <t>小龟2号</t>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_2</t>
-  </si>
-  <si>
-    <t>-205,-765,-5248</t>
-  </si>
-  <si>
-    <t>我是来自沙漠的龟,这么热的天获胜最终胜利的一定是我！</t>
-  </si>
-  <si>
-    <t>小龟3号</t>
-  </si>
-  <si>
-    <t>NPC_XiaoGui_3</t>
-  </si>
-  <si>
-    <t>92,-765,-5248</t>
-  </si>
-  <si>
-    <t>我拥有丰富的赛龟经验,获胜最终胜利的一定是我！</t>
-  </si>
-  <si>
-    <t>小龟一号选手</t>
-  </si>
-  <si>
-    <t>20000,5000,5000</t>
-  </si>
-  <si>
-    <t>-2.46;3.55;97.41</t>
-  </si>
-  <si>
-    <t>小龟二号选手</t>
-  </si>
-  <si>
-    <t>小龟三号选手</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>30000001</t>
-  </si>
-  <si>
-    <t>农场管理员</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanNongChang</t>
-  </si>
-  <si>
-    <t>-468,0,-2912</t>
-  </si>
-  <si>
-    <t>30000002</t>
-  </si>
-  <si>
-    <t>牧场管理员</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanMuChang</t>
-  </si>
-  <si>
-    <t>-1090,0,-1494</t>
-  </si>
-  <si>
-    <t>30000003</t>
-  </si>
-  <si>
-    <t>家园管家</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanGuanLi</t>
-  </si>
-  <si>
-    <t>3061,0,1224</t>
-  </si>
-  <si>
-    <t>30000004</t>
-  </si>
-  <si>
-    <t>家园公告牌</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanGongGao</t>
-  </si>
-  <si>
-    <t>1450,0,-3250</t>
-  </si>
-  <si>
-    <t>30000005</t>
-  </si>
-  <si>
-    <t>采购管理员</t>
-  </si>
-  <si>
-    <t>2963,0,-3074</t>
-  </si>
-  <si>
-    <t>30000006</t>
-  </si>
-  <si>
-    <t>家园存放员</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanPet</t>
-  </si>
-  <si>
-    <t>-1293,0,1892</t>
-  </si>
-  <si>
-    <t>30000007</t>
-  </si>
-  <si>
-    <t>家园士兵</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanShiBing</t>
-  </si>
-  <si>
-    <t>949,0,-4357</t>
-  </si>
-  <si>
-    <t>30000008</t>
-  </si>
-  <si>
-    <t>1532,0,-4366</t>
-  </si>
-  <si>
-    <t>30000009</t>
-  </si>
-  <si>
-    <t>美味大师</t>
-  </si>
-  <si>
-    <t>NPC_JiaYuanMeiWei</t>
-  </si>
-  <si>
-    <t>2845,0,-2586</t>
-  </si>
-  <si>
-    <t>30000010</t>
-  </si>
-  <si>
-    <t>家园宠物管理员</t>
-  </si>
-  <si>
-    <t>941,0,1588</t>
-  </si>
-  <si>
-    <t>30000011</t>
-  </si>
-  <si>
-    <t>装备宠物加锁</t>
-  </si>
-  <si>
-    <t>906,-423,-1201</t>
-  </si>
-  <si>
-    <t>30000013</t>
-  </si>
-  <si>
-    <t>家园商人</t>
-  </si>
-  <si>
-    <t>-1556,0,1277</t>
-  </si>
-  <si>
-    <t>30000014</t>
-  </si>
-  <si>
-    <t>藏宝图生活技能仓库</t>
-  </si>
-  <si>
-    <t>2350,0,1620</t>
-  </si>
-  <si>
-    <t>30000015</t>
-  </si>
-  <si>
-    <t>装备增幅</t>
-  </si>
-  <si>
-    <t>3439,0,804</t>
-  </si>
-  <si>
-    <t>30000016</t>
-  </si>
-  <si>
-    <t>家园觉醒大师</t>
-  </si>
-  <si>
-    <t>14,0,2133</t>
-  </si>
-  <si>
-    <t>40000001</t>
-  </si>
-  <si>
-    <t>战场招募·猎魔</t>
-  </si>
-  <si>
-    <t>-7655,0,-1313</t>
-  </si>
-  <si>
-    <t>40000002</t>
-  </si>
-  <si>
-    <t>战场招募·曙光</t>
-  </si>
-  <si>
-    <t>9256,0,-1330</t>
-  </si>
-  <si>
-    <t>40000003</t>
-  </si>
-  <si>
-    <t>神秘之门</t>
-  </si>
-  <si>
-    <t>NPC_ShenMiZhiMen</t>
-  </si>
-  <si>
-    <t>40000004</t>
-  </si>
-  <si>
-    <t>返回</t>
-  </si>
-  <si>
-    <t>0,0,-300</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>3443,350,4084</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2159,150 +2149,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2320,15 +2173,37 @@
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2349,198 +2224,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149723807489242"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14969328897976622"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2591,255 +2280,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2904,9 +2351,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2924,82 +2368,47 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 5" xfId="49"/>
-    <cellStyle name="常规 6" xfId="50"/>
+    <cellStyle name="常规 5" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3286,14 +2695,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
@@ -3321,13 +2730,13 @@
     <col min="26" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="4:4">
+    <row r="1" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:25">
+    <row r="3" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
@@ -3398,7 +2807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:25">
+    <row r="4" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
@@ -3467,7 +2876,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:25">
+    <row r="5" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>44</v>
       </c>
@@ -3536,7 +2945,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:18">
+    <row r="6" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="12">
         <v>10001</v>
       </c>
@@ -3559,9 +2968,9 @@
       <c r="N6" s="5">
         <v>0</v>
       </c>
-      <c r="R6" s="26"/>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R6" s="25"/>
+    </row>
+    <row r="7" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="12">
         <v>10002</v>
       </c>
@@ -3584,9 +2993,9 @@
       <c r="N7" s="5">
         <v>0</v>
       </c>
-      <c r="R7" s="26"/>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R7" s="25"/>
+    </row>
+    <row r="8" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="12">
         <v>10003</v>
       </c>
@@ -3609,9 +3018,9 @@
       <c r="N8" s="5">
         <v>0</v>
       </c>
-      <c r="R8" s="26"/>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:19">
+      <c r="R8" s="25"/>
+    </row>
+    <row r="9" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="12">
         <v>10004</v>
       </c>
@@ -3634,14 +3043,14 @@
       <c r="N9" s="5">
         <v>0</v>
       </c>
-      <c r="R9" s="26" t="s">
+      <c r="R9" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="S9" s="26" t="s">
+      <c r="S9" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:18">
+    <row r="10" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="13" t="s">
         <v>53</v>
       </c>
@@ -3663,7 +3072,7 @@
       <c r="L10" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="30" t="s">
+      <c r="M10" s="29" t="s">
         <v>56</v>
       </c>
       <c r="N10" s="5">
@@ -3671,7 +3080,7 @@
       </c>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:18">
+    <row r="11" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="13" t="s">
         <v>57</v>
       </c>
@@ -3693,7 +3102,7 @@
       <c r="L11" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="30" t="s">
+      <c r="M11" s="29" t="s">
         <v>60</v>
       </c>
       <c r="N11" s="5">
@@ -3701,7 +3110,7 @@
       </c>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:18">
+    <row r="12" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="13" t="s">
         <v>61</v>
       </c>
@@ -3721,7 +3130,7 @@
       <c r="L12" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="M12" s="30" t="s">
+      <c r="M12" s="29" t="s">
         <v>64</v>
       </c>
       <c r="N12" s="5">
@@ -3729,7 +3138,7 @@
       </c>
       <c r="R12" s="12"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:18">
+    <row r="13" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="13" t="s">
         <v>65</v>
       </c>
@@ -3749,7 +3158,7 @@
       <c r="L13" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M13" s="30" t="s">
+      <c r="M13" s="29" t="s">
         <v>68</v>
       </c>
       <c r="N13" s="5">
@@ -3757,7 +3166,7 @@
       </c>
       <c r="R13" s="12"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
+    <row r="14" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="14" t="s">
         <v>69</v>
       </c>
@@ -3779,7 +3188,7 @@
       <c r="L14" s="16">
         <v>20001007</v>
       </c>
-      <c r="M14" s="31" t="s">
+      <c r="M14" s="30" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="15">
@@ -3799,7 +3208,7 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:18">
+    <row r="15" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="13" t="s">
         <v>73</v>
       </c>
@@ -3818,7 +3227,7 @@
       <c r="L15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="31" t="s">
         <v>76</v>
       </c>
       <c r="N15" s="4">
@@ -3827,11 +3236,11 @@
       <c r="O15" s="4"/>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
-      <c r="R15" s="25" t="s">
+      <c r="R15" s="24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
+    <row r="16" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="14" t="s">
         <v>78</v>
       </c>
@@ -3853,7 +3262,7 @@
       <c r="L16" s="16">
         <v>20001024</v>
       </c>
-      <c r="M16" s="31" t="s">
+      <c r="M16" s="30" t="s">
         <v>80</v>
       </c>
       <c r="N16" s="15">
@@ -3873,7 +3282,7 @@
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:25">
+    <row r="17" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>81</v>
       </c>
@@ -3895,7 +3304,7 @@
       <c r="L17" s="16">
         <v>20001024</v>
       </c>
-      <c r="M17" s="31" t="s">
+      <c r="M17" s="30" t="s">
         <v>83</v>
       </c>
       <c r="N17" s="15">
@@ -3915,7 +3324,7 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:18">
+    <row r="18" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="13" t="s">
         <v>84</v>
       </c>
@@ -3935,7 +3344,7 @@
       <c r="L18" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="M18" s="30" t="s">
+      <c r="M18" s="29" t="s">
         <v>87</v>
       </c>
       <c r="N18" s="5">
@@ -3945,7 +3354,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:18">
+    <row r="19" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="13" t="s">
         <v>89</v>
       </c>
@@ -3965,7 +3374,7 @@
       <c r="L19" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="M19" s="30" t="s">
+      <c r="M19" s="29" t="s">
         <v>92</v>
       </c>
       <c r="N19" s="5">
@@ -3975,7 +3384,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:18">
+    <row r="20" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="13" t="s">
         <v>94</v>
       </c>
@@ -3995,7 +3404,7 @@
       <c r="L20" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M20" s="30" t="s">
+      <c r="M20" s="29" t="s">
         <v>97</v>
       </c>
       <c r="N20" s="5">
@@ -4003,7 +3412,7 @@
       </c>
       <c r="R20" s="12"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:18">
+    <row r="21" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="13" t="s">
         <v>98</v>
       </c>
@@ -4025,17 +3434,17 @@
       <c r="L21" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="32" t="s">
         <v>102</v>
       </c>
       <c r="N21" s="5">
         <v>90</v>
       </c>
-      <c r="R21" s="25" t="s">
+      <c r="R21" s="24" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:18">
+    <row r="22" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="13" t="s">
         <v>104</v>
       </c>
@@ -4057,17 +3466,17 @@
       <c r="L22" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="32" t="s">
         <v>108</v>
       </c>
       <c r="N22" s="5">
         <v>90</v>
       </c>
-      <c r="R22" s="25" t="s">
+      <c r="R22" s="24" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:18">
+    <row r="23" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="13" t="s">
         <v>110</v>
       </c>
@@ -4089,17 +3498,17 @@
       <c r="L23" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="M23" s="33" t="s">
+      <c r="M23" s="32" t="s">
         <v>114</v>
       </c>
       <c r="N23" s="5">
         <v>225</v>
       </c>
-      <c r="R23" s="25" t="s">
+      <c r="R23" s="24" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:18">
+    <row r="24" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="13" t="s">
         <v>116</v>
       </c>
@@ -4118,17 +3527,17 @@
       <c r="L24" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="32" t="s">
         <v>119</v>
       </c>
       <c r="N24" s="5">
         <v>0</v>
       </c>
-      <c r="R24" s="25" t="s">
+      <c r="R24" s="24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:18">
+    <row r="25" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="13" t="s">
         <v>121</v>
       </c>
@@ -4147,15 +3556,15 @@
       <c r="L25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="M25" s="33" t="s">
+      <c r="M25" s="32" t="s">
         <v>124</v>
       </c>
       <c r="N25" s="5">
         <v>-90</v>
       </c>
-      <c r="R25" s="25"/>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R25" s="24"/>
+    </row>
+    <row r="26" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="13" t="s">
         <v>125</v>
       </c>
@@ -4174,17 +3583,17 @@
       <c r="L26" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M26" s="33" t="s">
+      <c r="M26" s="32" t="s">
         <v>128</v>
       </c>
       <c r="N26" s="5">
         <v>180</v>
       </c>
-      <c r="R26" s="25" t="s">
+      <c r="R26" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="3:18">
+    <row r="27" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="13" t="s">
         <v>130</v>
       </c>
@@ -4206,17 +3615,17 @@
       <c r="L27" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="M27" s="33" t="s">
+      <c r="M27" s="32" t="s">
         <v>132</v>
       </c>
       <c r="N27" s="5">
         <v>180</v>
       </c>
-      <c r="R27" s="25" t="s">
+      <c r="R27" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:18">
+    <row r="28" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="13" t="s">
         <v>133</v>
       </c>
@@ -4238,15 +3647,15 @@
       <c r="L28" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M28" s="33" t="s">
+      <c r="M28" s="32" t="s">
         <v>136</v>
       </c>
       <c r="N28" s="5">
         <v>90</v>
       </c>
-      <c r="R28" s="25"/>
-    </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R28" s="24"/>
+    </row>
+    <row r="29" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="13" t="s">
         <v>137</v>
       </c>
@@ -4268,15 +3677,15 @@
       <c r="L29" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="M29" s="33" t="s">
+      <c r="M29" s="32" t="s">
         <v>140</v>
       </c>
       <c r="N29" s="5">
         <v>90</v>
       </c>
-      <c r="R29" s="25"/>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R29" s="24"/>
+    </row>
+    <row r="30" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="13" t="s">
         <v>141</v>
       </c>
@@ -4298,15 +3707,15 @@
       <c r="L30" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="M30" s="33" t="s">
+      <c r="M30" s="32" t="s">
         <v>144</v>
       </c>
       <c r="N30" s="5">
         <v>90</v>
       </c>
-      <c r="R30" s="25"/>
-    </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R30" s="24"/>
+    </row>
+    <row r="31" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="13" t="s">
         <v>145</v>
       </c>
@@ -4328,7 +3737,7 @@
       <c r="L31" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="M31" s="33" t="s">
+      <c r="M31" s="32" t="s">
         <v>149</v>
       </c>
       <c r="N31" s="5">
@@ -4336,7 +3745,7 @@
       </c>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:18">
+    <row r="32" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="13" t="s">
         <v>150</v>
       </c>
@@ -4358,17 +3767,17 @@
       <c r="L32" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="M32" s="33" t="s">
+      <c r="M32" s="32" t="s">
         <v>153</v>
       </c>
       <c r="N32" s="5">
         <v>-30</v>
       </c>
-      <c r="R32" s="25" t="s">
+      <c r="R32" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:18">
+    <row r="33" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="13" t="s">
         <v>154</v>
       </c>
@@ -4378,7 +3787,7 @@
       <c r="G33" s="4">
         <v>3</v>
       </c>
-      <c r="H33" s="34" t="s">
+      <c r="H33" s="33" t="s">
         <v>156</v>
       </c>
       <c r="I33" s="4">
@@ -4387,17 +3796,17 @@
       <c r="L33" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="M33" s="33" t="s">
+      <c r="M33" s="32" t="s">
         <v>158</v>
       </c>
       <c r="N33" s="5">
         <v>180</v>
       </c>
-      <c r="R33" s="25" t="s">
+      <c r="R33" s="24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:18">
+    <row r="34" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="13" t="s">
         <v>160</v>
       </c>
@@ -4413,17 +3822,17 @@
       <c r="L34" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M34" s="33" t="s">
+      <c r="M34" s="32" t="s">
         <v>162</v>
       </c>
       <c r="N34" s="5">
         <v>-30</v>
       </c>
-      <c r="R34" s="25" t="s">
+      <c r="R34" s="24" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:18">
+    <row r="35" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="13" t="s">
         <v>164</v>
       </c>
@@ -4445,17 +3854,17 @@
       <c r="L35" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="M35" s="33" t="s">
+      <c r="M35" s="32" t="s">
         <v>166</v>
       </c>
       <c r="N35" s="5">
         <v>-144</v>
       </c>
-      <c r="R35" s="25" t="s">
+      <c r="R35" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:18">
+    <row r="36" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="13" t="s">
         <v>168</v>
       </c>
@@ -4468,20 +3877,20 @@
       <c r="J36" s="4">
         <v>2000001</v>
       </c>
-      <c r="L36" s="25" t="s">
+      <c r="L36" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="M36" s="33" t="s">
+      <c r="M36" s="32" t="s">
         <v>170</v>
       </c>
       <c r="N36" s="5">
         <v>-180</v>
       </c>
-      <c r="R36" s="25" t="s">
+      <c r="R36" s="24" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:18">
+    <row r="37" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="13" t="s">
         <v>172</v>
       </c>
@@ -4494,20 +3903,20 @@
       <c r="J37" s="6">
         <v>2000002</v>
       </c>
-      <c r="L37" s="25" t="s">
+      <c r="L37" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="M37" s="33" t="s">
+      <c r="M37" s="32" t="s">
         <v>174</v>
       </c>
       <c r="N37" s="5">
         <v>90</v>
       </c>
-      <c r="R37" s="25" t="s">
+      <c r="R37" s="24" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:18">
+    <row r="38" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="13" t="s">
         <v>176</v>
       </c>
@@ -4517,21 +3926,21 @@
       <c r="G38" s="4">
         <v>1027</v>
       </c>
-      <c r="L38" s="25" t="s">
+      <c r="L38" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="M38" s="33" t="s">
+      <c r="M38" s="32" t="s">
         <v>178</v>
       </c>
       <c r="N38" s="5">
         <v>90</v>
       </c>
-      <c r="P38" s="24"/>
-      <c r="R38" s="25" t="s">
+      <c r="P38" s="23"/>
+      <c r="R38" s="24" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:18">
+    <row r="39" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="13" t="s">
         <v>180</v>
       </c>
@@ -4541,21 +3950,21 @@
       <c r="G39" s="4">
         <v>1028</v>
       </c>
-      <c r="L39" s="25" t="s">
+      <c r="L39" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="M39" s="33" t="s">
+      <c r="M39" s="32" t="s">
         <v>182</v>
       </c>
       <c r="N39" s="5">
         <v>129</v>
       </c>
-      <c r="P39" s="24"/>
-      <c r="R39" s="25" t="s">
+      <c r="P39" s="23"/>
+      <c r="R39" s="24" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:18">
+    <row r="40" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="13" t="s">
         <v>183</v>
       </c>
@@ -4577,15 +3986,15 @@
       <c r="L40" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M40" s="33" t="s">
+      <c r="M40" s="32" t="s">
         <v>185</v>
       </c>
       <c r="N40" s="5">
         <v>180</v>
       </c>
-      <c r="R40" s="25"/>
-    </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R40" s="24"/>
+    </row>
+    <row r="41" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="13" t="s">
         <v>186</v>
       </c>
@@ -4605,7 +4014,7 @@
       <c r="L41" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="M41" s="33" t="s">
+      <c r="M41" s="32" t="s">
         <v>189</v>
       </c>
       <c r="N41" s="5">
@@ -4613,7 +4022,7 @@
       </c>
       <c r="R41" s="12"/>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:18">
+    <row r="42" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="13" t="s">
         <v>190</v>
       </c>
@@ -4633,7 +4042,7 @@
       <c r="L42" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="M42" s="33" t="s">
+      <c r="M42" s="32" t="s">
         <v>193</v>
       </c>
       <c r="N42" s="5">
@@ -4643,7 +4052,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:18">
+    <row r="43" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="13" t="s">
         <v>195</v>
       </c>
@@ -4663,7 +4072,7 @@
       <c r="L43" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="M43" s="33" t="s">
+      <c r="M43" s="32" t="s">
         <v>197</v>
       </c>
       <c r="N43" s="5">
@@ -4673,7 +4082,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:18">
+    <row r="44" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="13" t="s">
         <v>199</v>
       </c>
@@ -4696,7 +4105,7 @@
       <c r="L44" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="M44" s="33" t="s">
+      <c r="M44" s="32" t="s">
         <v>202</v>
       </c>
       <c r="N44" s="5">
@@ -4706,7 +4115,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:18">
+    <row r="45" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="13" t="s">
         <v>204</v>
       </c>
@@ -4728,7 +4137,7 @@
       <c r="L45" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M45" s="30" t="s">
+      <c r="M45" s="29" t="s">
         <v>206</v>
       </c>
       <c r="N45" s="5">
@@ -4736,7 +4145,7 @@
       </c>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:18">
+    <row r="46" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="13" t="s">
         <v>207</v>
       </c>
@@ -4758,7 +4167,7 @@
       <c r="L46" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M46" s="30" t="s">
+      <c r="M46" s="29" t="s">
         <v>209</v>
       </c>
       <c r="N46" s="5">
@@ -4768,7 +4177,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:18">
+    <row r="47" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="13" t="s">
         <v>211</v>
       </c>
@@ -4790,7 +4199,7 @@
       <c r="L47" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M47" s="30" t="s">
+      <c r="M47" s="29" t="s">
         <v>213</v>
       </c>
       <c r="N47" s="5">
@@ -4800,7 +4209,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:18">
+    <row r="48" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="13" t="s">
         <v>215</v>
       </c>
@@ -4822,7 +4231,7 @@
       <c r="L48" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M48" s="30" t="s">
+      <c r="M48" s="29" t="s">
         <v>217</v>
       </c>
       <c r="N48" s="5">
@@ -4830,7 +4239,7 @@
       </c>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:18">
+    <row r="49" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="13" t="s">
         <v>218</v>
       </c>
@@ -4852,7 +4261,7 @@
       <c r="L49" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M49" s="30" t="s">
+      <c r="M49" s="29" t="s">
         <v>220</v>
       </c>
       <c r="N49" s="5">
@@ -4862,7 +4271,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="3:18">
+    <row r="50" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="13" t="s">
         <v>222</v>
       </c>
@@ -4872,20 +4281,20 @@
       <c r="G50" s="4">
         <v>1050</v>
       </c>
-      <c r="L50" s="25" t="s">
+      <c r="L50" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="M50" s="33" t="s">
+      <c r="M50" s="32" t="s">
         <v>225</v>
       </c>
       <c r="N50" s="5">
         <v>90</v>
       </c>
-      <c r="R50" s="25" t="s">
+      <c r="R50" s="24" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:18">
+    <row r="51" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="13" t="s">
         <v>227</v>
       </c>
@@ -4907,7 +4316,7 @@
       <c r="L51" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M51" s="30" t="s">
+      <c r="M51" s="29" t="s">
         <v>229</v>
       </c>
       <c r="N51" s="5">
@@ -4915,15 +4324,15 @@
       </c>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="52" spans="1:25" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
-      <c r="C52" s="13" t="s">
-        <v>230</v>
+      <c r="C52" s="37" t="s">
+        <v>518</v>
       </c>
       <c r="D52" s="5"/>
-      <c r="E52" s="12" t="s">
-        <v>231</v>
+      <c r="E52" s="36" t="s">
+        <v>517</v>
       </c>
       <c r="F52" s="12">
         <v>6000101</v>
@@ -4940,13 +4349,13 @@
       <c r="J52" s="6"/>
       <c r="K52" s="3"/>
       <c r="L52" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="M52" s="30" t="s">
-        <v>232</v>
+        <v>107</v>
+      </c>
+      <c r="M52" s="35" t="s">
+        <v>519</v>
       </c>
       <c r="N52" s="5">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="O52" s="5"/>
       <c r="R52" s="12"/>
@@ -4956,15 +4365,15 @@
       <c r="X52" s="5"/>
       <c r="Y52" s="5"/>
     </row>
-    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="53" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F53" s="12">
         <v>0</v>
@@ -4983,8 +4392,8 @@
       <c r="L53" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M53" s="30" t="s">
-        <v>235</v>
+      <c r="M53" s="29" t="s">
+        <v>232</v>
       </c>
       <c r="N53" s="5">
         <v>90</v>
@@ -4997,15 +4406,15 @@
       <c r="X53" s="5"/>
       <c r="Y53" s="5"/>
     </row>
-    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="54" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F54" s="12">
         <v>0</v>
@@ -5024,15 +4433,15 @@
       <c r="L54" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M54" s="30" t="s">
-        <v>238</v>
+      <c r="M54" s="29" t="s">
+        <v>235</v>
       </c>
       <c r="N54" s="5">
         <v>-140</v>
       </c>
       <c r="O54" s="5"/>
       <c r="R54" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
@@ -5040,15 +4449,15 @@
       <c r="X54" s="5"/>
       <c r="Y54" s="5"/>
     </row>
-    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="55" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F55" s="12">
         <v>0</v>
@@ -5067,8 +4476,8 @@
       <c r="L55" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M55" s="30" t="s">
-        <v>242</v>
+      <c r="M55" s="29" t="s">
+        <v>239</v>
       </c>
       <c r="N55" s="5">
         <v>90</v>
@@ -5081,15 +4490,15 @@
       <c r="X55" s="5"/>
       <c r="Y55" s="5"/>
     </row>
-    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="56" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F56" s="12">
         <v>0</v>
@@ -5106,10 +4515,10 @@
       <c r="J56" s="6"/>
       <c r="K56" s="3"/>
       <c r="L56" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="M56" s="30" t="s">
-        <v>246</v>
+        <v>242</v>
+      </c>
+      <c r="M56" s="29" t="s">
+        <v>243</v>
       </c>
       <c r="N56" s="5">
         <v>-180</v>
@@ -5122,15 +4531,15 @@
       <c r="X56" s="5"/>
       <c r="Y56" s="5"/>
     </row>
-    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="57" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="12" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F57" s="12">
         <v>0</v>
@@ -5149,8 +4558,8 @@
       <c r="L57" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="M57" s="30" t="s">
-        <v>249</v>
+      <c r="M57" s="29" t="s">
+        <v>246</v>
       </c>
       <c r="N57" s="5">
         <v>30</v>
@@ -5163,15 +4572,15 @@
       <c r="X57" s="5"/>
       <c r="Y57" s="5"/>
     </row>
-    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="58" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="13" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F58" s="12">
         <v>0</v>
@@ -5190,8 +4599,8 @@
       <c r="L58" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="M58" s="30" t="s">
-        <v>252</v>
+      <c r="M58" s="29" t="s">
+        <v>249</v>
       </c>
       <c r="N58" s="5">
         <v>130</v>
@@ -5204,12 +4613,12 @@
       <c r="X58" s="5"/>
       <c r="Y58" s="5"/>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:18">
+    <row r="59" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="13" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F59" s="12">
         <v>10001101</v>
@@ -5226,20 +4635,20 @@
       <c r="L59" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="M59" s="30" t="s">
-        <v>255</v>
+      <c r="M59" s="29" t="s">
+        <v>252</v>
       </c>
       <c r="N59" s="5">
         <v>60</v>
       </c>
       <c r="R59" s="12"/>
     </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:18">
+    <row r="60" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="13">
         <v>20001002</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F60" s="12">
         <v>10001201</v>
@@ -5257,46 +4666,46 @@
         <v>59</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N60" s="5">
         <v>-45</v>
       </c>
       <c r="R60" s="12"/>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:18">
+    <row r="61" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="12">
         <v>20001003</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F61" s="12"/>
       <c r="H61" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>147</v>
       </c>
       <c r="L61" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N61" s="5">
         <v>180</v>
       </c>
-      <c r="R61" s="26" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R61" s="25" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="13">
         <v>20001004</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F62" s="12"/>
       <c r="H62" s="6" t="s">
@@ -5306,24 +4715,24 @@
         <v>147</v>
       </c>
       <c r="L62" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="M62" s="30" t="s">
-        <v>264</v>
+        <v>260</v>
+      </c>
+      <c r="M62" s="29" t="s">
+        <v>261</v>
       </c>
       <c r="N62" s="5">
         <v>90</v>
       </c>
-      <c r="R62" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R62" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="12">
         <v>20001005</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F63" s="12"/>
       <c r="H63" s="6" t="s">
@@ -5333,24 +4742,24 @@
         <v>147</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N63" s="5">
         <v>-45</v>
       </c>
-      <c r="R63" s="26" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R63" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="12">
         <v>20001006</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F64" s="12"/>
       <c r="H64" s="6" t="s">
@@ -5360,28 +4769,28 @@
         <v>147</v>
       </c>
       <c r="L64" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="M64" s="30" t="s">
-        <v>269</v>
+        <v>260</v>
+      </c>
+      <c r="M64" s="29" t="s">
+        <v>266</v>
       </c>
       <c r="N64" s="5">
         <v>45</v>
       </c>
-      <c r="R64" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R64" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="65" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="12">
         <v>20001007</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F65" s="12"/>
       <c r="H65" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>147</v>
@@ -5389,22 +4798,22 @@
       <c r="L65" s="12">
         <v>20001007</v>
       </c>
-      <c r="M65" s="30" t="s">
-        <v>273</v>
+      <c r="M65" s="29" t="s">
+        <v>270</v>
       </c>
       <c r="N65" s="5">
         <v>150</v>
       </c>
-      <c r="R65" s="26" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R65" s="25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="66" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="12">
         <v>20001008</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F66" s="12"/>
       <c r="H66" s="6" t="s">
@@ -5416,26 +4825,26 @@
       <c r="L66" s="12">
         <v>20001008</v>
       </c>
-      <c r="M66" s="30" t="s">
-        <v>276</v>
+      <c r="M66" s="29" t="s">
+        <v>273</v>
       </c>
       <c r="N66" s="5">
         <v>-155</v>
       </c>
-      <c r="R66" s="26" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R66" s="25" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="12">
         <v>20001009</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F67" s="12"/>
       <c r="H67" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>147</v>
@@ -5443,22 +4852,22 @@
       <c r="L67" s="12">
         <v>20001009</v>
       </c>
-      <c r="M67" s="30" t="s">
-        <v>280</v>
+      <c r="M67" s="29" t="s">
+        <v>277</v>
       </c>
       <c r="N67" s="5">
         <v>35</v>
       </c>
-      <c r="R67" s="26" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R67" s="25" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="12">
         <v>20001010</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F68" s="12"/>
       <c r="H68" s="6" t="s">
@@ -5470,26 +4879,26 @@
       <c r="L68" s="12">
         <v>20001010</v>
       </c>
-      <c r="M68" s="34" t="s">
-        <v>283</v>
+      <c r="M68" s="33" t="s">
+        <v>280</v>
       </c>
       <c r="N68" s="5">
         <v>180</v>
       </c>
-      <c r="R68" s="26" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R68" s="25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="69" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="12">
         <v>20001011</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F69" s="12"/>
       <c r="H69" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>147</v>
@@ -5498,25 +4907,25 @@
         <v>20001011</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N69" s="5">
         <v>-180</v>
       </c>
-      <c r="R69" s="26" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R69" s="25" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="12">
         <v>20001012</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F70" s="12"/>
       <c r="H70" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>147</v>
@@ -5525,25 +4934,25 @@
         <v>20001012</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N70" s="5">
         <v>80</v>
       </c>
-      <c r="R70" s="26" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R70" s="25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="71" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="12">
         <v>20001013</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F71" s="12"/>
       <c r="H71" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>147</v>
@@ -5552,25 +4961,25 @@
         <v>20001013</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N71" s="5">
         <v>180</v>
       </c>
-      <c r="R71" s="26" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R71" s="25" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="12">
         <v>20001014</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F72" s="12"/>
       <c r="H72" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>147</v>
@@ -5579,25 +4988,25 @@
         <v>20001014</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N72" s="5">
         <v>180</v>
       </c>
-      <c r="R72" s="26" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R72" s="25" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="12">
         <v>20001015</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F73" s="12"/>
       <c r="H73" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>147</v>
@@ -5606,21 +5015,21 @@
         <v>20001015</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N73" s="5">
         <v>128</v>
       </c>
-      <c r="R73" s="26" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R73" s="25" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="74" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="12">
         <v>20001016</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F74" s="12"/>
       <c r="H74" s="6" t="s">
@@ -5633,25 +5042,25 @@
         <v>20001016</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N74" s="5">
         <v>180</v>
       </c>
-      <c r="R74" s="26" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R74" s="25" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="75" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="12">
         <v>20001017</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F75" s="12"/>
       <c r="H75" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>147</v>
@@ -5660,21 +5069,21 @@
         <v>20001017</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N75" s="5">
         <v>120</v>
       </c>
-      <c r="R75" s="26" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R75" s="25" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="12">
         <v>20001018</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F76" s="12"/>
       <c r="H76" s="6" t="s">
@@ -5684,29 +5093,29 @@
         <v>147</v>
       </c>
       <c r="J76" s="4"/>
-      <c r="L76" s="25">
+      <c r="L76" s="24">
         <v>0</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N76" s="5">
         <v>180</v>
       </c>
-      <c r="R76" s="26" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R76" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="77" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="12">
         <v>20001019</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F77" s="12"/>
       <c r="H77" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>147</v>
@@ -5715,21 +5124,21 @@
         <v>20001019</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="N77" s="5">
         <v>-180</v>
       </c>
-      <c r="R77" s="26" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="78" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R77" s="25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="78" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" s="12">
         <v>20001020</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F78" s="12"/>
       <c r="H78" s="6" t="s">
@@ -5742,21 +5151,21 @@
         <v>20001019</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N78" s="5">
         <v>180</v>
       </c>
-      <c r="R78" s="26" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R78" s="25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="79" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="12">
         <v>20001021</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F79" s="12"/>
       <c r="H79" s="6" t="s">
@@ -5769,25 +5178,25 @@
         <v>20001021</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N79" s="5">
         <v>-180</v>
       </c>
-      <c r="R79" s="26" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R79" s="25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="80" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="12">
         <v>20001022</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F80" s="12"/>
       <c r="H80" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>147</v>
@@ -5796,21 +5205,21 @@
         <v>20001022</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N80" s="5">
         <v>-106</v>
       </c>
-      <c r="R80" s="26" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R80" s="25" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C81" s="12">
         <v>20001023</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F81" s="12"/>
       <c r="G81" s="4">
@@ -5826,14 +5235,14 @@
         <v>20001023</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N81" s="5">
         <v>180</v>
       </c>
       <c r="R81" s="12"/>
     </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:18">
+    <row r="82" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="12">
         <v>20001024</v>
       </c>
@@ -5851,16 +5260,16 @@
         <v>20001024</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="N82" s="5">
         <v>-152</v>
       </c>
       <c r="R82" s="12"/>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:18">
+    <row r="83" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C83" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>54</v>
@@ -5881,19 +5290,19 @@
         <v>20001001</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N83" s="5">
         <v>-147</v>
       </c>
       <c r="R83" s="12"/>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:18">
+    <row r="84" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="13" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F84" s="12">
         <v>10002201</v>
@@ -5911,50 +5320,50 @@
         <v>20001002</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="N84" s="5">
         <v>-129</v>
       </c>
       <c r="R84" s="12"/>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:18">
+    <row r="85" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F85" s="12"/>
       <c r="H85" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L85" s="25">
+      <c r="L85" s="24">
         <v>20001007</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="N85" s="5">
         <v>-131</v>
       </c>
-      <c r="R85" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R85" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="13" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F86" s="12"/>
       <c r="H86" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>147</v>
@@ -5963,52 +5372,52 @@
         <v>20001005</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N86" s="5">
         <v>180</v>
       </c>
-      <c r="R86" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R86" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="13" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F87" s="12"/>
       <c r="H87" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="25">
+      <c r="L87" s="24">
         <v>20001009</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="N87" s="5">
         <v>180</v>
       </c>
-      <c r="R87" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R87" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="13" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F88" s="12"/>
       <c r="H88" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>147</v>
@@ -6017,21 +5426,21 @@
         <v>20001005</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="N88" s="5">
         <v>180</v>
       </c>
-      <c r="R88" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R88" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="13" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F89" s="12"/>
       <c r="H89" s="6" t="s">
@@ -6041,24 +5450,24 @@
         <v>147</v>
       </c>
       <c r="L89" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N89" s="5">
         <v>180</v>
       </c>
-      <c r="R89" s="26" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R89" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="13" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F90" s="12"/>
       <c r="H90" s="6" t="s">
@@ -6068,21 +5477,21 @@
         <v>147</v>
       </c>
       <c r="L90" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N90" s="5">
         <v>180</v>
       </c>
-      <c r="R90" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R90" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="91" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="13" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>184</v>
@@ -6094,22 +5503,22 @@
       <c r="I91" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L91" s="25">
+      <c r="L91" s="24">
         <v>20001017</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="N91" s="5">
         <v>27</v>
       </c>
-      <c r="R91" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R91" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="13" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>54</v>
@@ -6130,19 +5539,19 @@
         <v>20001001</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="N92" s="5">
         <v>123</v>
       </c>
       <c r="R92" s="12"/>
     </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:18">
+    <row r="93" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F93" s="12">
         <v>10003201</v>
@@ -6160,100 +5569,100 @@
         <v>20001002</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="N93" s="5">
         <v>45</v>
       </c>
       <c r="R93" s="12"/>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:18">
+    <row r="94" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="13" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F94" s="12"/>
       <c r="H94" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L94" s="25">
+      <c r="L94" s="24">
         <v>20001007</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="N94" s="5">
         <v>90</v>
       </c>
-      <c r="R94" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R94" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="13" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F95" s="12"/>
       <c r="H95" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L95" s="25">
+      <c r="L95" s="24">
         <v>20001011</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N95" s="5">
         <v>180</v>
       </c>
-      <c r="R95" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R95" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="13" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F96" s="12"/>
       <c r="H96" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L96" s="25">
+      <c r="L96" s="24">
         <v>20001017</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="N96" s="5">
         <v>95</v>
       </c>
-      <c r="R96" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R96" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="13" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F97" s="12"/>
       <c r="H97" s="6" t="s">
@@ -6266,21 +5675,21 @@
         <v>20001005</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="N97" s="5">
         <v>-70</v>
       </c>
-      <c r="R97" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R97" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="13" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F98" s="12"/>
       <c r="H98" s="6" t="s">
@@ -6290,24 +5699,24 @@
         <v>147</v>
       </c>
       <c r="L98" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N98" s="5">
         <v>180</v>
       </c>
-      <c r="R98" s="26" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R98" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="13" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F99" s="12"/>
       <c r="H99" s="6" t="s">
@@ -6317,28 +5726,28 @@
         <v>147</v>
       </c>
       <c r="L99" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N99" s="5">
         <v>180</v>
       </c>
-      <c r="R99" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R99" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="13" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F100" s="12"/>
       <c r="H100" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>147</v>
@@ -6347,45 +5756,45 @@
         <v>20001008</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="N100" s="5">
         <v>-70</v>
       </c>
-      <c r="R100" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R100" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="13" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F101" s="12"/>
       <c r="H101" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I101" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L101" s="25">
+      <c r="L101" s="24">
         <v>20001011</v>
       </c>
       <c r="M101" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="N101" s="5">
         <v>-180</v>
       </c>
-      <c r="R101" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R101" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="13" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E102" s="12" t="s">
         <v>54</v>
@@ -6406,19 +5815,19 @@
         <v>20001001</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="N102" s="5">
         <v>35</v>
       </c>
       <c r="R102" s="12"/>
     </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:18">
+    <row r="103" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="13" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F103" s="12">
         <v>10004201</v>
@@ -6436,100 +5845,100 @@
         <v>20001002</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="N103" s="5">
         <v>-41</v>
       </c>
       <c r="R103" s="12"/>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:18">
+    <row r="104" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F104" s="12"/>
       <c r="H104" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L104" s="24">
+        <v>20001007</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="N104" s="5">
+        <v>0</v>
+      </c>
+      <c r="R104" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="105" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C105" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="E105" s="12" t="s">
         <v>385</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="L104" s="25">
-        <v>20001007</v>
-      </c>
-      <c r="M104" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="N104" s="5">
-        <v>0</v>
-      </c>
-      <c r="R104" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:18">
-      <c r="C105" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>388</v>
       </c>
       <c r="F105" s="12"/>
       <c r="H105" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I105" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L105" s="25">
+      <c r="L105" s="24">
         <v>20001017</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N105" s="5">
         <v>101</v>
       </c>
-      <c r="R105" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R105" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="106" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F106" s="12"/>
       <c r="H106" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L106" s="25">
+      <c r="L106" s="24">
         <v>20001013</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="N106" s="5">
         <v>-3</v>
       </c>
-      <c r="R106" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R106" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="107" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F107" s="12"/>
       <c r="H107" s="6" t="s">
@@ -6539,24 +5948,24 @@
         <v>147</v>
       </c>
       <c r="L107" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N107" s="5">
         <v>180</v>
       </c>
-      <c r="R107" s="26" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R107" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F108" s="12"/>
       <c r="H108" s="6" t="s">
@@ -6566,75 +5975,75 @@
         <v>147</v>
       </c>
       <c r="L108" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N108" s="5">
         <v>180</v>
       </c>
-      <c r="R108" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R108" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="109" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="13" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F109" s="12"/>
       <c r="H109" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L109" s="25">
+      <c r="L109" s="24">
         <v>20001015</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="N109" s="5">
         <v>-180</v>
       </c>
-      <c r="R109" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R109" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="13" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F110" s="12"/>
       <c r="H110" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L110" s="25">
+      <c r="L110" s="24">
         <v>20001015</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="N110" s="5">
         <v>83</v>
       </c>
-      <c r="R110" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R110" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="111" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>54</v>
@@ -6655,19 +6064,19 @@
         <v>20001001</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N111" s="5">
         <v>51</v>
       </c>
       <c r="R111" s="12"/>
     </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:18">
+    <row r="112" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F112" s="12">
         <v>10005201</v>
@@ -6685,73 +6094,73 @@
         <v>20001002</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N112" s="5">
         <v>-44</v>
       </c>
       <c r="R112" s="12"/>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:18">
+    <row r="113" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F113" s="12"/>
       <c r="H113" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I113" s="6" t="s">
         <v>147</v>
       </c>
       <c r="L113" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="N113" s="5">
         <v>180</v>
       </c>
-      <c r="R113" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R113" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="114" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F114" s="12"/>
       <c r="H114" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L114" s="25">
+      <c r="L114" s="24">
         <v>20001012</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N114" s="5">
         <v>92</v>
       </c>
-      <c r="R114" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R114" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="13" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F115" s="12"/>
       <c r="H115" s="6" t="s">
@@ -6760,52 +6169,52 @@
       <c r="I115" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L115" s="25">
+      <c r="L115" s="24">
         <v>20001015</v>
       </c>
       <c r="M115" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N115" s="5">
         <v>180</v>
       </c>
-      <c r="R115" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R115" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="116" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="13" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F116" s="12"/>
       <c r="H116" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I116" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L116" s="25">
+      <c r="L116" s="24">
         <v>20001013</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="N116" s="5">
         <v>145</v>
       </c>
-      <c r="R116" s="26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R116" s="25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F117" s="12"/>
       <c r="H117" s="6" t="s">
@@ -6815,24 +6224,24 @@
         <v>147</v>
       </c>
       <c r="L117" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M117" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N117" s="5">
         <v>180</v>
       </c>
-      <c r="R117" s="26" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R117" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F118" s="12"/>
       <c r="H118" s="6" t="s">
@@ -6842,24 +6251,24 @@
         <v>147</v>
       </c>
       <c r="L118" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N118" s="5">
         <v>180</v>
       </c>
-      <c r="R118" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R118" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="119" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="12">
         <v>20099001</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F119" s="12"/>
       <c r="H119" s="6" t="s">
@@ -6868,25 +6277,25 @@
       <c r="I119" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L119" s="25" t="s">
-        <v>426</v>
+      <c r="L119" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N119" s="5">
         <v>180</v>
       </c>
-      <c r="R119" s="26" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R119" s="25" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="120" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="12">
         <v>20099002</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F120" s="12"/>
       <c r="H120" s="6" t="s">
@@ -6895,25 +6304,25 @@
       <c r="I120" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L120" s="25" t="s">
-        <v>426</v>
+      <c r="L120" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N120" s="5">
         <v>180</v>
       </c>
-      <c r="R120" s="26" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R120" s="25" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="121" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="12">
         <v>20099003</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F121" s="12"/>
       <c r="H121" s="6" t="s">
@@ -6922,25 +6331,25 @@
       <c r="I121" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L121" s="25" t="s">
-        <v>426</v>
+      <c r="L121" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N121" s="5">
         <v>180</v>
       </c>
-      <c r="R121" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R121" s="25" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="122" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="12">
         <v>20099004</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F122" s="12"/>
       <c r="H122" s="6" t="s">
@@ -6949,25 +6358,25 @@
       <c r="I122" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L122" s="25" t="s">
-        <v>426</v>
+      <c r="L122" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N122" s="5">
         <v>180</v>
       </c>
-      <c r="R122" s="26" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R122" s="25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="123" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="12">
         <v>20099005</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F123" s="12"/>
       <c r="H123" s="6" t="s">
@@ -6976,25 +6385,25 @@
       <c r="I123" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L123" s="25" t="s">
-        <v>426</v>
+      <c r="L123" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N123" s="5">
         <v>180</v>
       </c>
-      <c r="R123" s="26" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R123" s="25" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="124" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C124" s="12">
         <v>20099006</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F124" s="12"/>
       <c r="H124" s="6" t="s">
@@ -7007,116 +6416,116 @@
         <v>20001005</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N124" s="5">
         <v>180</v>
       </c>
-      <c r="R124" s="26" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R124" s="25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="125" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="12">
         <v>20099007</v>
       </c>
-      <c r="E125" s="27" t="s">
-        <v>437</v>
-      </c>
-      <c r="F125" s="27"/>
+      <c r="E125" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="F125" s="26"/>
       <c r="G125" s="4">
         <v>1057</v>
       </c>
       <c r="L125" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M125" s="30" t="s">
-        <v>438</v>
+      <c r="M125" s="29" t="s">
+        <v>435</v>
       </c>
       <c r="N125" s="5">
         <v>180</v>
       </c>
-      <c r="R125" s="28"/>
-    </row>
-    <row r="126" ht="20.1" customHeight="1" spans="3:18">
+      <c r="R125" s="27"/>
+    </row>
+    <row r="126" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C126" s="12">
         <v>20099008</v>
       </c>
-      <c r="E126" s="27" t="s">
+      <c r="E126" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="F126" s="26"/>
+      <c r="L126" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="M126" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="N126" s="5">
+        <v>0</v>
+      </c>
+      <c r="R126" s="27" t="s">
         <v>439</v>
       </c>
-      <c r="F126" s="27"/>
-      <c r="L126" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="M126" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="N126" s="5">
-        <v>0</v>
-      </c>
-      <c r="R126" s="28" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="127" ht="20.1" customHeight="1" spans="3:18">
+    </row>
+    <row r="127" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C127" s="12">
         <v>20099009</v>
       </c>
-      <c r="E127" s="27" t="s">
+      <c r="E127" s="26" t="s">
+        <v>440</v>
+      </c>
+      <c r="F127" s="26"/>
+      <c r="L127" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="M127" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="N127" s="5">
+        <v>0</v>
+      </c>
+      <c r="R127" s="27" t="s">
         <v>443</v>
       </c>
-      <c r="F127" s="27"/>
-      <c r="L127" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="M127" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="N127" s="5">
-        <v>0</v>
-      </c>
-      <c r="R127" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="128" ht="20.1" customHeight="1" spans="3:18">
+    </row>
+    <row r="128" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="12">
         <v>20099010</v>
       </c>
-      <c r="E128" s="27" t="s">
+      <c r="E128" s="26" t="s">
+        <v>444</v>
+      </c>
+      <c r="F128" s="26"/>
+      <c r="L128" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="M128" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="N128" s="5">
+        <v>0</v>
+      </c>
+      <c r="R128" s="27" t="s">
         <v>447</v>
       </c>
-      <c r="F128" s="27"/>
-      <c r="L128" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="M128" s="30" t="s">
-        <v>449</v>
-      </c>
-      <c r="N128" s="5">
-        <v>0</v>
-      </c>
-      <c r="R128" s="28" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="129" ht="20.1" customHeight="1" spans="3:18">
+    </row>
+    <row r="129" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C129" s="12">
         <v>20099011</v>
       </c>
-      <c r="E129" s="27" t="s">
-        <v>451</v>
-      </c>
-      <c r="F129" s="27"/>
+      <c r="E129" s="26" t="s">
+        <v>448</v>
+      </c>
+      <c r="F129" s="26"/>
       <c r="J129" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="L129" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="M129" s="30" t="s">
-        <v>441</v>
+        <v>437</v>
+      </c>
+      <c r="M129" s="29" t="s">
+        <v>438</v>
       </c>
       <c r="N129" s="5">
         <v>0</v>
@@ -7124,27 +6533,27 @@
       <c r="O129" s="5">
         <v>13</v>
       </c>
-      <c r="P129" s="35" t="s">
-        <v>453</v>
-      </c>
-      <c r="R129" s="28"/>
-    </row>
-    <row r="130" ht="20.1" customHeight="1" spans="3:18">
+      <c r="P129" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="R129" s="27"/>
+    </row>
+    <row r="130" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="12">
         <v>20099012</v>
       </c>
-      <c r="E130" s="27" t="s">
-        <v>454</v>
-      </c>
-      <c r="F130" s="27"/>
+      <c r="E130" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="F130" s="26"/>
       <c r="J130" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="L130" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="M130" s="30" t="s">
-        <v>445</v>
+        <v>441</v>
+      </c>
+      <c r="M130" s="29" t="s">
+        <v>442</v>
       </c>
       <c r="N130" s="5">
         <v>0</v>
@@ -7152,27 +6561,27 @@
       <c r="O130" s="5">
         <v>13</v>
       </c>
-      <c r="P130" s="35" t="s">
-        <v>453</v>
-      </c>
-      <c r="R130" s="28"/>
-    </row>
-    <row r="131" ht="20.1" customHeight="1" spans="3:18">
+      <c r="P130" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="R130" s="27"/>
+    </row>
+    <row r="131" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="12">
         <v>20099013</v>
       </c>
-      <c r="E131" s="27" t="s">
-        <v>455</v>
-      </c>
-      <c r="F131" s="27"/>
+      <c r="E131" s="26" t="s">
+        <v>452</v>
+      </c>
+      <c r="F131" s="26"/>
       <c r="J131" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="L131" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="M131" s="30" t="s">
-        <v>449</v>
+        <v>445</v>
+      </c>
+      <c r="M131" s="29" t="s">
+        <v>446</v>
       </c>
       <c r="N131" s="5">
         <v>0</v>
@@ -7180,22 +6589,22 @@
       <c r="O131" s="5">
         <v>13</v>
       </c>
-      <c r="P131" s="35" t="s">
+      <c r="P131" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="R131" s="27"/>
+    </row>
+    <row r="132" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="R131" s="28"/>
-    </row>
-    <row r="132" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
-      <c r="A132" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="13" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D132" s="5"/>
-      <c r="E132" s="29" t="s">
-        <v>458</v>
+      <c r="E132" s="28" t="s">
+        <v>455</v>
       </c>
       <c r="F132" s="5">
         <v>300001</v>
@@ -7211,33 +6620,33 @@
       </c>
       <c r="J132" s="4"/>
       <c r="K132" s="3"/>
-      <c r="L132" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="M132" s="33" t="s">
-        <v>460</v>
+      <c r="L132" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="M132" s="32" t="s">
+        <v>457</v>
       </c>
       <c r="N132" s="5">
         <v>0</v>
       </c>
       <c r="O132" s="5"/>
-      <c r="P132" s="24"/>
-      <c r="R132" s="25"/>
+      <c r="P132" s="23"/>
+      <c r="R132" s="24"/>
       <c r="U132" s="5"/>
       <c r="V132" s="5"/>
       <c r="W132" s="5"/>
       <c r="X132" s="5"/>
       <c r="Y132" s="5"/>
     </row>
-    <row r="133" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="133" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="13" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D133" s="5"/>
-      <c r="E133" s="29" t="s">
-        <v>462</v>
+      <c r="E133" s="28" t="s">
+        <v>459</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="4">
@@ -7251,33 +6660,33 @@
       </c>
       <c r="J133" s="4"/>
       <c r="K133" s="3"/>
-      <c r="L133" s="29" t="s">
-        <v>463</v>
-      </c>
-      <c r="M133" s="33" t="s">
-        <v>464</v>
+      <c r="L133" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="M133" s="32" t="s">
+        <v>461</v>
       </c>
       <c r="N133" s="5">
         <v>90</v>
       </c>
       <c r="O133" s="5"/>
-      <c r="P133" s="24"/>
-      <c r="R133" s="25"/>
+      <c r="P133" s="23"/>
+      <c r="R133" s="24"/>
       <c r="U133" s="5"/>
       <c r="V133" s="5"/>
       <c r="W133" s="5"/>
       <c r="X133" s="5"/>
       <c r="Y133" s="5"/>
     </row>
-    <row r="134" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="134" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="13" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D134" s="5"/>
-      <c r="E134" s="29" t="s">
-        <v>466</v>
+      <c r="E134" s="28" t="s">
+        <v>463</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="4">
@@ -7291,32 +6700,32 @@
       </c>
       <c r="J134" s="4"/>
       <c r="K134" s="3"/>
-      <c r="L134" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="M134" s="33" t="s">
-        <v>468</v>
+      <c r="L134" s="28" t="s">
+        <v>464</v>
+      </c>
+      <c r="M134" s="32" t="s">
+        <v>465</v>
       </c>
       <c r="N134" s="5">
         <v>210</v>
       </c>
       <c r="O134" s="5"/>
-      <c r="R134" s="25"/>
+      <c r="R134" s="24"/>
       <c r="U134" s="5"/>
       <c r="V134" s="5"/>
       <c r="W134" s="5"/>
       <c r="X134" s="5"/>
       <c r="Y134" s="5"/>
     </row>
-    <row r="135" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="135" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D135" s="5"/>
-      <c r="E135" s="29" t="s">
-        <v>470</v>
+      <c r="E135" s="28" t="s">
+        <v>467</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="4">
@@ -7330,29 +6739,29 @@
       </c>
       <c r="J135" s="4"/>
       <c r="K135" s="3"/>
-      <c r="L135" s="29" t="s">
-        <v>471</v>
-      </c>
-      <c r="M135" s="24" t="s">
-        <v>472</v>
+      <c r="L135" s="28" t="s">
+        <v>468</v>
+      </c>
+      <c r="M135" s="23" t="s">
+        <v>469</v>
       </c>
       <c r="N135" s="5">
         <v>0</v>
       </c>
       <c r="O135" s="5"/>
-      <c r="R135" s="25"/>
+      <c r="R135" s="24"/>
       <c r="U135" s="5"/>
       <c r="V135" s="5"/>
       <c r="W135" s="5"/>
       <c r="X135" s="5"/>
       <c r="Y135" s="5"/>
     </row>
-    <row r="136" ht="20.1" customHeight="1" spans="3:14">
+    <row r="136" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="13" t="s">
-        <v>473</v>
-      </c>
-      <c r="E136" s="29" t="s">
-        <v>474</v>
+        <v>470</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>471</v>
       </c>
       <c r="G136" s="4">
         <v>1036</v>
@@ -7364,22 +6773,22 @@
         <v>0</v>
       </c>
       <c r="J136" s="4"/>
-      <c r="L136" s="29" t="s">
+      <c r="L136" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="M136" s="24" t="s">
-        <v>475</v>
+      <c r="M136" s="23" t="s">
+        <v>472</v>
       </c>
       <c r="N136" s="5">
         <v>-100</v>
       </c>
     </row>
-    <row r="137" ht="20.1" customHeight="1" spans="3:14">
+    <row r="137" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="E137" s="29" t="s">
-        <v>477</v>
+        <v>473</v>
+      </c>
+      <c r="E137" s="28" t="s">
+        <v>474</v>
       </c>
       <c r="G137" s="4">
         <v>1032</v>
@@ -7391,50 +6800,50 @@
         <v>0</v>
       </c>
       <c r="J137" s="4"/>
-      <c r="L137" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="M137" s="33" t="s">
-        <v>479</v>
+      <c r="L137" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="M137" s="32" t="s">
+        <v>476</v>
       </c>
       <c r="N137" s="5">
         <v>123</v>
       </c>
     </row>
-    <row r="138" ht="20.1" customHeight="1" spans="3:14">
+    <row r="138" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="G138" s="4">
+        <v>0</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0</v>
+      </c>
+      <c r="I138" s="4">
+        <v>0</v>
+      </c>
+      <c r="J138" s="4"/>
+      <c r="L138" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="M138" s="23" t="s">
         <v>480</v>
-      </c>
-      <c r="E138" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="G138" s="4">
-        <v>0</v>
-      </c>
-      <c r="H138" s="4">
-        <v>0</v>
-      </c>
-      <c r="I138" s="4">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4"/>
-      <c r="L138" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="M138" s="24" t="s">
-        <v>483</v>
       </c>
       <c r="N138" s="5">
         <v>90</v>
       </c>
     </row>
-    <row r="139" ht="20.1" customHeight="1" spans="3:14">
+    <row r="139" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="E139" s="29" t="s">
         <v>481</v>
       </c>
+      <c r="E139" s="28" t="s">
+        <v>478</v>
+      </c>
       <c r="G139" s="4">
         <v>0</v>
       </c>
@@ -7445,22 +6854,22 @@
         <v>0</v>
       </c>
       <c r="J139" s="4"/>
-      <c r="L139" s="29" t="s">
+      <c r="L139" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="M139" s="23" t="s">
         <v>482</v>
-      </c>
-      <c r="M139" s="24" t="s">
-        <v>485</v>
       </c>
       <c r="N139" s="5">
         <v>270</v>
       </c>
     </row>
-    <row r="140" ht="20.1" customHeight="1" spans="3:14">
+    <row r="140" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="E140" s="29" t="s">
-        <v>487</v>
+        <v>483</v>
+      </c>
+      <c r="E140" s="28" t="s">
+        <v>484</v>
       </c>
       <c r="G140" s="4">
         <v>1037</v>
@@ -7472,22 +6881,22 @@
         <v>0</v>
       </c>
       <c r="J140" s="4"/>
-      <c r="L140" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="M140" s="24" t="s">
-        <v>489</v>
+      <c r="L140" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="M140" s="23" t="s">
+        <v>486</v>
       </c>
       <c r="N140" s="5">
         <v>-90</v>
       </c>
     </row>
-    <row r="141" ht="20.1" customHeight="1" spans="3:14">
+    <row r="141" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="E141" s="29" t="s">
-        <v>491</v>
+        <v>487</v>
+      </c>
+      <c r="E141" s="28" t="s">
+        <v>488</v>
       </c>
       <c r="G141" s="4">
         <v>1038</v>
@@ -7499,22 +6908,22 @@
         <v>0</v>
       </c>
       <c r="J141" s="4"/>
-      <c r="L141" s="29" t="s">
+      <c r="L141" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="M141" s="24" t="s">
-        <v>492</v>
+      <c r="M141" s="23" t="s">
+        <v>489</v>
       </c>
       <c r="N141" s="5">
         <v>-150</v>
       </c>
     </row>
-    <row r="142" ht="20.1" customHeight="1" spans="3:15">
+    <row r="142" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E142" s="29" t="s">
-        <v>494</v>
+        <v>490</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>491</v>
       </c>
       <c r="G142" s="4">
         <v>1047</v>
@@ -7526,26 +6935,26 @@
         <v>0</v>
       </c>
       <c r="J142" s="4"/>
-      <c r="L142" s="29" t="s">
+      <c r="L142" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="M142" s="32" t="s">
-        <v>495</v>
+      <c r="M142" s="31" t="s">
+        <v>492</v>
       </c>
       <c r="N142" s="4">
         <v>90</v>
       </c>
       <c r="O142" s="4"/>
     </row>
-    <row r="143" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="143" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="13" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D143" s="5"/>
-      <c r="E143" s="29" t="s">
-        <v>497</v>
+      <c r="E143" s="28" t="s">
+        <v>494</v>
       </c>
       <c r="F143" s="5">
         <v>400001</v>
@@ -7561,11 +6970,11 @@
       </c>
       <c r="J143" s="4"/>
       <c r="K143" s="3"/>
-      <c r="L143" s="29" t="s">
+      <c r="L143" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="M143" s="33" t="s">
-        <v>498</v>
+      <c r="M143" s="32" t="s">
+        <v>495</v>
       </c>
       <c r="N143" s="5">
         <v>110</v>
@@ -7577,12 +6986,12 @@
       <c r="X143" s="5"/>
       <c r="Y143" s="5"/>
     </row>
-    <row r="144" ht="20.1" customHeight="1" spans="3:14">
+    <row r="144" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C144" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="E144" s="29" t="s">
-        <v>500</v>
+        <v>496</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>497</v>
       </c>
       <c r="G144" s="4">
         <v>1049</v>
@@ -7594,22 +7003,22 @@
         <v>0</v>
       </c>
       <c r="J144" s="4"/>
-      <c r="L144" s="29" t="s">
+      <c r="L144" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="M144" s="33" t="s">
-        <v>501</v>
+      <c r="M144" s="32" t="s">
+        <v>498</v>
       </c>
       <c r="N144" s="5">
         <v>173</v>
       </c>
     </row>
-    <row r="145" ht="20.1" customHeight="1" spans="3:14">
+    <row r="145" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C145" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="E145" s="29" t="s">
-        <v>503</v>
+        <v>499</v>
+      </c>
+      <c r="E145" s="28" t="s">
+        <v>500</v>
       </c>
       <c r="G145" s="4">
         <v>1051</v>
@@ -7621,22 +7030,22 @@
         <v>0</v>
       </c>
       <c r="J145" s="4"/>
-      <c r="L145" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="M145" s="33" t="s">
-        <v>504</v>
+      <c r="L145" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="M145" s="32" t="s">
+        <v>501</v>
       </c>
       <c r="N145" s="5">
         <v>235</v>
       </c>
     </row>
-    <row r="146" ht="20.1" customHeight="1" spans="3:14">
+    <row r="146" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="E146" s="29" t="s">
-        <v>506</v>
+        <v>502</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>503</v>
       </c>
       <c r="G146" s="4">
         <v>1053</v>
@@ -7648,22 +7057,22 @@
         <v>0</v>
       </c>
       <c r="J146" s="4"/>
-      <c r="L146" s="29" t="s">
+      <c r="L146" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M146" s="33" t="s">
-        <v>507</v>
+      <c r="M146" s="32" t="s">
+        <v>504</v>
       </c>
       <c r="N146" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="147" ht="20.1" customHeight="1" spans="3:14">
+    <row r="147" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="E147" s="29" t="s">
-        <v>509</v>
+        <v>505</v>
+      </c>
+      <c r="E147" s="28" t="s">
+        <v>506</v>
       </c>
       <c r="G147" s="4">
         <v>1054</v>
@@ -7675,22 +7084,22 @@
         <v>0</v>
       </c>
       <c r="J147" s="4"/>
-      <c r="L147" s="29" t="s">
+      <c r="L147" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M147" s="33" t="s">
-        <v>510</v>
+      <c r="M147" s="32" t="s">
+        <v>507</v>
       </c>
       <c r="N147" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="148" ht="20.1" customHeight="1" spans="3:14">
+    <row r="148" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="E148" s="29" t="s">
-        <v>512</v>
+        <v>508</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>509</v>
       </c>
       <c r="G148" s="4">
         <v>1054</v>
@@ -7702,22 +7111,22 @@
         <v>0</v>
       </c>
       <c r="J148" s="4"/>
-      <c r="L148" s="29" t="s">
+      <c r="L148" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M148" s="33" t="s">
-        <v>513</v>
+      <c r="M148" s="32" t="s">
+        <v>510</v>
       </c>
       <c r="N148" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="149" ht="20.1" customHeight="1" spans="3:14">
+    <row r="149" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C149" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="E149" s="29" t="s">
-        <v>515</v>
+        <v>511</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>512</v>
       </c>
       <c r="G149" s="4">
         <v>10</v>
@@ -7729,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="J149" s="4"/>
-      <c r="L149" s="29" t="s">
-        <v>516</v>
-      </c>
-      <c r="M149" s="33" t="s">
+      <c r="L149" s="28" t="s">
         <v>513</v>
+      </c>
+      <c r="M149" s="32" t="s">
+        <v>510</v>
       </c>
       <c r="N149" s="5">
         <v>175</v>
       </c>
     </row>
-    <row r="150" ht="20.1" customHeight="1" spans="3:14">
+    <row r="150" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C150" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="E150" s="29" t="s">
-        <v>518</v>
+        <v>514</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>515</v>
       </c>
       <c r="G150" s="4">
         <v>19</v>
@@ -7756,33 +7165,33 @@
         <v>0</v>
       </c>
       <c r="J150" s="4"/>
-      <c r="L150" s="29" t="s">
+      <c r="L150" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="M150" s="33" t="s">
-        <v>519</v>
+      <c r="M150" s="32" t="s">
+        <v>516</v>
       </c>
       <c r="N150" s="5">
         <v>180</v>
       </c>
     </row>
-    <row r="151" ht="20.1" customHeight="1"/>
-    <row r="152" ht="20.1" customHeight="1"/>
-    <row r="153" ht="20.1" customHeight="1"/>
-    <row r="154" ht="20.1" customHeight="1"/>
-    <row r="155" ht="20.1" customHeight="1"/>
-    <row r="156" ht="20.1" customHeight="1"/>
-    <row r="157" ht="20.1" customHeight="1"/>
-    <row r="158" ht="20.1" customHeight="1"/>
-    <row r="159" ht="20.1" customHeight="1"/>
-    <row r="160" ht="20.1" customHeight="1"/>
-    <row r="161" ht="20.1" customHeight="1"/>
-    <row r="162" ht="20.1" customHeight="1"/>
-    <row r="163" ht="20.1" customHeight="1"/>
+    <row r="151" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8B30A1-ED41-406E-AC07-2389F065CBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE37F107-28E6-4B04-B682-3CF3ABF17E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31335" yWindow="1920" windowWidth="21600" windowHeight="11700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="700">
   <si>
     <t>#</t>
   </si>
@@ -2499,9 +2499,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>Village Chief Ulf</t>
-  </si>
-  <si>
     <t>Wounded Soldier</t>
   </si>
   <si>
@@ -2556,28 +2553,10 @@
     <t>Guard Kave</t>
   </si>
   <si>
-    <t>Ice Road Guide</t>
-  </si>
-  <si>
-    <t>Reese</t>
-  </si>
-  <si>
-    <t>Miner Haden</t>
-  </si>
-  <si>
-    <t>Canyon Guard</t>
-  </si>
-  <si>
     <t>Rift Guard</t>
   </si>
   <si>
     <t>Mayor Ulf</t>
-  </si>
-  <si>
-    <t>Karina</t>
-  </si>
-  <si>
-    <t>Stalker Uliz</t>
   </si>
   <si>
     <t>Equip Shop</t>
@@ -2668,6 +2647,38 @@
   </si>
   <si>
     <t>Awakening Master</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reese</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice Road Guide</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cave Guardian</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miner Haden</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Canyon Guard</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stalker Uliz</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Karina</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Village Chief Ulf</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -5556,7 +5567,7 @@
         <v>292</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G59" s="4">
         <v>10001101</v>
@@ -5591,7 +5602,7 @@
         <v>294</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G60" s="4">
         <v>10001201</v>
@@ -5626,7 +5637,7 @@
         <v>296</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="G61" s="4"/>
       <c r="I61" s="6" t="s">
@@ -5660,7 +5671,7 @@
         <v>301</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G62" s="4"/>
       <c r="I62" s="6" t="s">
@@ -5694,7 +5705,7 @@
         <v>306</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G63" s="4"/>
       <c r="I63" s="6" t="s">
@@ -5728,7 +5739,7 @@
         <v>306</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G64" s="4"/>
       <c r="I64" s="6" t="s">
@@ -5864,7 +5875,7 @@
         <v>330</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G68" s="4"/>
       <c r="I68" s="6" t="s">
@@ -5898,7 +5909,7 @@
         <v>334</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G69" s="4"/>
       <c r="I69" s="6" t="s">
@@ -5932,7 +5943,7 @@
         <v>339</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G70" s="4"/>
       <c r="I70" s="6" t="s">
@@ -6068,7 +6079,7 @@
         <v>362</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G74" s="4"/>
       <c r="I74" s="6" t="s">
@@ -6102,7 +6113,7 @@
         <v>365</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G75" s="4"/>
       <c r="I75" s="6" t="s">
@@ -6136,7 +6147,7 @@
         <v>371</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G76" s="4"/>
       <c r="I76" s="6" t="s">
@@ -6171,7 +6182,7 @@
         <v>374</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G77" s="4"/>
       <c r="I77" s="6" t="s">
@@ -6205,7 +6216,7 @@
         <v>379</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G78" s="4"/>
       <c r="I78" s="6" t="s">
@@ -6239,7 +6250,7 @@
         <v>382</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G79" s="4"/>
       <c r="I79" s="6" t="s">
@@ -6273,7 +6284,7 @@
         <v>384</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G80" s="4"/>
       <c r="I80" s="6" t="s">
@@ -6307,7 +6318,7 @@
         <v>389</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4">
@@ -6370,7 +6381,7 @@
         <v>62</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G83" s="4">
         <v>10002101</v>
@@ -6405,7 +6416,7 @@
         <v>294</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G84" s="4">
         <v>10002201</v>
@@ -6474,7 +6485,7 @@
         <v>401</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="G86" s="4"/>
       <c r="I86" s="6" t="s">
@@ -6576,7 +6587,7 @@
         <v>306</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G89" s="4"/>
       <c r="I89" s="6" t="s">
@@ -6610,7 +6621,7 @@
         <v>306</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G90" s="4"/>
       <c r="I90" s="6" t="s">
@@ -6678,7 +6689,7 @@
         <v>62</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G92" s="4">
         <v>10003101</v>
@@ -6713,7 +6724,7 @@
         <v>294</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G93" s="4">
         <v>10003201</v>
@@ -6748,7 +6759,7 @@
         <v>423</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G94" s="4"/>
       <c r="I94" s="6" t="s">
@@ -6782,7 +6793,7 @@
         <v>427</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G95" s="4"/>
       <c r="I95" s="6" t="s">
@@ -6816,7 +6827,7 @@
         <v>431</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="G96" s="4"/>
       <c r="I96" s="6" t="s">
@@ -6884,7 +6895,7 @@
         <v>306</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G98" s="4"/>
       <c r="I98" s="6" t="s">
@@ -6918,7 +6929,7 @@
         <v>306</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G99" s="4"/>
       <c r="I99" s="6" t="s">
@@ -6952,7 +6963,7 @@
         <v>439</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
       <c r="G100" s="4"/>
       <c r="I100" s="6" t="s">
@@ -6986,7 +6997,7 @@
         <v>443</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="G101" s="4"/>
       <c r="I101" s="6" t="s">
@@ -7020,7 +7031,7 @@
         <v>62</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G102" s="4">
         <v>10004101</v>
@@ -7055,7 +7066,7 @@
         <v>294</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G103" s="4">
         <v>10004201</v>
@@ -7158,7 +7169,7 @@
         <v>460</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="G106" s="4"/>
       <c r="I106" s="6" t="s">
@@ -7192,7 +7203,7 @@
         <v>306</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G107" s="4"/>
       <c r="I107" s="6" t="s">
@@ -7226,7 +7237,7 @@
         <v>306</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G108" s="4"/>
       <c r="I108" s="6" t="s">
@@ -7260,7 +7271,7 @@
         <v>466</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="G109" s="4"/>
       <c r="I109" s="6" t="s">
@@ -7294,7 +7305,7 @@
         <v>470</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="G110" s="4"/>
       <c r="I110" s="6" t="s">
@@ -7328,7 +7339,7 @@
         <v>62</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G111" s="4">
         <v>10005101</v>
@@ -7363,7 +7374,7 @@
         <v>294</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G112" s="4">
         <v>10005201</v>
@@ -7398,7 +7409,7 @@
         <v>478</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G113" s="4"/>
       <c r="I113" s="6" t="s">
@@ -7432,7 +7443,7 @@
         <v>482</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>668</v>
+        <v>698</v>
       </c>
       <c r="G114" s="4"/>
       <c r="I114" s="6" t="s">
@@ -7500,7 +7511,7 @@
         <v>489</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="G116" s="4"/>
       <c r="I116" s="6" t="s">
@@ -7534,7 +7545,7 @@
         <v>306</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G117" s="4"/>
       <c r="I117" s="6" t="s">
@@ -7568,7 +7579,7 @@
         <v>306</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G118" s="4"/>
       <c r="I118" s="6" t="s">
@@ -7602,7 +7613,7 @@
         <v>494</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G119" s="4"/>
       <c r="I119" s="6" t="s">
@@ -7636,7 +7647,7 @@
         <v>498</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G120" s="4"/>
       <c r="I120" s="6" t="s">
@@ -7670,7 +7681,7 @@
         <v>501</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="G121" s="4"/>
       <c r="I121" s="6" t="s">
@@ -7704,7 +7715,7 @@
         <v>504</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="G122" s="4"/>
       <c r="I122" s="6" t="s">
@@ -7738,7 +7749,7 @@
         <v>507</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="G123" s="4"/>
       <c r="I123" s="6" t="s">
@@ -7772,7 +7783,7 @@
         <v>306</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="G124" s="4"/>
       <c r="I124" s="6" t="s">
@@ -7806,7 +7817,7 @@
         <v>512</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4">
@@ -7833,7 +7844,7 @@
         <v>514</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="G126" s="4"/>
       <c r="M126" s="11" t="s">
@@ -7861,7 +7872,7 @@
         <v>519</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="G127" s="4"/>
       <c r="M127" s="11" t="s">
@@ -7889,7 +7900,7 @@
         <v>524</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="G128" s="4"/>
       <c r="M128" s="11" t="s">
@@ -7917,7 +7928,7 @@
         <v>529</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="G129" s="4"/>
       <c r="K129" s="6" t="s">
@@ -7950,7 +7961,7 @@
         <v>532</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="G130" s="4"/>
       <c r="K130" s="6" t="s">
@@ -7983,7 +7994,7 @@
         <v>533</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="G131" s="4"/>
       <c r="K131" s="6" t="s">
@@ -8021,7 +8032,7 @@
         <v>536</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="G132" s="5">
         <v>300001</v>
@@ -8068,7 +8079,7 @@
         <v>540</v>
       </c>
       <c r="F133" s="28" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="4">
@@ -8113,7 +8124,7 @@
         <v>544</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4">
@@ -8157,7 +8168,7 @@
         <v>548</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="4">
@@ -8198,7 +8209,7 @@
         <v>552</v>
       </c>
       <c r="F136" s="28" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="H136" s="4">
         <v>1036</v>
@@ -8230,7 +8241,7 @@
         <v>555</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="H137" s="4">
         <v>1032</v>
@@ -8326,7 +8337,7 @@
         <v>566</v>
       </c>
       <c r="F140" s="28" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="H140" s="4">
         <v>1037</v>
@@ -8358,7 +8369,7 @@
         <v>570</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="H141" s="4">
         <v>1038</v>
@@ -8390,7 +8401,7 @@
         <v>573</v>
       </c>
       <c r="F142" s="28" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="H142" s="4">
         <v>1047</v>
@@ -8468,7 +8479,7 @@
         <v>580</v>
       </c>
       <c r="F144" s="28" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="H144" s="4">
         <v>1049</v>
@@ -8500,7 +8511,7 @@
         <v>583</v>
       </c>
       <c r="F145" s="28" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="H145" s="4">
         <v>1051</v>
@@ -8532,7 +8543,7 @@
         <v>586</v>
       </c>
       <c r="F146" s="28" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="H146" s="4">
         <v>1053</v>
@@ -8561,10 +8572,10 @@
         <v>588</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="F147" s="28" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="H147" s="4">
         <v>1054</v>
@@ -8596,7 +8607,7 @@
         <v>591</v>
       </c>
       <c r="F148" s="28" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="H148" s="4">
         <v>1054</v>
@@ -8628,7 +8639,7 @@
         <v>594</v>
       </c>
       <c r="F149" s="28" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="H149" s="4">
         <v>10</v>

--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85E558E-868F-4EBB-A244-3E660FD66472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -48,6 +42,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -58,6 +53,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为0：</t>
@@ -66,6 +62,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -77,6 +74,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为1：</t>
@@ -85,6 +83,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -100,6 +99,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>NPC类型为2：</t>
@@ -108,6 +108,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -119,6 +120,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>商店类型为3：</t>
@@ -127,6 +129,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -134,13 +137,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="1">
+    <comment ref="H3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -149,6 +153,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -169,14 +174,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>作者:
 0:</t>
@@ -186,6 +191,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>表示不拉近</t>
@@ -194,7 +200,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 1</t>
@@ -203,19 +209,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：表示拉近</t>
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -224,6 +232,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -233,7 +242,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID,</t>
         </r>
@@ -241,6 +250,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>文件存储在</t>
@@ -249,7 +259,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>UI</t>
         </r>
@@ -257,6 +267,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>文件夹下</t>
@@ -265,7 +276,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -273,6 +284,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>多个音效用</t>
@@ -281,7 +293,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>;</t>
         </r>
@@ -289,6 +301,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>号间隔</t>
@@ -297,7 +310,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -305,6 +318,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>将会随机播放一个</t>
@@ -313,7 +327,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -321,6 +335,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>如果有概率不播放就写成</t>
@@ -329,7 +344,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">100;0  </t>
         </r>
@@ -337,6 +352,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>就表示</t>
@@ -345,7 +361,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>50%</t>
         </r>
@@ -353,6 +369,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>概率播放</t>
@@ -361,7 +378,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>100</t>
         </r>
@@ -369,19 +386,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>号音效</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -390,6 +409,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -399,7 +419,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">NPC
 </t>
@@ -408,6 +428,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>例如</t>
@@ -416,7 +437,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">:10;20 </t>
         </r>
@@ -424,6 +445,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>表示</t>
@@ -432,7 +454,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> 10-20</t>
         </r>
@@ -440,19 +462,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>级会出现</t>
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="Z3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -461,6 +485,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -474,13 +499,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0">
+    <comment ref="AA3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -489,6 +515,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -504,13 +531,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB4" authorId="0">
+    <comment ref="AB4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -519,6 +547,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -535,7 +564,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="707">
   <si>
     <t>#</t>
   </si>
@@ -2632,19 +2661,42 @@
   </si>
   <si>
     <t>0,0,-300</t>
+  </si>
+  <si>
+    <t>20000044</t>
+  </si>
+  <si>
+    <t>奇珍商人</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4107,615,6097</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare Curio Merchant</t>
+  </si>
+  <si>
+    <t>冒险家，我的宝物可都是独一无二的，千万别错过呀！</t>
+  </si>
+  <si>
+    <t>Adventurer, my treasures are one-of-a-kind—don’t miss out!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘿，勇士！这些奇珍异宝，只有你才配拥有！</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hey, hero! These exotic treasures are only worthy of someone like you!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2656,12 +2708,14 @@
       <sz val="9"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2669,12 +2723,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2682,6 +2738,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2689,6 +2746,7 @@
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2696,156 +2754,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2853,26 +2776,35 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2893,198 +2825,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14966277047029"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14963225196081423"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3135,255 +2881,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3450,9 +2954,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3468,82 +2969,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 5" xfId="49"/>
-    <cellStyle name="常规 6" xfId="50"/>
+    <cellStyle name="常规 5" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3830,14 +3290,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AB163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB164"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
@@ -3868,8 +3328,8 @@
     <col min="29" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="3:28">
+    <row r="1" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
@@ -3883,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:28">
+    <row r="3" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
@@ -3963,7 +3423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:28">
+    <row r="4" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
@@ -4041,7 +3501,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:28">
+    <row r="5" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
@@ -4119,7 +3579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:28">
+    <row r="6" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="14">
         <v>10001</v>
       </c>
@@ -4149,7 +3609,7 @@
       <c r="T6" s="16"/>
       <c r="V6" s="16"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:28">
+    <row r="7" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="14">
         <v>10002</v>
       </c>
@@ -4179,7 +3639,7 @@
       <c r="T7" s="16"/>
       <c r="V7" s="16"/>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:28">
+    <row r="8" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="14">
         <v>10003</v>
       </c>
@@ -4209,7 +3669,7 @@
       <c r="T8" s="16"/>
       <c r="V8" s="16"/>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:28">
+    <row r="9" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="14">
         <v>10004</v>
       </c>
@@ -4248,7 +3708,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:28">
+    <row r="10" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="17" t="s">
         <v>62</v>
       </c>
@@ -4273,7 +3733,7 @@
       <c r="M10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="N10" s="30" t="s">
+      <c r="N10" s="29" t="s">
         <v>66</v>
       </c>
       <c r="O10" s="5">
@@ -4283,7 +3743,7 @@
       <c r="T10" s="16"/>
       <c r="V10" s="16"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:28">
+    <row r="11" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="17" t="s">
         <v>67</v>
       </c>
@@ -4308,7 +3768,7 @@
       <c r="M11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N11" s="30" t="s">
+      <c r="N11" s="29" t="s">
         <v>71</v>
       </c>
       <c r="O11" s="5">
@@ -4318,7 +3778,7 @@
       <c r="T11" s="16"/>
       <c r="V11" s="16"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:28">
+    <row r="12" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="17" t="s">
         <v>72</v>
       </c>
@@ -4341,7 +3801,7 @@
       <c r="M12" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="29" t="s">
         <v>76</v>
       </c>
       <c r="O12" s="5">
@@ -4351,7 +3811,7 @@
       <c r="T12" s="16"/>
       <c r="V12" s="16"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:28">
+    <row r="13" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="17" t="s">
         <v>77</v>
       </c>
@@ -4374,7 +3834,7 @@
       <c r="M13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="30" t="s">
+      <c r="N13" s="29" t="s">
         <v>81</v>
       </c>
       <c r="O13" s="5">
@@ -4384,7 +3844,7 @@
       <c r="T13" s="16"/>
       <c r="V13" s="16"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="14" spans="3:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="18" t="s">
         <v>82</v>
       </c>
@@ -4409,7 +3869,7 @@
       <c r="M14" s="20">
         <v>20001007</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="30" t="s">
         <v>85</v>
       </c>
       <c r="O14" s="19">
@@ -4433,7 +3893,7 @@
       <c r="AA14" s="19"/>
       <c r="AB14" s="19"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:28">
+    <row r="15" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="17" t="s">
         <v>88</v>
       </c>
@@ -4455,7 +3915,7 @@
       <c r="M15" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="N15" s="32" t="s">
+      <c r="N15" s="31" t="s">
         <v>92</v>
       </c>
       <c r="O15" s="4">
@@ -4464,7 +3924,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
-      <c r="S15" s="25" t="s">
+      <c r="S15" s="24" t="s">
         <v>93</v>
       </c>
       <c r="T15" s="16" t="s">
@@ -4472,7 +3932,7 @@
       </c>
       <c r="V15" s="16"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="16" spans="3:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="18" t="s">
         <v>95</v>
       </c>
@@ -4497,7 +3957,7 @@
       <c r="M16" s="20">
         <v>20001024</v>
       </c>
-      <c r="N16" s="31" t="s">
+      <c r="N16" s="30" t="s">
         <v>98</v>
       </c>
       <c r="O16" s="19">
@@ -4521,7 +3981,7 @@
       <c r="AA16" s="19"/>
       <c r="AB16" s="19"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:28">
+    <row r="17" spans="3:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="18" t="s">
         <v>99</v>
       </c>
@@ -4546,7 +4006,7 @@
       <c r="M17" s="20">
         <v>20001024</v>
       </c>
-      <c r="N17" s="31" t="s">
+      <c r="N17" s="30" t="s">
         <v>102</v>
       </c>
       <c r="O17" s="19">
@@ -4570,7 +4030,7 @@
       <c r="AA17" s="19"/>
       <c r="AB17" s="19"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:28">
+    <row r="18" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="17" t="s">
         <v>103</v>
       </c>
@@ -4593,7 +4053,7 @@
       <c r="M18" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="N18" s="30" t="s">
+      <c r="N18" s="29" t="s">
         <v>107</v>
       </c>
       <c r="O18" s="5">
@@ -4607,7 +4067,7 @@
       </c>
       <c r="V18" s="16"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:28">
+    <row r="19" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="17" t="s">
         <v>110</v>
       </c>
@@ -4630,7 +4090,7 @@
       <c r="M19" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="N19" s="30" t="s">
+      <c r="N19" s="29" t="s">
         <v>114</v>
       </c>
       <c r="O19" s="5">
@@ -4644,7 +4104,7 @@
       </c>
       <c r="V19" s="16"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:28">
+    <row r="20" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="17" t="s">
         <v>117</v>
       </c>
@@ -4667,7 +4127,7 @@
       <c r="M20" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="30" t="s">
+      <c r="N20" s="29" t="s">
         <v>121</v>
       </c>
       <c r="O20" s="5">
@@ -4677,7 +4137,7 @@
       <c r="T20" s="16"/>
       <c r="V20" s="16"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:28">
+    <row r="21" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="17" t="s">
         <v>122</v>
       </c>
@@ -4702,13 +4162,13 @@
       <c r="M21" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="N21" s="33" t="s">
+      <c r="N21" s="32" t="s">
         <v>127</v>
       </c>
       <c r="O21" s="5">
         <v>90</v>
       </c>
-      <c r="S21" s="25" t="s">
+      <c r="S21" s="24" t="s">
         <v>128</v>
       </c>
       <c r="T21" s="16" t="s">
@@ -4716,7 +4176,7 @@
       </c>
       <c r="V21" s="16"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:28">
+    <row r="22" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="17" t="s">
         <v>130</v>
       </c>
@@ -4741,13 +4201,13 @@
       <c r="M22" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="N22" s="33" t="s">
+      <c r="N22" s="32" t="s">
         <v>135</v>
       </c>
       <c r="O22" s="5">
         <v>90</v>
       </c>
-      <c r="S22" s="25" t="s">
+      <c r="S22" s="24" t="s">
         <v>136</v>
       </c>
       <c r="T22" s="16" t="s">
@@ -4755,7 +4215,7 @@
       </c>
       <c r="V22" s="16"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:28">
+    <row r="23" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="17" t="s">
         <v>138</v>
       </c>
@@ -4780,13 +4240,13 @@
       <c r="M23" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="32" t="s">
         <v>143</v>
       </c>
       <c r="O23" s="5">
         <v>225</v>
       </c>
-      <c r="S23" s="25" t="s">
+      <c r="S23" s="24" t="s">
         <v>144</v>
       </c>
       <c r="T23" s="16" t="s">
@@ -4794,7 +4254,7 @@
       </c>
       <c r="V23" s="16"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:28">
+    <row r="24" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="17" t="s">
         <v>146</v>
       </c>
@@ -4816,13 +4276,13 @@
       <c r="M24" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="N24" s="33" t="s">
+      <c r="N24" s="32" t="s">
         <v>150</v>
       </c>
       <c r="O24" s="5">
         <v>0</v>
       </c>
-      <c r="S24" s="25" t="s">
+      <c r="S24" s="24" t="s">
         <v>151</v>
       </c>
       <c r="T24" s="16" t="s">
@@ -4830,7 +4290,7 @@
       </c>
       <c r="V24" s="16"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:28">
+    <row r="25" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="17" t="s">
         <v>153</v>
       </c>
@@ -4852,17 +4312,17 @@
       <c r="M25" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N25" s="33" t="s">
+      <c r="N25" s="32" t="s">
         <v>157</v>
       </c>
       <c r="O25" s="5">
         <v>-90</v>
       </c>
-      <c r="S25" s="25"/>
+      <c r="S25" s="24"/>
       <c r="T25" s="16"/>
       <c r="V25" s="16"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:28">
+    <row r="26" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="17" t="s">
         <v>158</v>
       </c>
@@ -4884,13 +4344,13 @@
       <c r="M26" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="N26" s="33" t="s">
+      <c r="N26" s="32" t="s">
         <v>162</v>
       </c>
       <c r="O26" s="5">
         <v>180</v>
       </c>
-      <c r="S26" s="25" t="s">
+      <c r="S26" s="24" t="s">
         <v>163</v>
       </c>
       <c r="T26" s="16" t="s">
@@ -4898,7 +4358,7 @@
       </c>
       <c r="V26" s="16"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="3:28">
+    <row r="27" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="17" t="s">
         <v>165</v>
       </c>
@@ -4923,13 +4383,13 @@
       <c r="M27" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N27" s="33" t="s">
+      <c r="N27" s="32" t="s">
         <v>168</v>
       </c>
       <c r="O27" s="5">
         <v>180</v>
       </c>
-      <c r="S27" s="25" t="s">
+      <c r="S27" s="24" t="s">
         <v>163</v>
       </c>
       <c r="T27" s="16" t="s">
@@ -4937,7 +4397,7 @@
       </c>
       <c r="V27" s="16"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:28">
+    <row r="28" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="17" t="s">
         <v>169</v>
       </c>
@@ -4962,17 +4422,17 @@
       <c r="M28" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="N28" s="33" t="s">
+      <c r="N28" s="32" t="s">
         <v>173</v>
       </c>
       <c r="O28" s="5">
         <v>90</v>
       </c>
-      <c r="S28" s="25"/>
+      <c r="S28" s="24"/>
       <c r="T28" s="16"/>
       <c r="V28" s="16"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:28">
+    <row r="29" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="17" t="s">
         <v>174</v>
       </c>
@@ -4997,17 +4457,17 @@
       <c r="M29" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="N29" s="33" t="s">
+      <c r="N29" s="32" t="s">
         <v>178</v>
       </c>
       <c r="O29" s="5">
         <v>90</v>
       </c>
-      <c r="S29" s="25"/>
+      <c r="S29" s="24"/>
       <c r="T29" s="16"/>
       <c r="V29" s="16"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:28">
+    <row r="30" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="17" t="s">
         <v>179</v>
       </c>
@@ -5032,17 +4492,17 @@
       <c r="M30" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="N30" s="33" t="s">
+      <c r="N30" s="32" t="s">
         <v>183</v>
       </c>
       <c r="O30" s="5">
         <v>90</v>
       </c>
-      <c r="S30" s="25"/>
+      <c r="S30" s="24"/>
       <c r="T30" s="16"/>
       <c r="V30" s="16"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:28">
+    <row r="31" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="17" t="s">
         <v>184</v>
       </c>
@@ -5067,7 +4527,7 @@
       <c r="M31" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N31" s="33" t="s">
+      <c r="N31" s="32" t="s">
         <v>189</v>
       </c>
       <c r="O31" s="5">
@@ -5077,7 +4537,7 @@
       <c r="T31" s="16"/>
       <c r="V31" s="16"/>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:28">
+    <row r="32" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="17" t="s">
         <v>190</v>
       </c>
@@ -5102,13 +4562,13 @@
       <c r="M32" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="N32" s="33" t="s">
+      <c r="N32" s="32" t="s">
         <v>194</v>
       </c>
       <c r="O32" s="5">
         <v>-30</v>
       </c>
-      <c r="S32" s="25" t="s">
+      <c r="S32" s="24" t="s">
         <v>163</v>
       </c>
       <c r="T32" s="16" t="s">
@@ -5116,7 +4576,7 @@
       </c>
       <c r="V32" s="16"/>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:22">
+    <row r="33" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="17" t="s">
         <v>195</v>
       </c>
@@ -5129,7 +4589,7 @@
       <c r="H33" s="4">
         <v>3</v>
       </c>
-      <c r="I33" s="34" t="s">
+      <c r="I33" s="33" t="s">
         <v>198</v>
       </c>
       <c r="J33" s="4">
@@ -5138,13 +4598,13 @@
       <c r="M33" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="N33" s="33" t="s">
+      <c r="N33" s="32" t="s">
         <v>200</v>
       </c>
       <c r="O33" s="5">
         <v>180</v>
       </c>
-      <c r="S33" s="25" t="s">
+      <c r="S33" s="24" t="s">
         <v>201</v>
       </c>
       <c r="T33" s="16" t="s">
@@ -5152,7 +4612,7 @@
       </c>
       <c r="V33" s="16"/>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:22">
+    <row r="34" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="17" t="s">
         <v>203</v>
       </c>
@@ -5162,7 +4622,7 @@
       <c r="F34" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="26">
         <v>0</v>
       </c>
       <c r="H34" s="4">
@@ -5171,13 +4631,13 @@
       <c r="M34" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N34" s="33" t="s">
+      <c r="N34" s="32" t="s">
         <v>206</v>
       </c>
       <c r="O34" s="5">
         <v>-30</v>
       </c>
-      <c r="S34" s="25" t="s">
+      <c r="S34" s="24" t="s">
         <v>207</v>
       </c>
       <c r="T34" s="16" t="s">
@@ -5185,7 +4645,7 @@
       </c>
       <c r="V34" s="16"/>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:22">
+    <row r="35" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="17" t="s">
         <v>209</v>
       </c>
@@ -5210,13 +4670,13 @@
       <c r="M35" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N35" s="33" t="s">
+      <c r="N35" s="32" t="s">
         <v>212</v>
       </c>
       <c r="O35" s="5">
         <v>-144</v>
       </c>
-      <c r="S35" s="25" t="s">
+      <c r="S35" s="24" t="s">
         <v>213</v>
       </c>
       <c r="T35" s="16" t="s">
@@ -5224,7 +4684,7 @@
       </c>
       <c r="V35" s="16"/>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:22">
+    <row r="36" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="17" t="s">
         <v>215</v>
       </c>
@@ -5240,16 +4700,16 @@
       <c r="K36" s="4">
         <v>2000001</v>
       </c>
-      <c r="M36" s="25" t="s">
+      <c r="M36" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="N36" s="33" t="s">
+      <c r="N36" s="32" t="s">
         <v>218</v>
       </c>
       <c r="O36" s="5">
         <v>-180</v>
       </c>
-      <c r="S36" s="25" t="s">
+      <c r="S36" s="24" t="s">
         <v>219</v>
       </c>
       <c r="T36" s="16" t="s">
@@ -5257,7 +4717,7 @@
       </c>
       <c r="V36" s="16"/>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:22">
+    <row r="37" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="17" t="s">
         <v>221</v>
       </c>
@@ -5273,16 +4733,16 @@
       <c r="K37" s="6">
         <v>2000002</v>
       </c>
-      <c r="M37" s="25" t="s">
+      <c r="M37" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="N37" s="33" t="s">
+      <c r="N37" s="32" t="s">
         <v>224</v>
       </c>
       <c r="O37" s="5">
         <v>90</v>
       </c>
-      <c r="S37" s="25" t="s">
+      <c r="S37" s="24" t="s">
         <v>225</v>
       </c>
       <c r="T37" s="16" t="s">
@@ -5290,7 +4750,7 @@
       </c>
       <c r="V37" s="16"/>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:22">
+    <row r="38" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="17" t="s">
         <v>227</v>
       </c>
@@ -5303,17 +4763,17 @@
       <c r="H38" s="4">
         <v>1027</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="N38" s="33" t="s">
+      <c r="N38" s="32" t="s">
         <v>230</v>
       </c>
       <c r="O38" s="5">
         <v>90</v>
       </c>
-      <c r="Q38" s="26"/>
-      <c r="S38" s="25" t="s">
+      <c r="Q38" s="25"/>
+      <c r="S38" s="24" t="s">
         <v>231</v>
       </c>
       <c r="T38" s="16" t="s">
@@ -5321,7 +4781,7 @@
       </c>
       <c r="V38" s="16"/>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:22">
+    <row r="39" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="17" t="s">
         <v>233</v>
       </c>
@@ -5334,17 +4794,17 @@
       <c r="H39" s="4">
         <v>1028</v>
       </c>
-      <c r="M39" s="25" t="s">
+      <c r="M39" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="N39" s="33" t="s">
+      <c r="N39" s="32" t="s">
         <v>236</v>
       </c>
       <c r="O39" s="5">
         <v>129</v>
       </c>
-      <c r="Q39" s="26"/>
-      <c r="S39" s="25" t="s">
+      <c r="Q39" s="25"/>
+      <c r="S39" s="24" t="s">
         <v>231</v>
       </c>
       <c r="T39" s="16" t="s">
@@ -5352,7 +4812,7 @@
       </c>
       <c r="V39" s="16"/>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:22">
+    <row r="40" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="17" t="s">
         <v>237</v>
       </c>
@@ -5377,17 +4837,17 @@
       <c r="M40" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="N40" s="33" t="s">
+      <c r="N40" s="32" t="s">
         <v>240</v>
       </c>
       <c r="O40" s="5">
         <v>180</v>
       </c>
-      <c r="S40" s="25"/>
+      <c r="S40" s="24"/>
       <c r="T40" s="16"/>
       <c r="V40" s="16"/>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:22">
+    <row r="41" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="17" t="s">
         <v>241</v>
       </c>
@@ -5410,7 +4870,7 @@
       <c r="M41" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="N41" s="33" t="s">
+      <c r="N41" s="32" t="s">
         <v>245</v>
       </c>
       <c r="O41" s="5">
@@ -5420,7 +4880,7 @@
       <c r="T41" s="16"/>
       <c r="V41" s="16"/>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:22">
+    <row r="42" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="17" t="s">
         <v>246</v>
       </c>
@@ -5443,7 +4903,7 @@
       <c r="M42" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="N42" s="33" t="s">
+      <c r="N42" s="32" t="s">
         <v>250</v>
       </c>
       <c r="O42" s="5">
@@ -5457,7 +4917,7 @@
       </c>
       <c r="V42" s="16"/>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:22">
+    <row r="43" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="17" t="s">
         <v>253</v>
       </c>
@@ -5480,7 +4940,7 @@
       <c r="M43" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="N43" s="33" t="s">
+      <c r="N43" s="32" t="s">
         <v>256</v>
       </c>
       <c r="O43" s="5">
@@ -5494,7 +4954,7 @@
       </c>
       <c r="V43" s="16"/>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:22">
+    <row r="44" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="17" t="s">
         <v>259</v>
       </c>
@@ -5520,7 +4980,7 @@
       <c r="M44" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="N44" s="33" t="s">
+      <c r="N44" s="32" t="s">
         <v>263</v>
       </c>
       <c r="O44" s="5">
@@ -5534,7 +4994,7 @@
       </c>
       <c r="V44" s="16"/>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:22">
+    <row r="45" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
         <v>266</v>
       </c>
@@ -5559,17 +5019,21 @@
       <c r="M45" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N45" s="30" t="s">
+      <c r="N45" s="29" t="s">
         <v>269</v>
       </c>
       <c r="O45" s="5">
         <v>106</v>
       </c>
-      <c r="S45" s="14"/>
-      <c r="T45" s="16"/>
+      <c r="S45" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="T45" s="35" t="s">
+        <v>704</v>
+      </c>
       <c r="V45" s="16"/>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:22">
+    <row r="46" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="17" t="s">
         <v>270</v>
       </c>
@@ -5594,7 +5058,7 @@
       <c r="M46" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="N46" s="30" t="s">
+      <c r="N46" s="29" t="s">
         <v>273</v>
       </c>
       <c r="O46" s="5">
@@ -5608,7 +5072,7 @@
       </c>
       <c r="V46" s="16"/>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:22">
+    <row r="47" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="17" t="s">
         <v>276</v>
       </c>
@@ -5633,7 +5097,7 @@
       <c r="M47" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="N47" s="30" t="s">
+      <c r="N47" s="29" t="s">
         <v>279</v>
       </c>
       <c r="O47" s="5">
@@ -5647,7 +5111,7 @@
       </c>
       <c r="V47" s="16"/>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:22">
+    <row r="48" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="17" t="s">
         <v>282</v>
       </c>
@@ -5672,7 +5136,7 @@
       <c r="M48" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N48" s="30" t="s">
+      <c r="N48" s="29" t="s">
         <v>285</v>
       </c>
       <c r="O48" s="5">
@@ -5682,7 +5146,7 @@
       <c r="T48" s="16"/>
       <c r="V48" s="16"/>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="1:28">
+    <row r="49" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="17" t="s">
         <v>286</v>
       </c>
@@ -5707,7 +5171,7 @@
       <c r="M49" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N49" s="30" t="s">
+      <c r="N49" s="29" t="s">
         <v>289</v>
       </c>
       <c r="O49" s="5">
@@ -5721,7 +5185,7 @@
       </c>
       <c r="V49" s="16"/>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="1:28">
+    <row r="50" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="17" t="s">
         <v>292</v>
       </c>
@@ -5735,16 +5199,16 @@
       <c r="H50" s="4">
         <v>1050</v>
       </c>
-      <c r="M50" s="25" t="s">
+      <c r="M50" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="N50" s="33" t="s">
+      <c r="N50" s="32" t="s">
         <v>296</v>
       </c>
       <c r="O50" s="5">
         <v>90</v>
       </c>
-      <c r="S50" s="25" t="s">
+      <c r="S50" s="24" t="s">
         <v>297</v>
       </c>
       <c r="T50" s="16" t="s">
@@ -5752,7 +5216,7 @@
       </c>
       <c r="V50" s="16"/>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="1:28">
+    <row r="51" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="17" t="s">
         <v>299</v>
       </c>
@@ -5777,7 +5241,7 @@
       <c r="M51" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N51" s="30" t="s">
+      <c r="N51" s="29" t="s">
         <v>302</v>
       </c>
       <c r="O51" s="5">
@@ -5787,7 +5251,7 @@
       <c r="T51" s="16"/>
       <c r="V51" s="16"/>
     </row>
-    <row r="52" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="52" spans="1:28" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="17" t="s">
@@ -5817,7 +5281,7 @@
       <c r="M52" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="N52" s="30" t="s">
+      <c r="N52" s="29" t="s">
         <v>306</v>
       </c>
       <c r="O52" s="5">
@@ -5833,24 +5297,21 @@
       <c r="AA52" s="5"/>
       <c r="AB52" s="5"/>
     </row>
-    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+    <row r="53" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="D53" s="5"/>
+        <v>699</v>
+      </c>
       <c r="E53" s="4" t="s">
-        <v>308</v>
+        <v>700</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>309</v>
+        <v>702</v>
       </c>
       <c r="G53" s="4">
-        <v>0</v>
+        <v>51000001</v>
       </c>
       <c r="H53" s="4">
-        <v>1046</v>
+        <v>1009</v>
       </c>
       <c r="I53" s="4">
         <v>0</v>
@@ -5858,45 +5319,41 @@
       <c r="J53" s="4">
         <v>0</v>
       </c>
-      <c r="K53" s="6"/>
-      <c r="L53" s="3"/>
       <c r="M53" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="N53" s="30" t="s">
-        <v>310</v>
+        <v>70</v>
+      </c>
+      <c r="N53" s="29" t="s">
+        <v>701</v>
       </c>
       <c r="O53" s="5">
-        <v>90</v>
-      </c>
-      <c r="P53" s="5"/>
-      <c r="S53" s="14"/>
-      <c r="T53" s="16"/>
+        <v>106</v>
+      </c>
+      <c r="S53" s="14" t="s">
+        <v>705</v>
+      </c>
+      <c r="T53" s="35" t="s">
+        <v>706</v>
+      </c>
       <c r="V53" s="16"/>
-      <c r="X53" s="5"/>
-      <c r="Y53" s="5"/>
-      <c r="Z53" s="5"/>
-      <c r="AA53" s="5"/>
-      <c r="AB53" s="5"/>
-    </row>
-    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    </row>
+    <row r="54" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="17" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" s="4">
-        <v>0</v>
+        <v>1046</v>
       </c>
       <c r="I54" s="4">
         <v>0</v>
@@ -5909,19 +5366,15 @@
       <c r="M54" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="N54" s="30" t="s">
-        <v>314</v>
+      <c r="N54" s="29" t="s">
+        <v>310</v>
       </c>
       <c r="O54" s="5">
-        <v>-140</v>
+        <v>90</v>
       </c>
       <c r="P54" s="5"/>
-      <c r="S54" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="T54" s="16" t="s">
-        <v>316</v>
-      </c>
+      <c r="S54" s="14"/>
+      <c r="T54" s="16"/>
       <c r="V54" s="16"/>
       <c r="X54" s="5"/>
       <c r="Y54" s="5"/>
@@ -5929,24 +5382,24 @@
       <c r="AA54" s="5"/>
       <c r="AB54" s="5"/>
     </row>
-    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="55" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="17" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" s="4">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="I55" s="4">
         <v>0</v>
@@ -5957,17 +5410,21 @@
       <c r="K55" s="6"/>
       <c r="L55" s="3"/>
       <c r="M55" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="N55" s="30" t="s">
-        <v>320</v>
+        <v>161</v>
+      </c>
+      <c r="N55" s="29" t="s">
+        <v>314</v>
       </c>
       <c r="O55" s="5">
-        <v>90</v>
+        <v>-140</v>
       </c>
       <c r="P55" s="5"/>
-      <c r="S55" s="14"/>
-      <c r="T55" s="16"/>
+      <c r="S55" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="T55" s="16" t="s">
+        <v>316</v>
+      </c>
       <c r="V55" s="16"/>
       <c r="X55" s="5"/>
       <c r="Y55" s="5"/>
@@ -5975,24 +5432,24 @@
       <c r="AA55" s="5"/>
       <c r="AB55" s="5"/>
     </row>
-    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="56" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G56" s="4">
         <v>0</v>
       </c>
       <c r="H56" s="4">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I56" s="4">
         <v>0</v>
@@ -6003,13 +5460,13 @@
       <c r="K56" s="6"/>
       <c r="L56" s="3"/>
       <c r="M56" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="N56" s="30" t="s">
-        <v>325</v>
+        <v>80</v>
+      </c>
+      <c r="N56" s="29" t="s">
+        <v>320</v>
       </c>
       <c r="O56" s="5">
-        <v>-180</v>
+        <v>90</v>
       </c>
       <c r="P56" s="5"/>
       <c r="S56" s="14"/>
@@ -6021,24 +5478,24 @@
       <c r="AA56" s="5"/>
       <c r="AB56" s="5"/>
     </row>
-    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="57" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="17" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G57" s="4">
         <v>0</v>
       </c>
       <c r="H57" s="4">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="I57" s="4">
         <v>0</v>
@@ -6049,13 +5506,13 @@
       <c r="K57" s="6"/>
       <c r="L57" s="3"/>
       <c r="M57" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="N57" s="30" t="s">
-        <v>329</v>
+        <v>324</v>
+      </c>
+      <c r="N57" s="29" t="s">
+        <v>325</v>
       </c>
       <c r="O57" s="5">
-        <v>30</v>
+        <v>-180</v>
       </c>
       <c r="P57" s="5"/>
       <c r="S57" s="14"/>
@@ -6067,24 +5524,24 @@
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
     </row>
-    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="58" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="17" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" s="4">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="I58" s="4">
         <v>0</v>
@@ -6097,11 +5554,11 @@
       <c r="M58" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="N58" s="30" t="s">
-        <v>333</v>
+      <c r="N58" s="29" t="s">
+        <v>329</v>
       </c>
       <c r="O58" s="5">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="P58" s="5"/>
       <c r="S58" s="14"/>
@@ -6113,53 +5570,64 @@
       <c r="AA58" s="5"/>
       <c r="AB58" s="5"/>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="1:28">
+    <row r="59" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
       <c r="C59" s="17" t="s">
-        <v>334</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="D59" s="5"/>
       <c r="E59" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G59" s="4">
-        <v>10001101</v>
+        <v>0</v>
       </c>
       <c r="H59" s="4">
-        <v>1009</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>1072</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="3"/>
       <c r="M59" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N59" s="30" t="s">
-        <v>337</v>
+        <v>193</v>
+      </c>
+      <c r="N59" s="29" t="s">
+        <v>333</v>
       </c>
       <c r="O59" s="5">
-        <v>60</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="P59" s="5"/>
       <c r="S59" s="14"/>
       <c r="T59" s="16"/>
       <c r="V59" s="16"/>
-    </row>
-    <row r="60" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C60" s="17">
-        <v>20001002</v>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="5"/>
+      <c r="AB59" s="5"/>
+    </row>
+    <row r="60" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="17" t="s">
+        <v>334</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G60" s="4">
-        <v>10001201</v>
+        <v>10001101</v>
       </c>
       <c r="H60" s="4">
         <v>1009</v>
@@ -6171,95 +5639,96 @@
         <v>187</v>
       </c>
       <c r="M60" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="N60" s="5" t="s">
-        <v>340</v>
+        <v>65</v>
+      </c>
+      <c r="N60" s="29" t="s">
+        <v>337</v>
       </c>
       <c r="O60" s="5">
-        <v>-45</v>
+        <v>60</v>
       </c>
       <c r="S60" s="14"/>
       <c r="T60" s="16"/>
       <c r="V60" s="16"/>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C61" s="14">
+    <row r="61" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C61" s="17">
+        <v>20001002</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="4">
+        <v>10001201</v>
+      </c>
+      <c r="H61" s="4">
+        <v>1009</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M61" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="O61" s="5">
+        <v>-45</v>
+      </c>
+      <c r="S61" s="14"/>
+      <c r="T61" s="16"/>
+      <c r="V61" s="16"/>
+    </row>
+    <row r="62" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="14">
         <v>20001003</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="I61" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M61" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="O61" s="5">
-        <v>180</v>
-      </c>
-      <c r="S61" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="T61" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="V61" s="16"/>
-    </row>
-    <row r="62" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C62" s="17">
-        <v>20001004</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="G62" s="4"/>
       <c r="I62" s="6" t="s">
-        <v>187</v>
+        <v>343</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M62" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="N62" s="30" t="s">
-        <v>350</v>
+        <v>324</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="O62" s="5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="S62" s="15" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="T62" s="16" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="V62" s="16"/>
     </row>
-    <row r="63" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C63" s="14">
-        <v>20001005</v>
+    <row r="63" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="17">
+        <v>20001004</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G63" s="4"/>
       <c r="I63" s="6" t="s">
@@ -6271,23 +5740,23 @@
       <c r="M63" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="N63" s="5" t="s">
-        <v>355</v>
+      <c r="N63" s="29" t="s">
+        <v>350</v>
       </c>
       <c r="O63" s="5">
-        <v>-45</v>
+        <v>90</v>
       </c>
       <c r="S63" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="T63" s="16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V63" s="16"/>
     </row>
-    <row r="64" ht="20.1" customHeight="1" spans="1:28">
+    <row r="64" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="14">
-        <v>20001006</v>
+        <v>20001005</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>353</v>
@@ -6305,476 +5774,476 @@
       <c r="M64" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="N64" s="30" t="s">
-        <v>358</v>
+      <c r="N64" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="O64" s="5">
-        <v>45</v>
+        <v>-45</v>
       </c>
       <c r="S64" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T64" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="V64" s="16"/>
     </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:22">
+    <row r="65" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="14">
-        <v>20001007</v>
+        <v>20001006</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G65" s="4"/>
       <c r="I65" s="6" t="s">
-        <v>363</v>
+        <v>187</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M65" s="14">
+      <c r="M65" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="N65" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="O65" s="5">
+        <v>45</v>
+      </c>
+      <c r="S65" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="V65" s="16"/>
+    </row>
+    <row r="66" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="14">
         <v>20001007</v>
       </c>
-      <c r="N65" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="O65" s="5">
-        <v>150</v>
-      </c>
-      <c r="S65" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="T65" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="V65" s="16"/>
-    </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C66" s="14">
-        <v>20001008</v>
-      </c>
       <c r="E66" s="4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G66" s="4"/>
       <c r="I66" s="6" t="s">
-        <v>187</v>
+        <v>363</v>
       </c>
       <c r="J66" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M66" s="14">
+        <v>20001007</v>
+      </c>
+      <c r="N66" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="O66" s="5">
+        <v>150</v>
+      </c>
+      <c r="S66" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="V66" s="16"/>
+    </row>
+    <row r="67" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="14">
         <v>20001008</v>
       </c>
-      <c r="N66" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="O66" s="5">
-        <v>-155</v>
-      </c>
-      <c r="S66" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="T66" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="V66" s="16"/>
-    </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C67" s="14">
-        <v>20001009</v>
-      </c>
       <c r="E67" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G67" s="4"/>
       <c r="I67" s="6" t="s">
-        <v>374</v>
+        <v>187</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M67" s="14">
+        <v>20001008</v>
+      </c>
+      <c r="N67" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="O67" s="5">
+        <v>-155</v>
+      </c>
+      <c r="S67" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="T67" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="V67" s="16"/>
+    </row>
+    <row r="68" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="14">
         <v>20001009</v>
       </c>
-      <c r="N67" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="O67" s="5">
-        <v>35</v>
-      </c>
-      <c r="S67" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="T67" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="V67" s="16"/>
-    </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C68" s="14">
-        <v>20001010</v>
-      </c>
       <c r="E68" s="4" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G68" s="4"/>
       <c r="I68" s="6" t="s">
-        <v>187</v>
+        <v>374</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M68" s="14">
+        <v>20001009</v>
+      </c>
+      <c r="N68" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="O68" s="5">
+        <v>35</v>
+      </c>
+      <c r="S68" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="T68" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="V68" s="16"/>
+    </row>
+    <row r="69" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="14">
         <v>20001010</v>
       </c>
-      <c r="N68" s="34" t="s">
-        <v>380</v>
-      </c>
-      <c r="O68" s="5">
-        <v>180</v>
-      </c>
-      <c r="S68" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="T68" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="V68" s="16"/>
-    </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C69" s="14">
-        <v>20001011</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="G69" s="4"/>
       <c r="I69" s="6" t="s">
-        <v>385</v>
+        <v>187</v>
       </c>
       <c r="J69" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M69" s="14">
+        <v>20001010</v>
+      </c>
+      <c r="N69" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="O69" s="5">
+        <v>180</v>
+      </c>
+      <c r="S69" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="T69" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="V69" s="16"/>
+    </row>
+    <row r="70" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="14">
         <v>20001011</v>
       </c>
-      <c r="N69" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="O69" s="5">
-        <v>-180</v>
-      </c>
-      <c r="S69" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="T69" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="V69" s="16"/>
-    </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C70" s="14">
-        <v>20001012</v>
-      </c>
       <c r="E70" s="4" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G70" s="4"/>
       <c r="I70" s="6" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M70" s="14">
+        <v>20001011</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="O70" s="5">
+        <v>-180</v>
+      </c>
+      <c r="S70" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="T70" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="V70" s="16"/>
+    </row>
+    <row r="71" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="14">
         <v>20001012</v>
       </c>
-      <c r="N70" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="O70" s="5">
-        <v>80</v>
-      </c>
-      <c r="S70" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="T70" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="V70" s="16"/>
-    </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C71" s="14">
-        <v>20001013</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="G71" s="4"/>
       <c r="I71" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M71" s="14">
+        <v>20001012</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="O71" s="5">
+        <v>80</v>
+      </c>
+      <c r="S71" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="T71" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="V71" s="16"/>
+    </row>
+    <row r="72" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="14">
         <v>20001013</v>
       </c>
-      <c r="N71" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="O71" s="5">
-        <v>180</v>
-      </c>
-      <c r="S71" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="T71" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="V71" s="16"/>
-    </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C72" s="14">
-        <v>20001014</v>
-      </c>
       <c r="E72" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="G72" s="4"/>
       <c r="I72" s="6" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M72" s="14">
-        <v>20001014</v>
+        <v>20001013</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="O72" s="5">
         <v>180</v>
       </c>
       <c r="S72" s="15" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="T72" s="16" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="V72" s="16"/>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:22">
+    <row r="73" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="14">
-        <v>20001015</v>
+        <v>20001014</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="G73" s="4"/>
       <c r="I73" s="6" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M73" s="14">
+        <v>20001014</v>
+      </c>
+      <c r="N73" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="O73" s="5">
+        <v>180</v>
+      </c>
+      <c r="S73" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="T73" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="V73" s="16"/>
+    </row>
+    <row r="74" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="14">
         <v>20001015</v>
       </c>
-      <c r="N73" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="O73" s="5">
-        <v>128</v>
-      </c>
-      <c r="S73" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="T73" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="V73" s="16"/>
-    </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C74" s="14">
-        <v>20001016</v>
-      </c>
       <c r="E74" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="G74" s="4"/>
       <c r="I74" s="6" t="s">
-        <v>187</v>
+        <v>409</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M74" s="14">
+        <v>20001015</v>
+      </c>
+      <c r="N74" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="O74" s="5">
+        <v>128</v>
+      </c>
+      <c r="S74" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="T74" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="V74" s="16"/>
+    </row>
+    <row r="75" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="14">
         <v>20001016</v>
       </c>
-      <c r="N74" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="O74" s="5">
-        <v>180</v>
-      </c>
-      <c r="S74" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="T74" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="V74" s="16"/>
-    </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C75" s="14">
-        <v>20001017</v>
-      </c>
       <c r="E75" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G75" s="4"/>
       <c r="I75" s="6" t="s">
-        <v>419</v>
+        <v>187</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>187</v>
       </c>
       <c r="M75" s="14">
+        <v>20001016</v>
+      </c>
+      <c r="N75" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="O75" s="5">
+        <v>180</v>
+      </c>
+      <c r="S75" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="T75" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="V75" s="16"/>
+    </row>
+    <row r="76" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="14">
         <v>20001017</v>
       </c>
-      <c r="N75" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="O75" s="5">
-        <v>120</v>
-      </c>
-      <c r="S75" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="T75" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="V75" s="16"/>
-    </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C76" s="14">
-        <v>20001018</v>
-      </c>
       <c r="E76" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G76" s="4"/>
       <c r="I76" s="6" t="s">
-        <v>187</v>
+        <v>419</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="K76" s="4"/>
-      <c r="M76" s="25">
-        <v>0</v>
+      <c r="M76" s="14">
+        <v>20001017</v>
       </c>
       <c r="N76" s="5" t="s">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="O76" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="S76" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="T76" s="16" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="V76" s="16"/>
     </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:22">
+    <row r="77" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="14">
-        <v>20001019</v>
+        <v>20001018</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G77" s="4"/>
       <c r="I77" s="6" t="s">
-        <v>429</v>
+        <v>187</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M77" s="14">
+      <c r="K77" s="4"/>
+      <c r="M77" s="24">
+        <v>0</v>
+      </c>
+      <c r="N77" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="O77" s="5">
+        <v>180</v>
+      </c>
+      <c r="S77" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="T77" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="V77" s="16"/>
+    </row>
+    <row r="78" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C78" s="14">
         <v>20001019</v>
       </c>
-      <c r="N77" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="O77" s="5">
-        <v>-180</v>
-      </c>
-      <c r="S77" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="T77" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="V77" s="16"/>
-    </row>
-    <row r="78" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C78" s="14">
-        <v>20001020</v>
-      </c>
       <c r="E78" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G78" s="4"/>
       <c r="I78" s="6" t="s">
-        <v>187</v>
+        <v>429</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>187</v>
@@ -6783,28 +6252,28 @@
         <v>20001019</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="O78" s="5">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="S78" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="T78" s="16" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="V78" s="16"/>
     </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:22">
+    <row r="79" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="14">
-        <v>20001021</v>
+        <v>20001020</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G79" s="4"/>
       <c r="I79" s="6" t="s">
@@ -6814,135 +6283,134 @@
         <v>187</v>
       </c>
       <c r="M79" s="14">
+        <v>20001019</v>
+      </c>
+      <c r="N79" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="O79" s="5">
+        <v>180</v>
+      </c>
+      <c r="S79" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="T79" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="V79" s="16"/>
+    </row>
+    <row r="80" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="14">
         <v>20001021</v>
       </c>
-      <c r="N79" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="O79" s="5">
-        <v>-180</v>
-      </c>
-      <c r="S79" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="T79" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="V79" s="16"/>
-    </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C80" s="14">
-        <v>20001022</v>
-      </c>
       <c r="E80" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G80" s="4"/>
       <c r="I80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M80" s="14">
+        <v>20001021</v>
+      </c>
+      <c r="N80" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="O80" s="5">
+        <v>-180</v>
+      </c>
+      <c r="S80" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="T80" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="V80" s="16"/>
+    </row>
+    <row r="81" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="14">
+        <v>20001022</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="I81" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="J80" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M80" s="14">
+      <c r="J81" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M81" s="14">
         <v>20001022</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="N81" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="O80" s="5">
+      <c r="O81" s="5">
         <v>-106</v>
       </c>
-      <c r="S80" s="15" t="s">
+      <c r="S81" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="T80" s="16" t="s">
+      <c r="T81" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="V80" s="16"/>
-    </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C81" s="14">
+      <c r="V81" s="16"/>
+    </row>
+    <row r="82" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="14">
         <v>20001023</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E82" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F82" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4">
+      <c r="G82" s="4"/>
+      <c r="H82" s="4">
         <v>1004</v>
       </c>
-      <c r="I81" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M81" s="14">
+      <c r="I82" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M82" s="14">
         <v>20001023</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="N82" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="O81" s="5">
+      <c r="O82" s="5">
         <v>180</v>
-      </c>
-      <c r="S81" s="14"/>
-      <c r="T81" s="16"/>
-      <c r="V81" s="16"/>
-    </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C82" s="14">
-        <v>20001024</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G82" s="4"/>
-      <c r="I82" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M82" s="14">
-        <v>20001024</v>
-      </c>
-      <c r="N82" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="O82" s="5">
-        <v>-152</v>
       </c>
       <c r="S82" s="14"/>
       <c r="T82" s="16"/>
       <c r="V82" s="16"/>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C83" s="17" t="s">
-        <v>449</v>
+    <row r="83" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="14">
+        <v>20001024</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="G83" s="4">
-        <v>10002101</v>
-      </c>
-      <c r="H83" s="4">
-        <v>1009</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G83" s="4"/>
       <c r="I83" s="6" t="s">
         <v>187</v>
       </c>
@@ -6950,30 +6418,30 @@
         <v>187</v>
       </c>
       <c r="M83" s="14">
-        <v>20001001</v>
+        <v>20001024</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="O83" s="5">
-        <v>-147</v>
+        <v>-152</v>
       </c>
       <c r="S83" s="14"/>
       <c r="T83" s="16"/>
       <c r="V83" s="16"/>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:22">
+    <row r="84" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>338</v>
+        <v>63</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>452</v>
+        <v>336</v>
       </c>
       <c r="G84" s="4">
-        <v>10002201</v>
+        <v>10002101</v>
       </c>
       <c r="H84" s="4">
         <v>1009</v>
@@ -6985,77 +6453,78 @@
         <v>187</v>
       </c>
       <c r="M84" s="14">
-        <v>20001002</v>
+        <v>20001001</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O84" s="5">
-        <v>-129</v>
+        <v>-147</v>
       </c>
       <c r="S84" s="14"/>
       <c r="T84" s="16"/>
       <c r="V84" s="16"/>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:22">
+    <row r="85" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G85" s="4">
+        <v>10002201</v>
+      </c>
+      <c r="H85" s="4">
+        <v>1009</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M85" s="14">
+        <v>20001002</v>
+      </c>
+      <c r="N85" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="O85" s="5">
+        <v>-129</v>
+      </c>
+      <c r="S85" s="14"/>
+      <c r="T85" s="16"/>
+      <c r="V85" s="16"/>
+    </row>
+    <row r="86" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E86" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F86" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="G85" s="4"/>
-      <c r="I85" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M85" s="25">
-        <v>20001007</v>
-      </c>
-      <c r="N85" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="O85" s="5">
-        <v>-131</v>
-      </c>
-      <c r="S85" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="T85" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="V85" s="16"/>
-    </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C86" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>461</v>
       </c>
       <c r="G86" s="4"/>
       <c r="I86" s="6" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M86" s="14">
-        <v>20001005</v>
+      <c r="M86" s="24">
+        <v>20001007</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="O86" s="5">
-        <v>180</v>
+        <v>-131</v>
       </c>
       <c r="S86" s="15" t="s">
         <v>351</v>
@@ -7065,28 +6534,28 @@
       </c>
       <c r="V86" s="16"/>
     </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:22">
+    <row r="87" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="17" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="G87" s="4"/>
       <c r="I87" s="6" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J87" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M87" s="25">
-        <v>20001009</v>
+      <c r="M87" s="14">
+        <v>20001005</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="O87" s="5">
         <v>180</v>
@@ -7099,28 +6568,28 @@
       </c>
       <c r="V87" s="16"/>
     </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:22">
+    <row r="88" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="17" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G88" s="4"/>
       <c r="I88" s="6" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M88" s="14">
-        <v>20001005</v>
+      <c r="M88" s="24">
+        <v>20001009</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O88" s="5">
         <v>180</v>
@@ -7133,43 +6602,43 @@
       </c>
       <c r="V88" s="16"/>
     </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:22">
+    <row r="89" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="17" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G89" s="4"/>
       <c r="I89" s="6" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M89" s="14" t="s">
-        <v>349</v>
+      <c r="M89" s="14">
+        <v>20001005</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>380</v>
+        <v>473</v>
       </c>
       <c r="O89" s="5">
         <v>180</v>
       </c>
       <c r="S89" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="T89" s="16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V89" s="16"/>
     </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:22">
+    <row r="90" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>353</v>
@@ -7194,22 +6663,22 @@
         <v>180</v>
       </c>
       <c r="S90" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T90" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="V90" s="16"/>
     </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:22">
+    <row r="91" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>239</v>
+        <v>475</v>
       </c>
       <c r="G91" s="4"/>
       <c r="I91" s="6" t="s">
@@ -7218,14 +6687,14 @@
       <c r="J91" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M91" s="25">
-        <v>20001017</v>
+      <c r="M91" s="14" t="s">
+        <v>349</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>478</v>
+        <v>380</v>
       </c>
       <c r="O91" s="5">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="S91" s="15" t="s">
         <v>359</v>
@@ -7235,53 +6704,52 @@
       </c>
       <c r="V91" s="16"/>
     </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:22">
+    <row r="92" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="I92" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M92" s="24">
+        <v>20001017</v>
+      </c>
+      <c r="N92" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="O92" s="5">
+        <v>27</v>
+      </c>
+      <c r="S92" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="T92" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="V92" s="16"/>
+    </row>
+    <row r="93" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C93" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E93" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F93" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G92" s="4">
+      <c r="G93" s="4">
         <v>10003101</v>
-      </c>
-      <c r="H92" s="4">
-        <v>1009</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M92" s="14">
-        <v>20001001</v>
-      </c>
-      <c r="N92" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="O92" s="5">
-        <v>123</v>
-      </c>
-      <c r="S92" s="14"/>
-      <c r="T92" s="16"/>
-      <c r="V92" s="16"/>
-    </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C93" s="17" t="s">
-        <v>481</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G93" s="4">
-        <v>10003201</v>
       </c>
       <c r="H93" s="4">
         <v>1009</v>
@@ -7293,77 +6761,78 @@
         <v>187</v>
       </c>
       <c r="M93" s="14">
-        <v>20001002</v>
+        <v>20001001</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="O93" s="5">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="S93" s="14"/>
       <c r="T93" s="16"/>
       <c r="V93" s="16"/>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:22">
+    <row r="94" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G94" s="4">
+        <v>10003201</v>
+      </c>
+      <c r="H94" s="4">
+        <v>1009</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M94" s="14">
+        <v>20001002</v>
+      </c>
+      <c r="N94" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="O94" s="5">
+        <v>45</v>
+      </c>
+      <c r="S94" s="14"/>
+      <c r="T94" s="16"/>
+      <c r="V94" s="16"/>
+    </row>
+    <row r="95" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C95" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E95" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F95" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="G94" s="4"/>
-      <c r="I94" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M94" s="25">
-        <v>20001007</v>
-      </c>
-      <c r="N94" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="O94" s="5">
-        <v>90</v>
-      </c>
-      <c r="S94" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="T94" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="V94" s="16"/>
-    </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C95" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="G95" s="4"/>
       <c r="I95" s="6" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J95" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M95" s="25">
-        <v>20001011</v>
+      <c r="M95" s="24">
+        <v>20001007</v>
       </c>
       <c r="N95" s="5" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="O95" s="5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="S95" s="15" t="s">
         <v>351</v>
@@ -7373,31 +6842,31 @@
       </c>
       <c r="V95" s="16"/>
     </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:22">
+    <row r="96" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="17" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G96" s="4"/>
       <c r="I96" s="6" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J96" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M96" s="25">
-        <v>20001017</v>
+      <c r="M96" s="24">
+        <v>20001011</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="O96" s="5">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="S96" s="15" t="s">
         <v>351</v>
@@ -7407,31 +6876,31 @@
       </c>
       <c r="V96" s="16"/>
     </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:22">
+    <row r="97" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="17" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="G97" s="4"/>
       <c r="I97" s="6" t="s">
-        <v>187</v>
+        <v>496</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M97" s="14">
-        <v>20001005</v>
+      <c r="M97" s="24">
+        <v>20001017</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="O97" s="5">
-        <v>-70</v>
+        <v>95</v>
       </c>
       <c r="S97" s="15" t="s">
         <v>351</v>
@@ -7441,15 +6910,15 @@
       </c>
       <c r="V97" s="16"/>
     </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:22">
+    <row r="98" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G98" s="4"/>
       <c r="I98" s="6" t="s">
@@ -7458,26 +6927,26 @@
       <c r="J98" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M98" s="14" t="s">
-        <v>349</v>
+      <c r="M98" s="14">
+        <v>20001005</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>380</v>
+        <v>499</v>
       </c>
       <c r="O98" s="5">
-        <v>180</v>
+        <v>-70</v>
       </c>
       <c r="S98" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="T98" s="16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V98" s="16"/>
     </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:22">
+    <row r="99" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>353</v>
@@ -7502,38 +6971,38 @@
         <v>180</v>
       </c>
       <c r="S99" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T99" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="V99" s="16"/>
     </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:22">
+    <row r="100" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>503</v>
+        <v>353</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="G100" s="4"/>
       <c r="I100" s="6" t="s">
-        <v>504</v>
+        <v>187</v>
       </c>
       <c r="J100" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M100" s="14">
-        <v>20001008</v>
+      <c r="M100" s="14" t="s">
+        <v>349</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>505</v>
+        <v>380</v>
       </c>
       <c r="O100" s="5">
-        <v>-70</v>
+        <v>180</v>
       </c>
       <c r="S100" s="15" t="s">
         <v>359</v>
@@ -7543,31 +7012,31 @@
       </c>
       <c r="V100" s="16"/>
     </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:22">
+    <row r="101" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="17" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>508</v>
+        <v>441</v>
       </c>
       <c r="G101" s="4"/>
       <c r="I101" s="6" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="J101" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M101" s="25">
-        <v>20001011</v>
+      <c r="M101" s="14">
+        <v>20001008</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="O101" s="5">
-        <v>-180</v>
+        <v>-70</v>
       </c>
       <c r="S101" s="15" t="s">
         <v>359</v>
@@ -7577,53 +7046,52 @@
       </c>
       <c r="V101" s="16"/>
     </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:22">
+    <row r="102" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="I102" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M102" s="24">
+        <v>20001011</v>
+      </c>
+      <c r="N102" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="O102" s="5">
+        <v>-180</v>
+      </c>
+      <c r="S102" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="T102" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="V102" s="16"/>
+    </row>
+    <row r="103" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F103" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G102" s="4">
+      <c r="G103" s="4">
         <v>10004101</v>
-      </c>
-      <c r="H102" s="4">
-        <v>1009</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M102" s="14">
-        <v>20001001</v>
-      </c>
-      <c r="N102" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="O102" s="5">
-        <v>35</v>
-      </c>
-      <c r="S102" s="14"/>
-      <c r="T102" s="16"/>
-      <c r="V102" s="16"/>
-    </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C103" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G103" s="4">
-        <v>10004201</v>
       </c>
       <c r="H103" s="4">
         <v>1009</v>
@@ -7635,77 +7103,78 @@
         <v>187</v>
       </c>
       <c r="M103" s="14">
-        <v>20001002</v>
+        <v>20001001</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="O103" s="5">
-        <v>-41</v>
+        <v>35</v>
       </c>
       <c r="S103" s="14"/>
       <c r="T103" s="16"/>
       <c r="V103" s="16"/>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:22">
+    <row r="104" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G104" s="4">
+        <v>10004201</v>
+      </c>
+      <c r="H104" s="4">
+        <v>1009</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M104" s="14">
+        <v>20001002</v>
+      </c>
+      <c r="N104" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="O104" s="5">
+        <v>-41</v>
+      </c>
+      <c r="S104" s="14"/>
+      <c r="T104" s="16"/>
+      <c r="V104" s="16"/>
+    </row>
+    <row r="105" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C105" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E105" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F105" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="G104" s="4"/>
-      <c r="I104" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M104" s="25">
-        <v>20001007</v>
-      </c>
-      <c r="N104" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="O104" s="5">
-        <v>0</v>
-      </c>
-      <c r="S104" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="T104" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="V104" s="16"/>
-    </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C105" s="17" t="s">
-        <v>520</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>522</v>
       </c>
       <c r="G105" s="4"/>
       <c r="I105" s="6" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="J105" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M105" s="25">
-        <v>20001017</v>
+      <c r="M105" s="24">
+        <v>20001007</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="O105" s="5">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="S105" s="15" t="s">
         <v>351</v>
@@ -7715,31 +7184,31 @@
       </c>
       <c r="V105" s="16"/>
     </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:22">
+    <row r="106" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="17" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="G106" s="4"/>
       <c r="I106" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M106" s="25">
-        <v>20001013</v>
+      <c r="M106" s="24">
+        <v>20001017</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="O106" s="5">
-        <v>-3</v>
+        <v>101</v>
       </c>
       <c r="S106" s="15" t="s">
         <v>351</v>
@@ -7749,43 +7218,43 @@
       </c>
       <c r="V106" s="16"/>
     </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:22">
+    <row r="107" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="17" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>353</v>
+        <v>526</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>475</v>
+        <v>527</v>
       </c>
       <c r="G107" s="4"/>
       <c r="I107" s="6" t="s">
-        <v>187</v>
+        <v>528</v>
       </c>
       <c r="J107" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M107" s="14" t="s">
-        <v>349</v>
+      <c r="M107" s="24">
+        <v>20001013</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>380</v>
+        <v>529</v>
       </c>
       <c r="O107" s="5">
-        <v>180</v>
+        <v>-3</v>
       </c>
       <c r="S107" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="T107" s="16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V107" s="16"/>
     </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:22">
+    <row r="108" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>353</v>
@@ -7810,38 +7279,38 @@
         <v>180</v>
       </c>
       <c r="S108" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T108" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="V108" s="16"/>
     </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:22">
+    <row r="109" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>533</v>
+        <v>353</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="G109" s="4"/>
       <c r="I109" s="6" t="s">
-        <v>535</v>
+        <v>187</v>
       </c>
       <c r="J109" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M109" s="25">
-        <v>20001015</v>
+      <c r="M109" s="14" t="s">
+        <v>349</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>536</v>
+        <v>380</v>
       </c>
       <c r="O109" s="5">
-        <v>-180</v>
+        <v>180</v>
       </c>
       <c r="S109" s="15" t="s">
         <v>359</v>
@@ -7851,31 +7320,31 @@
       </c>
       <c r="V109" s="16"/>
     </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:22">
+    <row r="110" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="17" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="G110" s="4"/>
       <c r="I110" s="6" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="J110" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M110" s="25">
+      <c r="M110" s="24">
         <v>20001015</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O110" s="5">
-        <v>83</v>
+        <v>-180</v>
       </c>
       <c r="S110" s="15" t="s">
         <v>359</v>
@@ -7885,53 +7354,52 @@
       </c>
       <c r="V110" s="16"/>
     </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:22">
+    <row r="111" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G111" s="4"/>
+      <c r="I111" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M111" s="24">
+        <v>20001015</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="O111" s="5">
+        <v>83</v>
+      </c>
+      <c r="S111" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="T111" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="V111" s="16"/>
+    </row>
+    <row r="112" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C112" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E112" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F112" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G112" s="4">
         <v>10005101</v>
-      </c>
-      <c r="H111" s="4">
-        <v>1009</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M111" s="14">
-        <v>20001001</v>
-      </c>
-      <c r="N111" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="O111" s="5">
-        <v>51</v>
-      </c>
-      <c r="S111" s="14"/>
-      <c r="T111" s="16"/>
-      <c r="V111" s="16"/>
-    </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C112" s="17" t="s">
-        <v>544</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G112" s="4">
-        <v>10005201</v>
       </c>
       <c r="H112" s="4">
         <v>1009</v>
@@ -7943,77 +7411,78 @@
         <v>187</v>
       </c>
       <c r="M112" s="14">
-        <v>20001002</v>
+        <v>20001001</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="O112" s="5">
-        <v>-44</v>
+        <v>51</v>
       </c>
       <c r="S112" s="14"/>
       <c r="T112" s="16"/>
       <c r="V112" s="16"/>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:22">
+    <row r="113" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G113" s="4">
+        <v>10005201</v>
+      </c>
+      <c r="H113" s="4">
+        <v>1009</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M113" s="14">
+        <v>20001002</v>
+      </c>
+      <c r="N113" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="O113" s="5">
+        <v>-44</v>
+      </c>
+      <c r="S113" s="14"/>
+      <c r="T113" s="16"/>
+      <c r="V113" s="16"/>
+    </row>
+    <row r="114" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C114" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E114" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F114" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="G113" s="4"/>
-      <c r="I113" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M113" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="N113" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="O113" s="5">
-        <v>180</v>
-      </c>
-      <c r="S113" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="T113" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="V113" s="16"/>
-    </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C114" s="17" t="s">
-        <v>551</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>553</v>
       </c>
       <c r="G114" s="4"/>
       <c r="I114" s="6" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="J114" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M114" s="25">
-        <v>20001012</v>
+      <c r="M114" s="14" t="s">
+        <v>324</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="O114" s="5">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="S114" s="15" t="s">
         <v>351</v>
@@ -8023,31 +7492,31 @@
       </c>
       <c r="V114" s="16"/>
     </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:22">
+    <row r="115" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="17" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G115" s="4"/>
       <c r="I115" s="6" t="s">
-        <v>187</v>
+        <v>554</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M115" s="25">
-        <v>20001015</v>
+      <c r="M115" s="24">
+        <v>20001012</v>
       </c>
       <c r="N115" s="5" t="s">
-        <v>380</v>
+        <v>555</v>
       </c>
       <c r="O115" s="5">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="S115" s="15" t="s">
         <v>351</v>
@@ -8057,31 +7526,31 @@
       </c>
       <c r="V115" s="16"/>
     </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:22">
+    <row r="116" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="17" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="G116" s="4"/>
       <c r="I116" s="6" t="s">
-        <v>562</v>
+        <v>187</v>
       </c>
       <c r="J116" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M116" s="25">
-        <v>20001013</v>
+      <c r="M116" s="24">
+        <v>20001015</v>
       </c>
       <c r="N116" s="5" t="s">
-        <v>563</v>
+        <v>380</v>
       </c>
       <c r="O116" s="5">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="S116" s="15" t="s">
         <v>351</v>
@@ -8091,43 +7560,43 @@
       </c>
       <c r="V116" s="16"/>
     </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:22">
+    <row r="117" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="17" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>353</v>
+        <v>560</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>354</v>
+        <v>561</v>
       </c>
       <c r="G117" s="4"/>
       <c r="I117" s="6" t="s">
-        <v>187</v>
+        <v>562</v>
       </c>
       <c r="J117" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M117" s="14" t="s">
-        <v>349</v>
+      <c r="M117" s="24">
+        <v>20001013</v>
       </c>
       <c r="N117" s="5" t="s">
-        <v>380</v>
+        <v>563</v>
       </c>
       <c r="O117" s="5">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="S117" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="T117" s="16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V117" s="16"/>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:22">
+    <row r="118" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>353</v>
@@ -8152,22 +7621,22 @@
         <v>180</v>
       </c>
       <c r="S118" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T118" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="V118" s="16"/>
     </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C119" s="14">
-        <v>20099001</v>
+    <row r="119" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C119" s="17" t="s">
+        <v>565</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>566</v>
+        <v>353</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="G119" s="4"/>
       <c r="I119" s="6" t="s">
@@ -8176,8 +7645,8 @@
       <c r="J119" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M119" s="25" t="s">
-        <v>567</v>
+      <c r="M119" s="14" t="s">
+        <v>349</v>
       </c>
       <c r="N119" s="5" t="s">
         <v>380</v>
@@ -8186,22 +7655,22 @@
         <v>180</v>
       </c>
       <c r="S119" s="15" t="s">
-        <v>568</v>
+        <v>359</v>
       </c>
       <c r="T119" s="16" t="s">
-        <v>569</v>
+        <v>360</v>
       </c>
       <c r="V119" s="16"/>
     </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:22">
+    <row r="120" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="14">
-        <v>20099002</v>
+        <v>20099001</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>452</v>
+        <v>336</v>
       </c>
       <c r="G120" s="4"/>
       <c r="I120" s="6" t="s">
@@ -8210,7 +7679,7 @@
       <c r="J120" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M120" s="25" t="s">
+      <c r="M120" s="24" t="s">
         <v>567</v>
       </c>
       <c r="N120" s="5" t="s">
@@ -8220,22 +7689,22 @@
         <v>180</v>
       </c>
       <c r="S120" s="15" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="T120" s="16" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="V120" s="16"/>
     </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:22">
+    <row r="121" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="14">
-        <v>20099003</v>
+        <v>20099002</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>574</v>
+        <v>452</v>
       </c>
       <c r="G121" s="4"/>
       <c r="I121" s="6" t="s">
@@ -8244,7 +7713,7 @@
       <c r="J121" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M121" s="25" t="s">
+      <c r="M121" s="24" t="s">
         <v>567</v>
       </c>
       <c r="N121" s="5" t="s">
@@ -8254,22 +7723,22 @@
         <v>180</v>
       </c>
       <c r="S121" s="15" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="T121" s="16" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="V121" s="16"/>
     </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:22">
+    <row r="122" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="14">
-        <v>20099004</v>
+        <v>20099003</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G122" s="4"/>
       <c r="I122" s="6" t="s">
@@ -8278,7 +7747,7 @@
       <c r="J122" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M122" s="25" t="s">
+      <c r="M122" s="24" t="s">
         <v>567</v>
       </c>
       <c r="N122" s="5" t="s">
@@ -8288,22 +7757,22 @@
         <v>180</v>
       </c>
       <c r="S122" s="15" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="T122" s="16" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="V122" s="16"/>
     </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:22">
+    <row r="123" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="14">
-        <v>20099005</v>
+        <v>20099004</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G123" s="4"/>
       <c r="I123" s="6" t="s">
@@ -8312,7 +7781,7 @@
       <c r="J123" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M123" s="25" t="s">
+      <c r="M123" s="24" t="s">
         <v>567</v>
       </c>
       <c r="N123" s="5" t="s">
@@ -8322,22 +7791,22 @@
         <v>180</v>
       </c>
       <c r="S123" s="15" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="T123" s="16" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="V123" s="16"/>
     </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:22">
+    <row r="124" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C124" s="14">
-        <v>20099006</v>
+        <v>20099005</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>353</v>
+        <v>581</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G124" s="4"/>
       <c r="I124" s="6" t="s">
@@ -8346,8 +7815,8 @@
       <c r="J124" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M124" s="14">
-        <v>20001005</v>
+      <c r="M124" s="24" t="s">
+        <v>567</v>
       </c>
       <c r="N124" s="5" t="s">
         <v>380</v>
@@ -8356,176 +7825,177 @@
         <v>180</v>
       </c>
       <c r="S124" s="15" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="T124" s="16" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="V124" s="16"/>
     </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:22">
+    <row r="125" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="14">
-        <v>20099007</v>
+        <v>20099006</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>588</v>
+        <v>353</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G125" s="4"/>
-      <c r="H125" s="4">
-        <v>1057</v>
-      </c>
-      <c r="M125" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="N125" s="30" t="s">
-        <v>590</v>
+      <c r="I125" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M125" s="14">
+        <v>20001005</v>
+      </c>
+      <c r="N125" s="5" t="s">
+        <v>380</v>
       </c>
       <c r="O125" s="5">
         <v>180</v>
       </c>
-      <c r="S125" s="28"/>
-      <c r="T125" s="16"/>
+      <c r="S125" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="T125" s="16" t="s">
+        <v>587</v>
+      </c>
       <c r="V125" s="16"/>
     </row>
-    <row r="126" ht="20.1" customHeight="1" spans="3:22">
+    <row r="126" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C126" s="14">
+        <v>20099007</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4">
+        <v>1057</v>
+      </c>
+      <c r="M126" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="N126" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="O126" s="5">
+        <v>180</v>
+      </c>
+      <c r="S126" s="27"/>
+      <c r="T126" s="16"/>
+      <c r="V126" s="16"/>
+    </row>
+    <row r="127" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C127" s="14">
         <v>20099008</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="E127" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="F126" s="4" t="s">
+      <c r="F127" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="G126" s="4"/>
-      <c r="M126" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="N126" s="30" t="s">
-        <v>594</v>
-      </c>
-      <c r="O126" s="5">
-        <v>0</v>
-      </c>
-      <c r="S126" s="28" t="s">
-        <v>595</v>
-      </c>
-      <c r="T126" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="V126" s="16"/>
-    </row>
-    <row r="127" ht="20.1" customHeight="1" spans="3:22">
-      <c r="C127" s="14">
-        <v>20099009</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>598</v>
       </c>
       <c r="G127" s="4"/>
       <c r="M127" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="N127" s="30" t="s">
-        <v>600</v>
+        <v>593</v>
+      </c>
+      <c r="N127" s="29" t="s">
+        <v>594</v>
       </c>
       <c r="O127" s="5">
         <v>0</v>
       </c>
-      <c r="S127" s="28" t="s">
-        <v>601</v>
+      <c r="S127" s="27" t="s">
+        <v>595</v>
       </c>
       <c r="T127" s="16" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="V127" s="16"/>
     </row>
-    <row r="128" ht="20.1" customHeight="1" spans="3:22">
+    <row r="128" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="14">
-        <v>20099010</v>
+        <v>20099009</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="G128" s="4"/>
       <c r="M128" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="N128" s="29" t="s">
+        <v>600</v>
+      </c>
+      <c r="O128" s="5">
+        <v>0</v>
+      </c>
+      <c r="S128" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="T128" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="V128" s="16"/>
+    </row>
+    <row r="129" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="14">
+        <v>20099010</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="G129" s="4"/>
+      <c r="M129" s="14" t="s">
         <v>605</v>
       </c>
-      <c r="N128" s="30" t="s">
+      <c r="N129" s="29" t="s">
         <v>606</v>
       </c>
-      <c r="O128" s="5">
-        <v>0</v>
-      </c>
-      <c r="S128" s="28" t="s">
+      <c r="O129" s="5">
+        <v>0</v>
+      </c>
+      <c r="S129" s="27" t="s">
         <v>607</v>
       </c>
-      <c r="T128" s="16" t="s">
+      <c r="T129" s="16" t="s">
         <v>608</v>
       </c>
-      <c r="V128" s="16"/>
-    </row>
-    <row r="129" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C129" s="14">
+      <c r="V129" s="16"/>
+    </row>
+    <row r="130" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="14">
         <v>20099011</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="E130" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="F130" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="G129" s="4"/>
-      <c r="K129" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="M129" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="N129" s="30" t="s">
-        <v>594</v>
-      </c>
-      <c r="O129" s="5">
-        <v>0</v>
-      </c>
-      <c r="P129" s="5">
-        <v>13</v>
-      </c>
-      <c r="Q129" s="35" t="s">
-        <v>612</v>
-      </c>
-      <c r="S129" s="28"/>
-      <c r="T129" s="16"/>
-      <c r="V129" s="16"/>
-    </row>
-    <row r="130" ht="20.1" customHeight="1" spans="1:28">
-      <c r="C130" s="14">
-        <v>20099012</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>614</v>
       </c>
       <c r="G130" s="4"/>
       <c r="K130" s="6" t="s">
         <v>611</v>
       </c>
       <c r="M130" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="N130" s="30" t="s">
-        <v>600</v>
+        <v>593</v>
+      </c>
+      <c r="N130" s="29" t="s">
+        <v>594</v>
       </c>
       <c r="O130" s="5">
         <v>0</v>
@@ -8533,32 +8003,32 @@
       <c r="P130" s="5">
         <v>13</v>
       </c>
-      <c r="Q130" s="35" t="s">
+      <c r="Q130" s="34" t="s">
         <v>612</v>
       </c>
-      <c r="S130" s="28"/>
+      <c r="S130" s="27"/>
       <c r="T130" s="16"/>
       <c r="V130" s="16"/>
     </row>
-    <row r="131" ht="20.1" customHeight="1" spans="1:28">
+    <row r="131" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="14">
-        <v>20099013</v>
+        <v>20099012</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G131" s="4"/>
       <c r="K131" s="6" t="s">
         <v>611</v>
       </c>
       <c r="M131" s="14" t="s">
-        <v>605</v>
-      </c>
-      <c r="N131" s="30" t="s">
-        <v>606</v>
+        <v>599</v>
+      </c>
+      <c r="N131" s="29" t="s">
+        <v>600</v>
       </c>
       <c r="O131" s="5">
         <v>0</v>
@@ -8566,78 +8036,66 @@
       <c r="P131" s="5">
         <v>13</v>
       </c>
-      <c r="Q131" s="35" t="s">
+      <c r="Q131" s="34" t="s">
         <v>612</v>
       </c>
-      <c r="S131" s="28"/>
+      <c r="S131" s="27"/>
       <c r="T131" s="16"/>
       <c r="V131" s="16"/>
     </row>
-    <row r="132" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
-      <c r="A132" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="D132" s="5"/>
-      <c r="E132" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="F132" s="29" t="s">
-        <v>620</v>
-      </c>
-      <c r="G132" s="5">
-        <v>300001</v>
-      </c>
-      <c r="H132" s="4">
-        <v>1034</v>
-      </c>
-      <c r="I132" s="4">
-        <v>0</v>
-      </c>
-      <c r="J132" s="4">
-        <v>0</v>
-      </c>
-      <c r="K132" s="4"/>
-      <c r="L132" s="3"/>
-      <c r="M132" s="29" t="s">
-        <v>621</v>
-      </c>
-      <c r="N132" s="33" t="s">
-        <v>622</v>
+    <row r="132" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C132" s="14">
+        <v>20099013</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="G132" s="4"/>
+      <c r="K132" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="M132" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="N132" s="29" t="s">
+        <v>606</v>
       </c>
       <c r="O132" s="5">
         <v>0</v>
       </c>
-      <c r="P132" s="5"/>
-      <c r="Q132" s="26"/>
-      <c r="S132" s="25"/>
+      <c r="P132" s="5">
+        <v>13</v>
+      </c>
+      <c r="Q132" s="34" t="s">
+        <v>612</v>
+      </c>
+      <c r="S132" s="27"/>
       <c r="T132" s="16"/>
       <c r="V132" s="16"/>
-      <c r="X132" s="5"/>
-      <c r="Y132" s="5"/>
-      <c r="Z132" s="5"/>
-      <c r="AA132" s="5"/>
-      <c r="AB132" s="5"/>
-    </row>
-    <row r="133" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
-      <c r="A133" s="3"/>
+    </row>
+    <row r="133" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="B133" s="3"/>
       <c r="C133" s="17" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D133" s="5"/>
-      <c r="E133" s="29" t="s">
-        <v>624</v>
-      </c>
-      <c r="F133" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="G133" s="5"/>
+      <c r="E133" s="28" t="s">
+        <v>619</v>
+      </c>
+      <c r="F133" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="G133" s="5">
+        <v>300001</v>
+      </c>
       <c r="H133" s="4">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="I133" s="4">
         <v>0</v>
@@ -8647,18 +8105,18 @@
       </c>
       <c r="K133" s="4"/>
       <c r="L133" s="3"/>
-      <c r="M133" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="N133" s="33" t="s">
-        <v>627</v>
+      <c r="M133" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="N133" s="32" t="s">
+        <v>622</v>
       </c>
       <c r="O133" s="5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P133" s="5"/>
-      <c r="Q133" s="26"/>
-      <c r="S133" s="25"/>
+      <c r="Q133" s="25"/>
+      <c r="S133" s="24"/>
       <c r="T133" s="16"/>
       <c r="V133" s="16"/>
       <c r="X133" s="5"/>
@@ -8667,22 +8125,22 @@
       <c r="AA133" s="5"/>
       <c r="AB133" s="5"/>
     </row>
-    <row r="134" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="134" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="17" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D134" s="5"/>
-      <c r="E134" s="29" t="s">
-        <v>629</v>
-      </c>
-      <c r="F134" s="29" t="s">
-        <v>630</v>
+      <c r="E134" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="F134" s="28" t="s">
+        <v>625</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="I134" s="4">
         <v>0</v>
@@ -8692,17 +8150,18 @@
       </c>
       <c r="K134" s="4"/>
       <c r="L134" s="3"/>
-      <c r="M134" s="29" t="s">
-        <v>631</v>
-      </c>
-      <c r="N134" s="33" t="s">
-        <v>632</v>
+      <c r="M134" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="N134" s="32" t="s">
+        <v>627</v>
       </c>
       <c r="O134" s="5">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="P134" s="5"/>
-      <c r="S134" s="25"/>
+      <c r="Q134" s="25"/>
+      <c r="S134" s="24"/>
       <c r="T134" s="16"/>
       <c r="V134" s="16"/>
       <c r="X134" s="5"/>
@@ -8711,22 +8170,22 @@
       <c r="AA134" s="5"/>
       <c r="AB134" s="5"/>
     </row>
-    <row r="135" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
+    <row r="135" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="17" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D135" s="5"/>
-      <c r="E135" s="29" t="s">
-        <v>634</v>
-      </c>
-      <c r="F135" s="29" t="s">
-        <v>635</v>
+      <c r="E135" s="28" t="s">
+        <v>629</v>
+      </c>
+      <c r="F135" s="28" t="s">
+        <v>630</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="4">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="I135" s="4">
         <v>0</v>
@@ -8736,17 +8195,17 @@
       </c>
       <c r="K135" s="4"/>
       <c r="L135" s="3"/>
-      <c r="M135" s="29" t="s">
-        <v>636</v>
-      </c>
-      <c r="N135" s="26" t="s">
-        <v>637</v>
+      <c r="M135" s="28" t="s">
+        <v>631</v>
+      </c>
+      <c r="N135" s="32" t="s">
+        <v>632</v>
       </c>
       <c r="O135" s="5">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="P135" s="5"/>
-      <c r="S135" s="25"/>
+      <c r="S135" s="24"/>
       <c r="T135" s="16"/>
       <c r="V135" s="16"/>
       <c r="X135" s="5"/>
@@ -8755,18 +8214,22 @@
       <c r="AA135" s="5"/>
       <c r="AB135" s="5"/>
     </row>
-    <row r="136" ht="20.1" customHeight="1" spans="1:28">
+    <row r="136" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
       <c r="C136" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="E136" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="F136" s="29" t="s">
-        <v>640</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="D136" s="5"/>
+      <c r="E136" s="28" t="s">
+        <v>634</v>
+      </c>
+      <c r="F136" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="G136" s="5"/>
       <c r="H136" s="4">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="I136" s="4">
         <v>0</v>
@@ -8775,30 +8238,38 @@
         <v>0</v>
       </c>
       <c r="K136" s="4"/>
-      <c r="M136" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="N136" s="26" t="s">
-        <v>641</v>
+      <c r="L136" s="3"/>
+      <c r="M136" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="N136" s="25" t="s">
+        <v>637</v>
       </c>
       <c r="O136" s="5">
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P136" s="5"/>
+      <c r="S136" s="24"/>
       <c r="T136" s="16"/>
       <c r="V136" s="16"/>
-    </row>
-    <row r="137" ht="20.1" customHeight="1" spans="1:28">
+      <c r="X136" s="5"/>
+      <c r="Y136" s="5"/>
+      <c r="Z136" s="5"/>
+      <c r="AA136" s="5"/>
+      <c r="AB136" s="5"/>
+    </row>
+    <row r="137" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="17" t="s">
-        <v>642</v>
-      </c>
-      <c r="E137" s="29" t="s">
-        <v>643</v>
-      </c>
-      <c r="F137" s="29" t="s">
-        <v>644</v>
+        <v>638</v>
+      </c>
+      <c r="E137" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="F137" s="28" t="s">
+        <v>640</v>
       </c>
       <c r="H137" s="4">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="I137" s="4">
         <v>0</v>
@@ -8807,30 +8278,30 @@
         <v>0</v>
       </c>
       <c r="K137" s="4"/>
-      <c r="M137" s="29" t="s">
-        <v>645</v>
-      </c>
-      <c r="N137" s="33" t="s">
-        <v>646</v>
+      <c r="M137" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="N137" s="25" t="s">
+        <v>641</v>
       </c>
       <c r="O137" s="5">
-        <v>123</v>
+        <v>-100</v>
       </c>
       <c r="T137" s="16"/>
       <c r="V137" s="16"/>
     </row>
-    <row r="138" ht="20.1" customHeight="1" spans="1:28">
+    <row r="138" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="17" t="s">
-        <v>647</v>
-      </c>
-      <c r="E138" s="29" t="s">
-        <v>648</v>
-      </c>
-      <c r="F138" s="29" t="s">
-        <v>649</v>
+        <v>642</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="F138" s="28" t="s">
+        <v>644</v>
       </c>
       <c r="H138" s="4">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="I138" s="4">
         <v>0</v>
@@ -8839,26 +8310,26 @@
         <v>0</v>
       </c>
       <c r="K138" s="4"/>
-      <c r="M138" s="29" t="s">
-        <v>650</v>
-      </c>
-      <c r="N138" s="26" t="s">
-        <v>651</v>
+      <c r="M138" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="N138" s="32" t="s">
+        <v>646</v>
       </c>
       <c r="O138" s="5">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="T138" s="16"/>
       <c r="V138" s="16"/>
     </row>
-    <row r="139" ht="20.1" customHeight="1" spans="1:28">
+    <row r="139" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="17" t="s">
-        <v>652</v>
-      </c>
-      <c r="E139" s="29" t="s">
+        <v>647</v>
+      </c>
+      <c r="E139" s="28" t="s">
         <v>648</v>
       </c>
-      <c r="F139" s="29" t="s">
+      <c r="F139" s="28" t="s">
         <v>649</v>
       </c>
       <c r="H139" s="4">
@@ -8871,30 +8342,30 @@
         <v>0</v>
       </c>
       <c r="K139" s="4"/>
-      <c r="M139" s="29" t="s">
+      <c r="M139" s="28" t="s">
         <v>650</v>
       </c>
-      <c r="N139" s="26" t="s">
-        <v>653</v>
+      <c r="N139" s="25" t="s">
+        <v>651</v>
       </c>
       <c r="O139" s="5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="T139" s="16"/>
       <c r="V139" s="16"/>
     </row>
-    <row r="140" ht="20.1" customHeight="1" spans="1:28">
+    <row r="140" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="17" t="s">
-        <v>654</v>
-      </c>
-      <c r="E140" s="29" t="s">
-        <v>655</v>
-      </c>
-      <c r="F140" s="29" t="s">
-        <v>656</v>
+        <v>652</v>
+      </c>
+      <c r="E140" s="28" t="s">
+        <v>648</v>
+      </c>
+      <c r="F140" s="28" t="s">
+        <v>649</v>
       </c>
       <c r="H140" s="4">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="I140" s="4">
         <v>0</v>
@@ -8903,30 +8374,30 @@
         <v>0</v>
       </c>
       <c r="K140" s="4"/>
-      <c r="M140" s="29" t="s">
-        <v>657</v>
-      </c>
-      <c r="N140" s="26" t="s">
-        <v>658</v>
+      <c r="M140" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="N140" s="25" t="s">
+        <v>653</v>
       </c>
       <c r="O140" s="5">
-        <v>-90</v>
+        <v>270</v>
       </c>
       <c r="T140" s="16"/>
       <c r="V140" s="16"/>
     </row>
-    <row r="141" ht="20.1" customHeight="1" spans="1:28">
+    <row r="141" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="17" t="s">
-        <v>659</v>
-      </c>
-      <c r="E141" s="29" t="s">
-        <v>660</v>
-      </c>
-      <c r="F141" s="29" t="s">
-        <v>661</v>
+        <v>654</v>
+      </c>
+      <c r="E141" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="F141" s="28" t="s">
+        <v>656</v>
       </c>
       <c r="H141" s="4">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="I141" s="4">
         <v>0</v>
@@ -8935,30 +8406,30 @@
         <v>0</v>
       </c>
       <c r="K141" s="4"/>
-      <c r="M141" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="N141" s="26" t="s">
-        <v>662</v>
+      <c r="M141" s="28" t="s">
+        <v>657</v>
+      </c>
+      <c r="N141" s="25" t="s">
+        <v>658</v>
       </c>
       <c r="O141" s="5">
-        <v>-150</v>
+        <v>-90</v>
       </c>
       <c r="T141" s="16"/>
       <c r="V141" s="16"/>
     </row>
-    <row r="142" ht="20.1" customHeight="1" spans="1:28">
+    <row r="142" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="E142" s="29" t="s">
-        <v>664</v>
-      </c>
-      <c r="F142" s="29" t="s">
-        <v>665</v>
+        <v>659</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="F142" s="28" t="s">
+        <v>661</v>
       </c>
       <c r="H142" s="4">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="I142" s="4">
         <v>0</v>
@@ -8967,37 +8438,30 @@
         <v>0</v>
       </c>
       <c r="K142" s="4"/>
-      <c r="M142" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="N142" s="32" t="s">
-        <v>666</v>
-      </c>
-      <c r="O142" s="4">
-        <v>90</v>
-      </c>
-      <c r="P142" s="4"/>
+      <c r="M142" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="N142" s="25" t="s">
+        <v>662</v>
+      </c>
+      <c r="O142" s="5">
+        <v>-150</v>
+      </c>
       <c r="T142" s="16"/>
       <c r="V142" s="16"/>
     </row>
-    <row r="143" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:28">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
+    <row r="143" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C143" s="17" t="s">
-        <v>667</v>
-      </c>
-      <c r="D143" s="5"/>
-      <c r="E143" s="29" t="s">
-        <v>668</v>
-      </c>
-      <c r="F143" s="29" t="s">
-        <v>669</v>
-      </c>
-      <c r="G143" s="5">
-        <v>400001</v>
+        <v>663</v>
+      </c>
+      <c r="E143" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="F143" s="28" t="s">
+        <v>665</v>
       </c>
       <c r="H143" s="4">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="I143" s="4">
         <v>0</v>
@@ -9006,37 +8470,37 @@
         <v>0</v>
       </c>
       <c r="K143" s="4"/>
-      <c r="L143" s="3"/>
-      <c r="M143" s="29" t="s">
+      <c r="M143" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="N143" s="33" t="s">
-        <v>670</v>
-      </c>
-      <c r="O143" s="5">
-        <v>110</v>
-      </c>
-      <c r="P143" s="5"/>
+      <c r="N143" s="31" t="s">
+        <v>666</v>
+      </c>
+      <c r="O143" s="4">
+        <v>90</v>
+      </c>
+      <c r="P143" s="4"/>
       <c r="T143" s="16"/>
       <c r="V143" s="16"/>
-      <c r="X143" s="5"/>
-      <c r="Y143" s="5"/>
-      <c r="Z143" s="5"/>
-      <c r="AA143" s="5"/>
-      <c r="AB143" s="5"/>
-    </row>
-    <row r="144" ht="20.1" customHeight="1" spans="1:28">
+    </row>
+    <row r="144" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
       <c r="C144" s="17" t="s">
-        <v>671</v>
-      </c>
-      <c r="E144" s="29" t="s">
-        <v>672</v>
-      </c>
-      <c r="F144" s="29" t="s">
-        <v>673</v>
+        <v>667</v>
+      </c>
+      <c r="D144" s="5"/>
+      <c r="E144" s="28" t="s">
+        <v>668</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>669</v>
+      </c>
+      <c r="G144" s="5">
+        <v>400001</v>
       </c>
       <c r="H144" s="4">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="I144" s="4">
         <v>0</v>
@@ -9045,30 +8509,37 @@
         <v>0</v>
       </c>
       <c r="K144" s="4"/>
-      <c r="M144" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="N144" s="33" t="s">
-        <v>674</v>
+      <c r="L144" s="3"/>
+      <c r="M144" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="N144" s="32" t="s">
+        <v>670</v>
       </c>
       <c r="O144" s="5">
-        <v>173</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="P144" s="5"/>
       <c r="T144" s="16"/>
       <c r="V144" s="16"/>
-    </row>
-    <row r="145" ht="20.1" customHeight="1" spans="3:22">
+      <c r="X144" s="5"/>
+      <c r="Y144" s="5"/>
+      <c r="Z144" s="5"/>
+      <c r="AA144" s="5"/>
+      <c r="AB144" s="5"/>
+    </row>
+    <row r="145" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C145" s="17" t="s">
-        <v>675</v>
-      </c>
-      <c r="E145" s="29" t="s">
-        <v>676</v>
-      </c>
-      <c r="F145" s="29" t="s">
-        <v>677</v>
+        <v>671</v>
+      </c>
+      <c r="E145" s="28" t="s">
+        <v>672</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>673</v>
       </c>
       <c r="H145" s="4">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="I145" s="4">
         <v>0</v>
@@ -9077,30 +8548,30 @@
         <v>0</v>
       </c>
       <c r="K145" s="4"/>
-      <c r="M145" s="29" t="s">
-        <v>650</v>
-      </c>
-      <c r="N145" s="33" t="s">
-        <v>678</v>
+      <c r="M145" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="N145" s="32" t="s">
+        <v>674</v>
       </c>
       <c r="O145" s="5">
-        <v>235</v>
+        <v>173</v>
       </c>
       <c r="T145" s="16"/>
       <c r="V145" s="16"/>
     </row>
-    <row r="146" ht="20.1" customHeight="1" spans="3:22">
+    <row r="146" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="17" t="s">
-        <v>679</v>
-      </c>
-      <c r="E146" s="29" t="s">
-        <v>680</v>
-      </c>
-      <c r="F146" s="29" t="s">
-        <v>681</v>
+        <v>675</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>677</v>
       </c>
       <c r="H146" s="4">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="I146" s="4">
         <v>0</v>
@@ -9109,30 +8580,30 @@
         <v>0</v>
       </c>
       <c r="K146" s="4"/>
-      <c r="M146" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="N146" s="33" t="s">
-        <v>682</v>
+      <c r="M146" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="N146" s="32" t="s">
+        <v>678</v>
       </c>
       <c r="O146" s="5">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="T146" s="16"/>
       <c r="V146" s="16"/>
     </row>
-    <row r="147" ht="20.1" customHeight="1" spans="3:22">
+    <row r="147" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="17" t="s">
-        <v>683</v>
-      </c>
-      <c r="E147" s="29" t="s">
-        <v>684</v>
-      </c>
-      <c r="F147" s="29" t="s">
-        <v>685</v>
+        <v>679</v>
+      </c>
+      <c r="E147" s="28" t="s">
+        <v>680</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>681</v>
       </c>
       <c r="H147" s="4">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="I147" s="4">
         <v>0</v>
@@ -9141,11 +8612,11 @@
         <v>0</v>
       </c>
       <c r="K147" s="4"/>
-      <c r="M147" s="29" t="s">
+      <c r="M147" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="N147" s="33" t="s">
-        <v>686</v>
+      <c r="N147" s="32" t="s">
+        <v>682</v>
       </c>
       <c r="O147" s="5">
         <v>175</v>
@@ -9153,15 +8624,15 @@
       <c r="T147" s="16"/>
       <c r="V147" s="16"/>
     </row>
-    <row r="148" ht="20.1" customHeight="1" spans="3:22">
+    <row r="148" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="17" t="s">
-        <v>687</v>
-      </c>
-      <c r="E148" s="29" t="s">
-        <v>688</v>
-      </c>
-      <c r="F148" s="29" t="s">
-        <v>689</v>
+        <v>683</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>685</v>
       </c>
       <c r="H148" s="4">
         <v>1054</v>
@@ -9173,11 +8644,11 @@
         <v>0</v>
       </c>
       <c r="K148" s="4"/>
-      <c r="M148" s="29" t="s">
+      <c r="M148" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="N148" s="33" t="s">
-        <v>690</v>
+      <c r="N148" s="32" t="s">
+        <v>686</v>
       </c>
       <c r="O148" s="5">
         <v>175</v>
@@ -9185,18 +8656,18 @@
       <c r="T148" s="16"/>
       <c r="V148" s="16"/>
     </row>
-    <row r="149" ht="20.1" customHeight="1" spans="3:22">
+    <row r="149" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C149" s="17" t="s">
-        <v>691</v>
-      </c>
-      <c r="E149" s="29" t="s">
-        <v>692</v>
-      </c>
-      <c r="F149" s="29" t="s">
-        <v>693</v>
+        <v>687</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>689</v>
       </c>
       <c r="H149" s="4">
-        <v>10</v>
+        <v>1054</v>
       </c>
       <c r="I149" s="4">
         <v>0</v>
@@ -9205,10 +8676,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="4"/>
-      <c r="M149" s="29" t="s">
-        <v>694</v>
-      </c>
-      <c r="N149" s="33" t="s">
+      <c r="M149" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="N149" s="32" t="s">
         <v>690</v>
       </c>
       <c r="O149" s="5">
@@ -9217,18 +8688,18 @@
       <c r="T149" s="16"/>
       <c r="V149" s="16"/>
     </row>
-    <row r="150" ht="20.1" customHeight="1" spans="3:22">
+    <row r="150" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C150" s="17" t="s">
-        <v>695</v>
-      </c>
-      <c r="E150" s="29" t="s">
-        <v>696</v>
-      </c>
-      <c r="F150" s="29" t="s">
-        <v>697</v>
+        <v>691</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>693</v>
       </c>
       <c r="H150" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I150" s="4">
         <v>0</v>
@@ -9237,35 +8708,67 @@
         <v>0</v>
       </c>
       <c r="K150" s="4"/>
-      <c r="M150" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="N150" s="33" t="s">
-        <v>698</v>
+      <c r="M150" s="28" t="s">
+        <v>694</v>
+      </c>
+      <c r="N150" s="32" t="s">
+        <v>690</v>
       </c>
       <c r="O150" s="5">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="T150" s="16"/>
       <c r="V150" s="16"/>
     </row>
-    <row r="151" ht="20.1" customHeight="1"/>
-    <row r="152" ht="20.1" customHeight="1"/>
-    <row r="153" ht="20.1" customHeight="1"/>
-    <row r="154" ht="20.1" customHeight="1"/>
-    <row r="155" ht="20.1" customHeight="1"/>
-    <row r="156" ht="20.1" customHeight="1"/>
-    <row r="157" ht="20.1" customHeight="1"/>
-    <row r="158" ht="20.1" customHeight="1"/>
-    <row r="159" ht="20.1" customHeight="1"/>
-    <row r="160" ht="20.1" customHeight="1"/>
-    <row r="161" ht="20.1" customHeight="1"/>
-    <row r="162" ht="20.1" customHeight="1"/>
-    <row r="163" ht="20.1" customHeight="1"/>
+    <row r="151" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="17" t="s">
+        <v>695</v>
+      </c>
+      <c r="E151" s="28" t="s">
+        <v>696</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>697</v>
+      </c>
+      <c r="H151" s="4">
+        <v>19</v>
+      </c>
+      <c r="I151" s="4">
+        <v>0</v>
+      </c>
+      <c r="J151" s="4">
+        <v>0</v>
+      </c>
+      <c r="K151" s="4"/>
+      <c r="M151" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="N151" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="O151" s="5">
+        <v>180</v>
+      </c>
+      <c r="T151" s="16"/>
+      <c r="V151" s="16"/>
+    </row>
+    <row r="152" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85E558E-868F-4EBB-A244-3E660FD66472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC5A736-D8AE-473B-923B-22783CC8D623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="709">
   <si>
     <t>#</t>
   </si>
@@ -2689,6 +2689,14 @@
   </si>
   <si>
     <t>Hey, hero! These exotic treasures are only worthy of someone like you!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC_ZaHuo</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC_ZaHuo_2</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -5017,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="14" t="s">
-        <v>70</v>
+        <v>707</v>
       </c>
       <c r="N45" s="29" t="s">
         <v>269</v>
@@ -5320,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>70</v>
+        <v>708</v>
       </c>
       <c r="N53" s="29" t="s">
         <v>701</v>

--- a/Excel/NpcConfig.xlsx
+++ b/Excel/NpcConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC5A736-D8AE-473B-923B-22783CC8D623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CD45C9-361D-41BD-976A-F35A561EDDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
